--- a/MS BENGKAYANG 19 JULI 2026.xlsx
+++ b/MS BENGKAYANG 19 JULI 2026.xlsx
@@ -278,7 +278,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="43" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
@@ -305,7 +305,6 @@
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="164" fontId="5" fillId="5" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
@@ -659,31 +658,31 @@
       </c>
       <c r="C6" s="5">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>7511420.9336513663</v>
+        <v>8660479.7989407126</v>
       </c>
       <c r="D6" s="5">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>7507509.8967372607</v>
+        <v>7510668.6871368838</v>
       </c>
       <c r="E6" s="5">
         <f>VLOOKUP(A:A,MASTER!A:H,8,0)</f>
-        <v>229029889.1891892</v>
+        <v>232469742.34234235</v>
       </c>
       <c r="F6" s="5">
         <f>VLOOKUP(A:A,MASTER!A:I,9,0)</f>
-        <v>99612883.783783779</v>
+        <v>148396432.43243244</v>
       </c>
       <c r="G6" s="5">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>0</v>
+        <v>533558.55855855905</v>
       </c>
       <c r="H6" s="5">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>90090.090090090001</v>
+        <v>158558.558558558</v>
       </c>
       <c r="I6" s="5">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
-        <v>4061855.8558558561</v>
+        <v>4872702.702702703</v>
       </c>
       <c r="J6" s="5">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
@@ -707,43 +706,43 @@
       </c>
       <c r="C7" s="5">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>196176570.97486886</v>
+        <v>221769958.63266039</v>
       </c>
       <c r="D7" s="5">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>199414498.13007444</v>
+        <v>229044753.07596684</v>
       </c>
       <c r="E7" s="5">
         <f>VLOOKUP(A:A,MASTER!A:H,8,0)</f>
-        <v>2845945.945945947</v>
+        <v>4406306.3063063063</v>
       </c>
       <c r="F7" s="5">
         <f>VLOOKUP(A:A,MASTER!A:I,9,0)</f>
-        <v>3820720.7207207172</v>
+        <v>4004504.5045045</v>
       </c>
       <c r="G7" s="5">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>68249549.54954955</v>
+        <v>112500000</v>
       </c>
       <c r="H7" s="5">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>154871801.8018018</v>
+        <v>155177207.2072072</v>
       </c>
       <c r="I7" s="5">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
-        <v>131342459.45945945</v>
+        <v>152323765.76576576</v>
       </c>
       <c r="J7" s="5">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>130473117.11711712</v>
+        <v>150183072.07207206</v>
       </c>
       <c r="K7" s="5">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>59288558.558558561</v>
+        <v>105400720.72072072</v>
       </c>
       <c r="L7" s="5">
         <f>VLOOKUP(A:A,MASTER!A:C,3,0)</f>
-        <v>136425855.85585585</v>
+        <v>140731621.62162161</v>
       </c>
     </row>
     <row r="8" spans="1:12" ht="64.5" customHeight="1" x14ac:dyDescent="0.35">
@@ -755,43 +754,43 @@
       </c>
       <c r="C8" s="5">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>49393746.862353623</v>
+        <v>55784970.612387374</v>
       </c>
       <c r="D8" s="5">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>48616953.909952343</v>
+        <v>55050728.680071183</v>
       </c>
       <c r="E8" s="5">
         <f>VLOOKUP(A:A,MASTER!A:H,8,0)</f>
-        <v>136936.936936938</v>
+        <v>152252.25225225301</v>
       </c>
       <c r="F8" s="5">
         <f>VLOOKUP(A:A,MASTER!A:I,9,0)</f>
-        <v>27027.027027027001</v>
+        <v>37837.837837838</v>
       </c>
       <c r="G8" s="5">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>6997297.2972972961</v>
+        <v>7012612.6126126107</v>
       </c>
       <c r="H8" s="5">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>9277027.027027024</v>
+        <v>19690990.990990993</v>
       </c>
       <c r="I8" s="5">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
-        <v>34849666.666666664</v>
+        <v>39424072.072072074</v>
       </c>
       <c r="J8" s="5">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>31194990.990990993</v>
+        <v>35650486.486486487</v>
       </c>
       <c r="K8" s="5">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>8593423.4234234225</v>
+        <v>8717387.3873873875</v>
       </c>
       <c r="L8" s="5">
         <f>VLOOKUP(A:A,MASTER!A:C,3,0)</f>
-        <v>9835315.3153153118</v>
+        <v>20225225.225225225</v>
       </c>
     </row>
     <row r="9" spans="1:12" ht="64.5" customHeight="1" x14ac:dyDescent="0.35">
@@ -803,35 +802,35 @@
       </c>
       <c r="C9" s="5">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>52030457.127091497</v>
+        <v>59447255.050917439</v>
       </c>
       <c r="D9" s="5">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>57426483.631933667</v>
+        <v>64839617.028884411</v>
       </c>
       <c r="E9" s="5">
         <f>VLOOKUP(A:A,MASTER!A:H,8,0)</f>
-        <v>3378378.3783783782</v>
+        <v>0</v>
       </c>
       <c r="F9" s="5">
         <f>VLOOKUP(A:A,MASTER!A:I,9,0)</f>
-        <v>47477477.477477483</v>
+        <v>0</v>
       </c>
       <c r="G9" s="5">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>315540.540540541</v>
+        <v>0</v>
       </c>
       <c r="H9" s="5">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>14414.414414413999</v>
+        <v>0</v>
       </c>
       <c r="I9" s="5">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
-        <v>31396702.702702705</v>
+        <v>35940792.79279279</v>
       </c>
       <c r="J9" s="5">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>34195801.801801801</v>
+        <v>39796477.477477483</v>
       </c>
       <c r="K9" s="5">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
@@ -851,11 +850,11 @@
       </c>
       <c r="C10" s="5">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>45012979.346594982</v>
+        <v>51389036.302047253</v>
       </c>
       <c r="D10" s="5">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>45436787.487359814</v>
+        <v>51054003.623513147</v>
       </c>
       <c r="E10" s="5">
         <f>VLOOKUP(A:A,MASTER!A:H,8,0)</f>
@@ -863,7 +862,7 @@
       </c>
       <c r="F10" s="5">
         <f>VLOOKUP(A:A,MASTER!A:I,9,0)</f>
-        <v>9009.0090090089998</v>
+        <v>18018.018018018</v>
       </c>
       <c r="G10" s="5">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
@@ -871,15 +870,15 @@
       </c>
       <c r="H10" s="5">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>639639.63963963999</v>
+        <v>648648.64864864899</v>
       </c>
       <c r="I10" s="5">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
-        <v>15800657.657657657</v>
+        <v>17627540.540540539</v>
       </c>
       <c r="J10" s="5">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>19452351.351351351</v>
+        <v>21593117.117117114</v>
       </c>
       <c r="K10" s="5">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
@@ -887,7 +886,7 @@
       </c>
       <c r="L10" s="5">
         <f>VLOOKUP(A:A,MASTER!A:C,3,0)</f>
-        <v>728108.10810810805</v>
+        <v>849729.72972973005</v>
       </c>
     </row>
     <row r="11" spans="1:12" ht="64.5" customHeight="1" x14ac:dyDescent="0.35">
@@ -899,43 +898,43 @@
       </c>
       <c r="C11" s="5">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>28913433.219965655</v>
+        <v>33166530.840455465</v>
       </c>
       <c r="D11" s="5">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>31805391.81232474</v>
+        <v>35688394.586691581</v>
       </c>
       <c r="E11" s="5">
         <f>VLOOKUP(A:A,MASTER!A:H,8,0)</f>
-        <v>54954.954954954999</v>
+        <v>279279.27927927999</v>
       </c>
       <c r="F11" s="5">
         <f>VLOOKUP(A:A,MASTER!A:I,9,0)</f>
-        <v>63063.063063062997</v>
+        <v>100900.900900901</v>
       </c>
       <c r="G11" s="5">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>54954.954954954999</v>
+        <v>2981981.981981982</v>
       </c>
       <c r="H11" s="5">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>513513.51351351303</v>
+        <v>551351.35135135101</v>
       </c>
       <c r="I11" s="5">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
-        <v>12292441.441441439</v>
+        <v>13945720.72072072</v>
       </c>
       <c r="J11" s="5">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>14513405.405405408</v>
+        <v>16015612.612612613</v>
       </c>
       <c r="K11" s="5">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>1597837.837837839</v>
+        <v>4705675.6756756762</v>
       </c>
       <c r="L11" s="5">
         <f>VLOOKUP(A:A,MASTER!A:C,3,0)</f>
-        <v>821171.17117117206</v>
+        <v>1931531.5315315309</v>
       </c>
     </row>
     <row r="12" spans="1:12" ht="64.5" customHeight="1" x14ac:dyDescent="0.35">
@@ -947,43 +946,43 @@
       </c>
       <c r="C12" s="5">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>116267585.84095243</v>
+        <v>132264920.29211617</v>
       </c>
       <c r="D12" s="5">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>126507289.14125644</v>
+        <v>142994835.09886238</v>
       </c>
       <c r="E12" s="5">
         <f>VLOOKUP(A:A,MASTER!A:H,8,0)</f>
-        <v>956756.75675675995</v>
+        <v>315073894.5945946</v>
       </c>
       <c r="F12" s="5">
         <f>VLOOKUP(A:A,MASTER!A:I,9,0)</f>
-        <v>523423.423423425</v>
+        <v>256209569.36936939</v>
       </c>
       <c r="G12" s="5">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>20454324.324324325</v>
+        <v>41743063.063063063</v>
       </c>
       <c r="H12" s="5">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>18734459.459459461</v>
+        <v>57606306.306306303</v>
       </c>
       <c r="I12" s="5">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
-        <v>56265009.009009011</v>
+        <v>64046747.747747742</v>
       </c>
       <c r="J12" s="5">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>57269711.711711712</v>
+        <v>65476054.054054059</v>
       </c>
       <c r="K12" s="5">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>15536576.576576579</v>
+        <v>16552522.522522526</v>
       </c>
       <c r="L12" s="5">
         <f>VLOOKUP(A:A,MASTER!A:C,3,0)</f>
-        <v>16872207.207207207</v>
+        <v>19355630.630630631</v>
       </c>
     </row>
     <row r="13" spans="1:12" ht="64.5" customHeight="1" x14ac:dyDescent="0.35">
@@ -995,43 +994,43 @@
       </c>
       <c r="C13" s="5">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>86248085.706081927</v>
+        <v>98339581.103002876</v>
       </c>
       <c r="D13" s="5">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>78619082.392572537</v>
+        <v>88025424.340662733</v>
       </c>
       <c r="E13" s="5">
         <f>VLOOKUP(A:A,MASTER!A:H,8,0)</f>
-        <v>1017117.117117118</v>
+        <v>1364864.864864866</v>
       </c>
       <c r="F13" s="5">
         <f>VLOOKUP(A:A,MASTER!A:I,9,0)</f>
-        <v>279279.27927927999</v>
+        <v>517567.56756756699</v>
       </c>
       <c r="G13" s="5">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>15818018.018018018</v>
+        <v>17967567.567567568</v>
       </c>
       <c r="H13" s="5">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>27872972.97297297</v>
+        <v>35318468.468468465</v>
       </c>
       <c r="I13" s="5">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
-        <v>24560612.612612613</v>
+        <v>28004486.486486487</v>
       </c>
       <c r="J13" s="5">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>22512063.063063063</v>
+        <v>24938810.810810812</v>
       </c>
       <c r="K13" s="5">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>13959999.999999998</v>
+        <v>16709189.189189188</v>
       </c>
       <c r="L13" s="5">
         <f>VLOOKUP(A:A,MASTER!A:C,3,0)</f>
-        <v>25294774.774774775</v>
+        <v>31392342.342342339</v>
       </c>
     </row>
     <row r="14" spans="1:12" ht="64.5" customHeight="1" x14ac:dyDescent="0.35">
@@ -1043,43 +1042,43 @@
       </c>
       <c r="C14" s="5">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>54837497.224373043</v>
+        <v>62404702.44519119</v>
       </c>
       <c r="D14" s="5">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>52939180.99643144</v>
+        <v>59767927.222687922</v>
       </c>
       <c r="E14" s="5">
         <f>VLOOKUP(A:A,MASTER!A:H,8,0)</f>
-        <v>76729729.729729727</v>
+        <v>581081.08108108304</v>
       </c>
       <c r="F14" s="5">
         <f>VLOOKUP(A:A,MASTER!A:I,9,0)</f>
-        <v>22752252.252252251</v>
+        <v>681081.08108108095</v>
       </c>
       <c r="G14" s="5">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>26411261.261261266</v>
+        <v>18331531.531531531</v>
       </c>
       <c r="H14" s="5">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>18085135.135135133</v>
+        <v>17289189.189189188</v>
       </c>
       <c r="I14" s="5">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
-        <v>18937099.0990991</v>
+        <v>21517324.324324325</v>
       </c>
       <c r="J14" s="5">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>20442684.684684683</v>
+        <v>23160972.972972974</v>
       </c>
       <c r="K14" s="5">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>17864054.054054052</v>
+        <v>18255495.495495494</v>
       </c>
       <c r="L14" s="5">
         <f>VLOOKUP(A:A,MASTER!A:C,3,0)</f>
-        <v>7227522.5225225221</v>
+        <v>18200990.990990993</v>
       </c>
     </row>
     <row r="15" spans="1:12" ht="64.5" customHeight="1" x14ac:dyDescent="0.35">
@@ -1091,43 +1090,43 @@
       </c>
       <c r="C15" s="5">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>58472443.376442537</v>
+        <v>66338717.994545102</v>
       </c>
       <c r="D15" s="5">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>59692394.781567022</v>
+        <v>66872358.581491873</v>
       </c>
       <c r="E15" s="5">
         <f>VLOOKUP(A:A,MASTER!A:H,8,0)</f>
-        <v>111711.711711713</v>
+        <v>133333.33333333401</v>
       </c>
       <c r="F15" s="5">
         <f>VLOOKUP(A:A,MASTER!A:I,9,0)</f>
-        <v>10810.810810810999</v>
+        <v>13513.513513514001</v>
       </c>
       <c r="G15" s="5">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>5398198.1981981983</v>
+        <v>5870270.2702702703</v>
       </c>
       <c r="H15" s="5">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>10272072.072072072</v>
+        <v>10545045.045045046</v>
       </c>
       <c r="I15" s="5">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
-        <v>23848630.630630631</v>
+        <v>26884432.432432432</v>
       </c>
       <c r="J15" s="5">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>23302198.198198199</v>
+        <v>27272828.828828827</v>
       </c>
       <c r="K15" s="5">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>4770270.2702702703</v>
+        <v>5072072.072072072</v>
       </c>
       <c r="L15" s="5">
         <f>VLOOKUP(A:A,MASTER!A:C,3,0)</f>
-        <v>8657567.5675675683</v>
+        <v>9064594.594594596</v>
       </c>
     </row>
     <row r="16" spans="1:12" ht="64.5" customHeight="1" x14ac:dyDescent="0.35">
@@ -1139,43 +1138,43 @@
       </c>
       <c r="C16" s="5">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>64742855.47537601</v>
+        <v>73767078.653999969</v>
       </c>
       <c r="D16" s="5">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>73291343.993570343</v>
+        <v>82122878.510911092</v>
       </c>
       <c r="E16" s="5">
         <f>VLOOKUP(A:A,MASTER!A:H,8,0)</f>
-        <v>1016216.216216218</v>
+        <v>1076576.5765765789</v>
       </c>
       <c r="F16" s="5">
         <f>VLOOKUP(A:A,MASTER!A:I,9,0)</f>
-        <v>844144.14414414403</v>
+        <v>1043243.243243242</v>
       </c>
       <c r="G16" s="5">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>8817117.1171171181</v>
+        <v>12693693.693693696</v>
       </c>
       <c r="H16" s="5">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>11301351.351351352</v>
+        <v>15003153.153153153</v>
       </c>
       <c r="I16" s="5">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
-        <v>18698747.747747749</v>
+        <v>21991135.135135137</v>
       </c>
       <c r="J16" s="5">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>21853468.468468469</v>
+        <v>24521081.081081081</v>
       </c>
       <c r="K16" s="5">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>7440900.9009009004</v>
+        <v>10061801.801801801</v>
       </c>
       <c r="L16" s="5">
         <f>VLOOKUP(A:A,MASTER!A:C,3,0)</f>
-        <v>10503153.153153151</v>
+        <v>14082162.162162162</v>
       </c>
     </row>
     <row r="17" spans="1:12" ht="64.5" customHeight="1" x14ac:dyDescent="0.35">
@@ -1187,43 +1186,43 @@
       </c>
       <c r="C17" s="5">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>127540408.71188343</v>
+        <v>145409761.07349011</v>
       </c>
       <c r="D17" s="5">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>131246451.07484853</v>
+        <v>146328695.43384358</v>
       </c>
       <c r="E17" s="5">
         <f>VLOOKUP(A:A,MASTER!A:H,8,0)</f>
-        <v>966666.66666667</v>
+        <v>1290090.0900900951</v>
       </c>
       <c r="F17" s="5">
         <f>VLOOKUP(A:A,MASTER!A:I,9,0)</f>
-        <v>596396.39639639505</v>
+        <v>806306.30630630604</v>
       </c>
       <c r="G17" s="5">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>135054054.05405405</v>
+        <v>156094594.5945946</v>
       </c>
       <c r="H17" s="5">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>176228963.96396396</v>
+        <v>234180990.99099097</v>
       </c>
       <c r="I17" s="5">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
-        <v>46387306.306306303</v>
+        <v>52621846.846846849</v>
       </c>
       <c r="J17" s="5">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>47068990.990990989</v>
+        <v>52213945.945945941</v>
       </c>
       <c r="K17" s="5">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>112215675.67567568</v>
+        <v>138257117.11711711</v>
       </c>
       <c r="L17" s="5">
         <f>VLOOKUP(A:A,MASTER!A:C,3,0)</f>
-        <v>170740315.31531531</v>
+        <v>203271891.8918919</v>
       </c>
     </row>
     <row r="18" spans="1:12" ht="64.5" customHeight="1" x14ac:dyDescent="0.35">
@@ -1235,43 +1234,43 @@
       </c>
       <c r="C18" s="5">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>104774965.49819887</v>
+        <v>119450143.23495574</v>
       </c>
       <c r="D18" s="5">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>107393975.116455</v>
+        <v>120834377.32331549</v>
       </c>
       <c r="E18" s="5">
         <f>VLOOKUP(A:A,MASTER!A:H,8,0)</f>
-        <v>202123931.53153151</v>
+        <v>725225.22522522497</v>
       </c>
       <c r="F18" s="5">
         <f>VLOOKUP(A:A,MASTER!A:I,9,0)</f>
-        <v>186233841.44144145</v>
+        <v>130180.180180182</v>
       </c>
       <c r="G18" s="5">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>31365495.495495494</v>
+        <v>26844054.054054055</v>
       </c>
       <c r="H18" s="5">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>38459909.909909919</v>
+        <v>29228378.378378384</v>
       </c>
       <c r="I18" s="5">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
-        <v>58596306.306306303</v>
+        <v>67946792.792792797</v>
       </c>
       <c r="J18" s="5">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>59852846.846846849</v>
+        <v>67848189.189189181</v>
       </c>
       <c r="K18" s="5">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>24503423.423423424</v>
+        <v>29070360.360360362</v>
       </c>
       <c r="L18" s="5">
         <f>VLOOKUP(A:A,MASTER!A:C,3,0)</f>
-        <v>23350360.360360365</v>
+        <v>27853423.423423424</v>
       </c>
     </row>
     <row r="19" spans="1:12" ht="64.5" customHeight="1" x14ac:dyDescent="0.35">
@@ -1283,43 +1282,43 @@
       </c>
       <c r="C19" s="5">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>53904115.230463743</v>
+        <v>61961269.757889666</v>
       </c>
       <c r="D19" s="5">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>61497440.916110247</v>
+        <v>68884930.57055968</v>
       </c>
       <c r="E19" s="5">
         <f>VLOOKUP(A:A,MASTER!A:H,8,0)</f>
-        <v>657657.65765765903</v>
+        <v>669369.36936937098</v>
       </c>
       <c r="F19" s="5">
         <f>VLOOKUP(A:A,MASTER!A:I,9,0)</f>
-        <v>81981.981981981997</v>
+        <v>101801.80180180199</v>
       </c>
       <c r="G19" s="5">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>22231531.531531531</v>
+        <v>22243243.243243244</v>
       </c>
       <c r="H19" s="5">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>4109009.0090090092</v>
+        <v>6840540.5405405406</v>
       </c>
       <c r="I19" s="5">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
-        <v>18543135.135135137</v>
+        <v>21682549.54954955</v>
       </c>
       <c r="J19" s="5">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>20923711.711711712</v>
+        <v>23622765.765765768</v>
       </c>
       <c r="K19" s="5">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>24953783.783783782</v>
+        <v>25825225.225225225</v>
       </c>
       <c r="L19" s="5">
         <f>VLOOKUP(A:A,MASTER!A:C,3,0)</f>
-        <v>4320090.0900900885</v>
+        <v>4760720.7207207195</v>
       </c>
     </row>
   </sheetData>
@@ -1335,7 +1334,7 @@
   <cols>
     <col min="1" max="1" width="36.90625" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="19.36328125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="20.36328125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="25.81640625" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="17.6328125" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="18.6328125" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="17.1796875" bestFit="1" customWidth="1"/>
@@ -1385,533 +1384,523 @@
       <c r="A3" s="9" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="10">
-        <v>15536576.576576579</v>
-      </c>
-      <c r="C3" s="10">
-        <v>16872207.207207207</v>
-      </c>
-      <c r="D3" s="10">
-        <v>56265009.009009011</v>
-      </c>
-      <c r="E3" s="10">
-        <v>57269711.711711712</v>
-      </c>
-      <c r="F3" s="10">
-        <v>20454324.324324325</v>
-      </c>
-      <c r="G3" s="10">
-        <v>18734459.459459461</v>
-      </c>
-      <c r="H3" s="10">
-        <v>956756.75675675995</v>
-      </c>
-      <c r="I3" s="10">
-        <v>523423.423423425</v>
-      </c>
-      <c r="J3" s="10">
-        <v>116267585.84095243</v>
-      </c>
-      <c r="K3" s="10">
-        <v>126507289.14125644</v>
+      <c r="B3">
+        <v>16552522.522522526</v>
+      </c>
+      <c r="C3">
+        <v>19355630.630630631</v>
+      </c>
+      <c r="D3">
+        <v>64046747.747747742</v>
+      </c>
+      <c r="E3">
+        <v>65476054.054054059</v>
+      </c>
+      <c r="F3">
+        <v>41743063.063063063</v>
+      </c>
+      <c r="G3">
+        <v>57606306.306306303</v>
+      </c>
+      <c r="H3">
+        <v>315073894.5945946</v>
+      </c>
+      <c r="I3">
+        <v>256209569.36936939</v>
+      </c>
+      <c r="J3">
+        <v>132264920.29211617</v>
+      </c>
+      <c r="K3">
+        <v>142994835.09886238</v>
       </c>
     </row>
     <row r="4" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A4" s="9" t="s">
         <v>2</v>
       </c>
-      <c r="B4" s="10">
+      <c r="B4">
         <v>157657.65765765801</v>
       </c>
-      <c r="C4" s="10">
+      <c r="C4">
         <v>118918.91891891899</v>
       </c>
-      <c r="D4" s="10">
-        <v>4061855.8558558561</v>
-      </c>
-      <c r="E4" s="10">
+      <c r="D4">
+        <v>4872702.702702703</v>
+      </c>
+      <c r="E4">
         <v>4088639.6396396402</v>
       </c>
-      <c r="F4" s="10"/>
-      <c r="G4" s="10">
-        <v>90090.090090090001</v>
-      </c>
-      <c r="H4" s="10">
-        <v>229029889.1891892</v>
-      </c>
-      <c r="I4" s="10">
-        <v>99612883.783783779</v>
-      </c>
-      <c r="J4" s="10">
-        <v>7511420.9336513663</v>
-      </c>
-      <c r="K4" s="10">
-        <v>7507509.8967372607</v>
+      <c r="F4">
+        <v>533558.55855855905</v>
+      </c>
+      <c r="G4">
+        <v>158558.558558558</v>
+      </c>
+      <c r="H4">
+        <v>232469742.34234235</v>
+      </c>
+      <c r="I4">
+        <v>148396432.43243244</v>
+      </c>
+      <c r="J4">
+        <v>8660479.7989407126</v>
+      </c>
+      <c r="K4">
+        <v>7510668.6871368838</v>
       </c>
     </row>
     <row r="5" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A5" s="9" t="s">
         <v>3</v>
       </c>
-      <c r="B5" s="10">
-        <v>13959999.999999998</v>
-      </c>
-      <c r="C5" s="10">
-        <v>25294774.774774775</v>
-      </c>
-      <c r="D5" s="10">
-        <v>24560612.612612613</v>
-      </c>
-      <c r="E5" s="10">
-        <v>22512063.063063063</v>
-      </c>
-      <c r="F5" s="10">
-        <v>15818018.018018018</v>
-      </c>
-      <c r="G5" s="10">
-        <v>27872972.97297297</v>
-      </c>
-      <c r="H5" s="10">
-        <v>1017117.117117118</v>
-      </c>
-      <c r="I5" s="10">
-        <v>279279.27927927999</v>
-      </c>
-      <c r="J5" s="10">
-        <v>86248085.706081927</v>
-      </c>
-      <c r="K5" s="10">
-        <v>78619082.392572537</v>
+      <c r="B5">
+        <v>16709189.189189188</v>
+      </c>
+      <c r="C5">
+        <v>31392342.342342339</v>
+      </c>
+      <c r="D5">
+        <v>28004486.486486487</v>
+      </c>
+      <c r="E5">
+        <v>24938810.810810812</v>
+      </c>
+      <c r="F5">
+        <v>17967567.567567568</v>
+      </c>
+      <c r="G5">
+        <v>35318468.468468465</v>
+      </c>
+      <c r="H5">
+        <v>1364864.864864866</v>
+      </c>
+      <c r="I5">
+        <v>517567.56756756699</v>
+      </c>
+      <c r="J5">
+        <v>98339581.103002876</v>
+      </c>
+      <c r="K5">
+        <v>88025424.340662733</v>
       </c>
     </row>
     <row r="6" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A6" s="9" t="s">
         <v>4</v>
       </c>
-      <c r="B6" s="10">
-        <v>17864054.054054052</v>
-      </c>
-      <c r="C6" s="10">
-        <v>7227522.5225225221</v>
-      </c>
-      <c r="D6" s="10">
-        <v>18937099.0990991</v>
-      </c>
-      <c r="E6" s="10">
-        <v>20442684.684684683</v>
-      </c>
-      <c r="F6" s="10">
-        <v>26411261.261261266</v>
-      </c>
-      <c r="G6" s="10">
-        <v>18085135.135135133</v>
-      </c>
-      <c r="H6" s="10">
-        <v>76729729.729729727</v>
-      </c>
-      <c r="I6" s="10">
-        <v>22752252.252252251</v>
-      </c>
-      <c r="J6" s="10">
-        <v>54837497.224373043</v>
-      </c>
-      <c r="K6" s="10">
-        <v>52939180.99643144</v>
+      <c r="B6">
+        <v>18255495.495495494</v>
+      </c>
+      <c r="C6">
+        <v>18200990.990990993</v>
+      </c>
+      <c r="D6">
+        <v>21517324.324324325</v>
+      </c>
+      <c r="E6">
+        <v>23160972.972972974</v>
+      </c>
+      <c r="F6">
+        <v>18331531.531531531</v>
+      </c>
+      <c r="G6">
+        <v>17289189.189189188</v>
+      </c>
+      <c r="H6">
+        <v>581081.08108108304</v>
+      </c>
+      <c r="I6">
+        <v>681081.08108108095</v>
+      </c>
+      <c r="J6">
+        <v>62404702.44519119</v>
+      </c>
+      <c r="K6">
+        <v>59767927.222687922</v>
       </c>
     </row>
     <row r="7" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A7" s="9" t="s">
         <v>5</v>
       </c>
-      <c r="B7" s="10">
-        <v>4770270.2702702703</v>
-      </c>
-      <c r="C7" s="10">
-        <v>8657567.5675675683</v>
-      </c>
-      <c r="D7" s="10">
-        <v>23848630.630630631</v>
-      </c>
-      <c r="E7" s="10">
-        <v>23302198.198198199</v>
-      </c>
-      <c r="F7" s="10">
-        <v>5398198.1981981983</v>
-      </c>
-      <c r="G7" s="10">
-        <v>10272072.072072072</v>
-      </c>
-      <c r="H7" s="10">
-        <v>111711.711711713</v>
-      </c>
-      <c r="I7" s="10">
-        <v>10810.810810810999</v>
-      </c>
-      <c r="J7" s="10">
-        <v>58472443.376442537</v>
-      </c>
-      <c r="K7" s="10">
-        <v>59692394.781567022</v>
+      <c r="B7">
+        <v>5072072.072072072</v>
+      </c>
+      <c r="C7">
+        <v>9064594.594594596</v>
+      </c>
+      <c r="D7">
+        <v>26884432.432432432</v>
+      </c>
+      <c r="E7">
+        <v>27272828.828828827</v>
+      </c>
+      <c r="F7">
+        <v>5870270.2702702703</v>
+      </c>
+      <c r="G7">
+        <v>10545045.045045046</v>
+      </c>
+      <c r="H7">
+        <v>133333.33333333401</v>
+      </c>
+      <c r="I7">
+        <v>13513.513513514001</v>
+      </c>
+      <c r="J7">
+        <v>66338717.994545102</v>
+      </c>
+      <c r="K7">
+        <v>66872358.581491873</v>
       </c>
     </row>
     <row r="8" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A8" s="9" t="s">
         <v>6</v>
       </c>
-      <c r="B8" s="10">
-        <v>59288558.558558561</v>
-      </c>
-      <c r="C8" s="10">
-        <v>136425855.85585585</v>
-      </c>
-      <c r="D8" s="10">
-        <v>131342459.45945945</v>
-      </c>
-      <c r="E8" s="10">
-        <v>130473117.11711712</v>
-      </c>
-      <c r="F8" s="10">
-        <v>68249549.54954955</v>
-      </c>
-      <c r="G8" s="10">
-        <v>154871801.8018018</v>
-      </c>
-      <c r="H8" s="10">
-        <v>2845945.945945947</v>
-      </c>
-      <c r="I8" s="10">
-        <v>3820720.7207207172</v>
-      </c>
-      <c r="J8" s="10">
-        <v>196176570.97486886</v>
-      </c>
-      <c r="K8" s="10">
-        <v>199414498.13007444</v>
+      <c r="B8">
+        <v>105400720.72072072</v>
+      </c>
+      <c r="C8">
+        <v>140731621.62162161</v>
+      </c>
+      <c r="D8">
+        <v>152323765.76576576</v>
+      </c>
+      <c r="E8">
+        <v>150183072.07207206</v>
+      </c>
+      <c r="F8">
+        <v>112500000</v>
+      </c>
+      <c r="G8">
+        <v>155177207.2072072</v>
+      </c>
+      <c r="H8">
+        <v>4406306.3063063063</v>
+      </c>
+      <c r="I8">
+        <v>4004504.5045045</v>
+      </c>
+      <c r="J8">
+        <v>221769958.63266039</v>
+      </c>
+      <c r="K8">
+        <v>229044753.07596684</v>
       </c>
     </row>
     <row r="9" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A9" s="9" t="s">
         <v>7</v>
       </c>
-      <c r="B9" s="10">
-        <v>8593423.4234234225</v>
-      </c>
-      <c r="C9" s="10">
-        <v>9835315.3153153118</v>
-      </c>
-      <c r="D9" s="10">
-        <v>34849666.666666664</v>
-      </c>
-      <c r="E9" s="10">
-        <v>31194990.990990993</v>
-      </c>
-      <c r="F9" s="10">
-        <v>6997297.2972972961</v>
-      </c>
-      <c r="G9" s="10">
-        <v>9277027.027027024</v>
-      </c>
-      <c r="H9" s="10">
-        <v>136936.936936938</v>
-      </c>
-      <c r="I9" s="10">
-        <v>27027.027027027001</v>
-      </c>
-      <c r="J9" s="10">
-        <v>49393746.862353623</v>
-      </c>
-      <c r="K9" s="10">
-        <v>48616953.909952343</v>
+      <c r="B9">
+        <v>8717387.3873873875</v>
+      </c>
+      <c r="C9">
+        <v>20225225.225225225</v>
+      </c>
+      <c r="D9">
+        <v>39424072.072072074</v>
+      </c>
+      <c r="E9">
+        <v>35650486.486486487</v>
+      </c>
+      <c r="F9">
+        <v>7012612.6126126107</v>
+      </c>
+      <c r="G9">
+        <v>19690990.990990993</v>
+      </c>
+      <c r="H9">
+        <v>152252.25225225301</v>
+      </c>
+      <c r="I9">
+        <v>37837.837837838</v>
+      </c>
+      <c r="J9">
+        <v>55784970.612387374</v>
+      </c>
+      <c r="K9">
+        <v>55050728.680071183</v>
       </c>
     </row>
     <row r="10" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A10" s="9" t="s">
         <v>8</v>
       </c>
-      <c r="B10" s="10">
-        <v>7440900.9009009004</v>
-      </c>
-      <c r="C10" s="10">
-        <v>10503153.153153151</v>
-      </c>
-      <c r="D10" s="10">
-        <v>18698747.747747749</v>
-      </c>
-      <c r="E10" s="10">
-        <v>21853468.468468469</v>
-      </c>
-      <c r="F10" s="10">
-        <v>8817117.1171171181</v>
-      </c>
-      <c r="G10" s="10">
-        <v>11301351.351351352</v>
-      </c>
-      <c r="H10" s="10">
-        <v>1016216.216216218</v>
-      </c>
-      <c r="I10" s="10">
-        <v>844144.14414414403</v>
-      </c>
-      <c r="J10" s="10">
-        <v>64742855.47537601</v>
-      </c>
-      <c r="K10" s="10">
-        <v>73291343.993570343</v>
+      <c r="B10">
+        <v>10061801.801801801</v>
+      </c>
+      <c r="C10">
+        <v>14082162.162162162</v>
+      </c>
+      <c r="D10">
+        <v>21991135.135135137</v>
+      </c>
+      <c r="E10">
+        <v>24521081.081081081</v>
+      </c>
+      <c r="F10">
+        <v>12693693.693693696</v>
+      </c>
+      <c r="G10">
+        <v>15003153.153153153</v>
+      </c>
+      <c r="H10">
+        <v>1076576.5765765789</v>
+      </c>
+      <c r="I10">
+        <v>1043243.243243242</v>
+      </c>
+      <c r="J10">
+        <v>73767078.653999969</v>
+      </c>
+      <c r="K10">
+        <v>82122878.510911092</v>
       </c>
     </row>
     <row r="11" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A11" s="9" t="s">
         <v>9</v>
       </c>
-      <c r="B11" s="10">
-        <v>112215675.67567568</v>
-      </c>
-      <c r="C11" s="10">
-        <v>170740315.31531531</v>
-      </c>
-      <c r="D11" s="10">
-        <v>46387306.306306303</v>
-      </c>
-      <c r="E11" s="10">
-        <v>47068990.990990989</v>
-      </c>
-      <c r="F11" s="10">
-        <v>135054054.05405405</v>
-      </c>
-      <c r="G11" s="10">
-        <v>176228963.96396396</v>
-      </c>
-      <c r="H11" s="10">
-        <v>966666.66666667</v>
-      </c>
-      <c r="I11" s="10">
-        <v>596396.39639639505</v>
-      </c>
-      <c r="J11" s="10">
-        <v>127540408.71188343</v>
-      </c>
-      <c r="K11" s="10">
-        <v>131246451.07484853</v>
+      <c r="B11">
+        <v>138257117.11711711</v>
+      </c>
+      <c r="C11">
+        <v>203271891.8918919</v>
+      </c>
+      <c r="D11">
+        <v>52621846.846846849</v>
+      </c>
+      <c r="E11">
+        <v>52213945.945945941</v>
+      </c>
+      <c r="F11">
+        <v>156094594.5945946</v>
+      </c>
+      <c r="G11">
+        <v>234180990.99099097</v>
+      </c>
+      <c r="H11">
+        <v>1290090.0900900951</v>
+      </c>
+      <c r="I11">
+        <v>806306.30630630604</v>
+      </c>
+      <c r="J11">
+        <v>145409761.07349011</v>
+      </c>
+      <c r="K11">
+        <v>146328695.43384358</v>
       </c>
     </row>
     <row r="12" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A12" s="9" t="s">
         <v>10</v>
       </c>
-      <c r="B12" s="10">
+      <c r="B12">
         <v>11081.081081081</v>
       </c>
-      <c r="C12" s="10">
+      <c r="C12">
         <v>250720.72072072001</v>
       </c>
-      <c r="D12" s="10">
-        <v>31396702.702702705</v>
-      </c>
-      <c r="E12" s="10">
-        <v>34195801.801801801</v>
-      </c>
-      <c r="F12" s="10">
-        <v>315540.540540541</v>
-      </c>
-      <c r="G12" s="10">
-        <v>14414.414414413999</v>
-      </c>
-      <c r="H12" s="10">
-        <v>3378378.3783783782</v>
-      </c>
-      <c r="I12" s="10">
-        <v>47477477.477477483</v>
-      </c>
-      <c r="J12" s="10">
-        <v>52030457.127091497</v>
-      </c>
-      <c r="K12" s="10">
-        <v>57426483.631933667</v>
+      <c r="D12">
+        <v>35940792.79279279</v>
+      </c>
+      <c r="E12">
+        <v>39796477.477477483</v>
+      </c>
+      <c r="J12">
+        <v>59447255.050917439</v>
+      </c>
+      <c r="K12">
+        <v>64839617.028884411</v>
       </c>
     </row>
     <row r="13" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A13" s="9" t="s">
         <v>11</v>
       </c>
-      <c r="B13" s="10">
+      <c r="B13">
         <v>1335585.585585586</v>
       </c>
-      <c r="C13" s="10">
-        <v>728108.10810810805</v>
-      </c>
-      <c r="D13" s="10">
-        <v>15800657.657657657</v>
-      </c>
-      <c r="E13" s="10">
-        <v>19452351.351351351</v>
-      </c>
-      <c r="F13" s="10">
+      <c r="C13">
+        <v>849729.72972973005</v>
+      </c>
+      <c r="D13">
+        <v>17627540.540540539</v>
+      </c>
+      <c r="E13">
+        <v>21593117.117117114</v>
+      </c>
+      <c r="F13">
         <v>1819819.8198198189</v>
       </c>
-      <c r="G13" s="10">
-        <v>639639.63963963999</v>
-      </c>
-      <c r="H13" s="10">
+      <c r="G13">
+        <v>648648.64864864899</v>
+      </c>
+      <c r="H13">
         <v>18018.018018018</v>
       </c>
-      <c r="I13" s="10">
-        <v>9009.0090090089998</v>
-      </c>
-      <c r="J13" s="10">
-        <v>45012979.346594982</v>
-      </c>
-      <c r="K13" s="10">
-        <v>45436787.487359814</v>
+      <c r="I13">
+        <v>18018.018018018</v>
+      </c>
+      <c r="J13">
+        <v>51389036.302047253</v>
+      </c>
+      <c r="K13">
+        <v>51054003.623513147</v>
       </c>
     </row>
     <row r="14" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A14" s="9" t="s">
         <v>12</v>
       </c>
-      <c r="B14" s="10">
-        <v>1597837.837837839</v>
-      </c>
-      <c r="C14" s="10">
-        <v>821171.17117117206</v>
-      </c>
-      <c r="D14" s="10">
-        <v>12292441.441441439</v>
-      </c>
-      <c r="E14" s="10">
-        <v>14513405.405405408</v>
-      </c>
-      <c r="F14" s="10">
-        <v>54954.954954954999</v>
-      </c>
-      <c r="G14" s="10">
-        <v>513513.51351351303</v>
-      </c>
-      <c r="H14" s="10">
-        <v>54954.954954954999</v>
-      </c>
-      <c r="I14" s="10">
-        <v>63063.063063062997</v>
-      </c>
-      <c r="J14" s="10">
-        <v>28913433.219965655</v>
-      </c>
-      <c r="K14" s="10">
-        <v>31805391.81232474</v>
+      <c r="B14">
+        <v>4705675.6756756762</v>
+      </c>
+      <c r="C14">
+        <v>1931531.5315315309</v>
+      </c>
+      <c r="D14">
+        <v>13945720.72072072</v>
+      </c>
+      <c r="E14">
+        <v>16015612.612612613</v>
+      </c>
+      <c r="F14">
+        <v>2981981.981981982</v>
+      </c>
+      <c r="G14">
+        <v>551351.35135135101</v>
+      </c>
+      <c r="H14">
+        <v>279279.27927927999</v>
+      </c>
+      <c r="I14">
+        <v>100900.900900901</v>
+      </c>
+      <c r="J14">
+        <v>33166530.840455465</v>
+      </c>
+      <c r="K14">
+        <v>35688394.586691581</v>
       </c>
     </row>
     <row r="15" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A15" s="9" t="s">
         <v>13</v>
       </c>
-      <c r="B15" s="10">
-        <v>24503423.423423424</v>
-      </c>
-      <c r="C15" s="10">
-        <v>23350360.360360365</v>
-      </c>
-      <c r="D15" s="10">
-        <v>58596306.306306303</v>
-      </c>
-      <c r="E15" s="10">
-        <v>59852846.846846849</v>
-      </c>
-      <c r="F15" s="10">
-        <v>31365495.495495494</v>
-      </c>
-      <c r="G15" s="10">
-        <v>38459909.909909919</v>
-      </c>
-      <c r="H15" s="10">
-        <v>202123931.53153151</v>
-      </c>
-      <c r="I15" s="10">
-        <v>186233841.44144145</v>
-      </c>
-      <c r="J15" s="10">
-        <v>104774965.49819887</v>
-      </c>
-      <c r="K15" s="10">
-        <v>107393975.116455</v>
+      <c r="B15">
+        <v>29070360.360360362</v>
+      </c>
+      <c r="C15">
+        <v>27853423.423423424</v>
+      </c>
+      <c r="D15">
+        <v>67946792.792792797</v>
+      </c>
+      <c r="E15">
+        <v>67848189.189189181</v>
+      </c>
+      <c r="F15">
+        <v>26844054.054054055</v>
+      </c>
+      <c r="G15">
+        <v>29228378.378378384</v>
+      </c>
+      <c r="H15">
+        <v>725225.22522522497</v>
+      </c>
+      <c r="I15">
+        <v>130180.180180182</v>
+      </c>
+      <c r="J15">
+        <v>119450143.23495574</v>
+      </c>
+      <c r="K15">
+        <v>120834377.32331549</v>
       </c>
     </row>
     <row r="16" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A16" s="9" t="s">
         <v>14</v>
       </c>
-      <c r="B16" s="10">
-        <v>24953783.783783782</v>
-      </c>
-      <c r="C16" s="10">
-        <v>4320090.0900900885</v>
-      </c>
-      <c r="D16" s="10">
-        <v>18543135.135135137</v>
-      </c>
-      <c r="E16" s="10">
-        <v>20923711.711711712</v>
-      </c>
-      <c r="F16" s="10">
-        <v>22231531.531531531</v>
-      </c>
-      <c r="G16" s="10">
-        <v>4109009.0090090092</v>
-      </c>
-      <c r="H16" s="10">
-        <v>657657.65765765903</v>
-      </c>
-      <c r="I16" s="10">
-        <v>81981.981981981997</v>
-      </c>
-      <c r="J16" s="10">
-        <v>53904115.230463743</v>
-      </c>
-      <c r="K16" s="10">
-        <v>61497440.916110247</v>
+      <c r="B16">
+        <v>25825225.225225225</v>
+      </c>
+      <c r="C16">
+        <v>4760720.7207207195</v>
+      </c>
+      <c r="D16">
+        <v>21682549.54954955</v>
+      </c>
+      <c r="E16">
+        <v>23622765.765765768</v>
+      </c>
+      <c r="F16">
+        <v>22243243.243243244</v>
+      </c>
+      <c r="G16">
+        <v>6840540.5405405406</v>
+      </c>
+      <c r="H16">
+        <v>669369.36936937098</v>
+      </c>
+      <c r="I16">
+        <v>101801.80180180199</v>
+      </c>
+      <c r="J16">
+        <v>61961269.757889666</v>
+      </c>
+      <c r="K16">
+        <v>68884930.57055968</v>
       </c>
     </row>
     <row r="17" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A17" s="11" t="s">
+      <c r="A17" s="10" t="s">
         <v>34</v>
       </c>
-      <c r="B17" s="12">
+      <c r="B17" s="11">
         <f>SUM(B3:B16)</f>
-        <v>292228828.82882887</v>
-      </c>
-      <c r="C17" s="12">
+        <v>380131891.89189196</v>
+      </c>
+      <c r="C17" s="11">
         <f t="shared" ref="C17:K17" si="0">SUM(C3:C16)</f>
-        <v>415146081.08108109</v>
-      </c>
-      <c r="D17" s="12">
+        <v>492089504.50450444</v>
+      </c>
+      <c r="D17" s="11">
         <f t="shared" si="0"/>
-        <v>495580630.63063067</v>
-      </c>
-      <c r="E17" s="12">
+        <v>568829909.90990984</v>
+      </c>
+      <c r="E17" s="11">
         <f t="shared" si="0"/>
-        <v>507143981.98198193</v>
-      </c>
-      <c r="F17" s="12">
+        <v>576382054.05405402</v>
+      </c>
+      <c r="F17" s="11">
         <f t="shared" si="0"/>
-        <v>342987162.16216213</v>
-      </c>
-      <c r="G17" s="12">
+        <v>426635990.990991</v>
+      </c>
+      <c r="G17" s="11">
         <f t="shared" si="0"/>
-        <v>470470360.36036026</v>
-      </c>
-      <c r="H17" s="12">
+        <v>582238828.82882893</v>
+      </c>
+      <c r="H17" s="11">
         <f t="shared" si="0"/>
-        <v>519043910.8108108</v>
-      </c>
-      <c r="I17" s="12">
+        <v>558240033.33333325</v>
+      </c>
+      <c r="I17" s="11">
         <f t="shared" si="0"/>
-        <v>362332310.8108108</v>
-      </c>
-      <c r="J17" s="12">
+        <v>412060956.75675672</v>
+      </c>
+      <c r="J17" s="11">
         <f t="shared" si="0"/>
-        <v>1045826565.528298</v>
-      </c>
-      <c r="K17" s="12">
+        <v>1190154405.7925994</v>
+      </c>
+      <c r="K17" s="11">
         <f t="shared" si="0"/>
-        <v>1081394783.2811937</v>
+        <v>1219019592.7645988</v>
       </c>
     </row>
   </sheetData>

--- a/MS BENGKAYANG 19 JULI 2026.xlsx
+++ b/MS BENGKAYANG 19 JULI 2026.xlsx
@@ -658,31 +658,31 @@
       </c>
       <c r="C6" s="5">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>8660479.7989407126</v>
+        <v>9987199.9195197597</v>
       </c>
       <c r="D6" s="5">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>7510668.6871368838</v>
+        <v>7512189.1632019328</v>
       </c>
       <c r="E6" s="5">
         <f>VLOOKUP(A:A,MASTER!A:H,8,0)</f>
-        <v>232469742.34234235</v>
+        <v>3378378.3783783782</v>
       </c>
       <c r="F6" s="5">
         <f>VLOOKUP(A:A,MASTER!A:I,9,0)</f>
-        <v>148396432.43243244</v>
+        <v>51171171.171171166</v>
       </c>
       <c r="G6" s="5">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>533558.55855855905</v>
+        <v>647522.52252252295</v>
       </c>
       <c r="H6" s="5">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>158558.558558558</v>
+        <v>248648.648648648</v>
       </c>
       <c r="I6" s="5">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
-        <v>4872702.702702703</v>
+        <v>5641351.3513513505</v>
       </c>
       <c r="J6" s="5">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
@@ -694,7 +694,7 @@
       </c>
       <c r="L6" s="5">
         <f>VLOOKUP(A:A,MASTER!A:C,3,0)</f>
-        <v>118918.91891891899</v>
+        <v>203603.60360360399</v>
       </c>
     </row>
     <row r="7" spans="1:12" ht="64.5" customHeight="1" x14ac:dyDescent="0.35">
@@ -706,43 +706,43 @@
       </c>
       <c r="C7" s="5">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>221769958.63266039</v>
+        <v>250965168.44339868</v>
       </c>
       <c r="D7" s="5">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>229044753.07596684</v>
+        <v>257398940.21128601</v>
       </c>
       <c r="E7" s="5">
         <f>VLOOKUP(A:A,MASTER!A:H,8,0)</f>
-        <v>4406306.3063063063</v>
+        <v>235798781.98198199</v>
       </c>
       <c r="F7" s="5">
         <f>VLOOKUP(A:A,MASTER!A:I,9,0)</f>
-        <v>4004504.5045045</v>
+        <v>151377498.1981982</v>
       </c>
       <c r="G7" s="5">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>112500000</v>
+        <v>112554954.95495497</v>
       </c>
       <c r="H7" s="5">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>155177207.2072072</v>
+        <v>170276306.3063063</v>
       </c>
       <c r="I7" s="5">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
-        <v>152323765.76576576</v>
+        <v>174425135.13513514</v>
       </c>
       <c r="J7" s="5">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>150183072.07207206</v>
+        <v>167789855.85585588</v>
       </c>
       <c r="K7" s="5">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>105400720.72072072</v>
+        <v>107143243.24324325</v>
       </c>
       <c r="L7" s="5">
         <f>VLOOKUP(A:A,MASTER!A:C,3,0)</f>
-        <v>140731621.62162161</v>
+        <v>153548468.46846846</v>
       </c>
     </row>
     <row r="8" spans="1:12" ht="64.5" customHeight="1" x14ac:dyDescent="0.35">
@@ -754,11 +754,11 @@
       </c>
       <c r="C8" s="5">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>55784970.612387374</v>
+        <v>62714447.095244333</v>
       </c>
       <c r="D8" s="5">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>55050728.680071183</v>
+        <v>61120914.303842261</v>
       </c>
       <c r="E8" s="5">
         <f>VLOOKUP(A:A,MASTER!A:H,8,0)</f>
@@ -778,19 +778,19 @@
       </c>
       <c r="I8" s="5">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
-        <v>39424072.072072074</v>
+        <v>44273927.927927926</v>
       </c>
       <c r="J8" s="5">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>35650486.486486487</v>
+        <v>40218369.369369365</v>
       </c>
       <c r="K8" s="5">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>8717387.3873873875</v>
+        <v>8814774.774774773</v>
       </c>
       <c r="L8" s="5">
         <f>VLOOKUP(A:A,MASTER!A:C,3,0)</f>
-        <v>20225225.225225225</v>
+        <v>20500810.810810808</v>
       </c>
     </row>
     <row r="9" spans="1:12" ht="64.5" customHeight="1" x14ac:dyDescent="0.35">
@@ -802,11 +802,11 @@
       </c>
       <c r="C9" s="5">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>59447255.050917439</v>
+        <v>67720075.572822079</v>
       </c>
       <c r="D9" s="5">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>64839617.028884411</v>
+        <v>72300740.44801721</v>
       </c>
       <c r="E9" s="5">
         <f>VLOOKUP(A:A,MASTER!A:H,8,0)</f>
@@ -826,11 +826,11 @@
       </c>
       <c r="I9" s="5">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
-        <v>35940792.79279279</v>
+        <v>40885747.747747742</v>
       </c>
       <c r="J9" s="5">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>39796477.477477483</v>
+        <v>44202873.873873875</v>
       </c>
       <c r="K9" s="5">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
@@ -850,11 +850,11 @@
       </c>
       <c r="C10" s="5">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>51389036.302047253</v>
+        <v>58717243.269229785</v>
       </c>
       <c r="D10" s="5">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>51054003.623513147</v>
+        <v>57049699.601031773</v>
       </c>
       <c r="E10" s="5">
         <f>VLOOKUP(A:A,MASTER!A:H,8,0)</f>
@@ -870,23 +870,23 @@
       </c>
       <c r="H10" s="5">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>648648.64864864899</v>
+        <v>2450450.4504504511</v>
       </c>
       <c r="I10" s="5">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
-        <v>17627540.540540539</v>
+        <v>20201414.414414417</v>
       </c>
       <c r="J10" s="5">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>21593117.117117114</v>
+        <v>23949729.729729727</v>
       </c>
       <c r="K10" s="5">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>1335585.585585586</v>
+        <v>1365315.315315316</v>
       </c>
       <c r="L10" s="5">
         <f>VLOOKUP(A:A,MASTER!A:C,3,0)</f>
-        <v>849729.72972973005</v>
+        <v>909189.189189189</v>
       </c>
     </row>
     <row r="11" spans="1:12" ht="64.5" customHeight="1" x14ac:dyDescent="0.35">
@@ -898,15 +898,15 @@
       </c>
       <c r="C11" s="5">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>33166530.840455465</v>
+        <v>38037294.012150496</v>
       </c>
       <c r="D11" s="5">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>35688394.586691581</v>
+        <v>39399917.081062913</v>
       </c>
       <c r="E11" s="5">
         <f>VLOOKUP(A:A,MASTER!A:H,8,0)</f>
-        <v>279279.27927927999</v>
+        <v>289189.18918918999</v>
       </c>
       <c r="F11" s="5">
         <f>VLOOKUP(A:A,MASTER!A:I,9,0)</f>
@@ -914,7 +914,7 @@
       </c>
       <c r="G11" s="5">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>2981981.981981982</v>
+        <v>3442342.3423423418</v>
       </c>
       <c r="H11" s="5">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
@@ -922,19 +922,19 @@
       </c>
       <c r="I11" s="5">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
-        <v>13945720.72072072</v>
+        <v>15974360.36036036</v>
       </c>
       <c r="J11" s="5">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>16015612.612612613</v>
+        <v>17574081.081081081</v>
       </c>
       <c r="K11" s="5">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>4705675.6756756762</v>
+        <v>4922792.7927927934</v>
       </c>
       <c r="L11" s="5">
         <f>VLOOKUP(A:A,MASTER!A:C,3,0)</f>
-        <v>1931531.5315315309</v>
+        <v>1938738.738738738</v>
       </c>
     </row>
     <row r="12" spans="1:12" ht="64.5" customHeight="1" x14ac:dyDescent="0.35">
@@ -946,43 +946,43 @@
       </c>
       <c r="C12" s="5">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>132264920.29211617</v>
+        <v>150167027.1591804</v>
       </c>
       <c r="D12" s="5">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>142994835.09886238</v>
+        <v>158833895.18746045</v>
       </c>
       <c r="E12" s="5">
         <f>VLOOKUP(A:A,MASTER!A:H,8,0)</f>
-        <v>315073894.5945946</v>
+        <v>1062162.1621621649</v>
       </c>
       <c r="F12" s="5">
         <f>VLOOKUP(A:A,MASTER!A:I,9,0)</f>
-        <v>256209569.36936939</v>
+        <v>803603.60360360495</v>
       </c>
       <c r="G12" s="5">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>41743063.063063063</v>
+        <v>21616486.486486487</v>
       </c>
       <c r="H12" s="5">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>57606306.306306303</v>
+        <v>22493918.918918919</v>
       </c>
       <c r="I12" s="5">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
-        <v>64046747.747747742</v>
+        <v>73013324.324324325</v>
       </c>
       <c r="J12" s="5">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>65476054.054054059</v>
+        <v>73107450.45045045</v>
       </c>
       <c r="K12" s="5">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>16552522.522522526</v>
+        <v>18313333.333333332</v>
       </c>
       <c r="L12" s="5">
         <f>VLOOKUP(A:A,MASTER!A:C,3,0)</f>
-        <v>19355630.630630631</v>
+        <v>21375450.450450446</v>
       </c>
     </row>
     <row r="13" spans="1:12" ht="64.5" customHeight="1" x14ac:dyDescent="0.35">
@@ -994,43 +994,43 @@
       </c>
       <c r="C13" s="5">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>98339581.103002876</v>
+        <v>112187053.30400717</v>
       </c>
       <c r="D13" s="5">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>88025424.340662733</v>
+        <v>99340915.538647428</v>
       </c>
       <c r="E13" s="5">
         <f>VLOOKUP(A:A,MASTER!A:H,8,0)</f>
-        <v>1364864.864864866</v>
+        <v>319496879.27927929</v>
       </c>
       <c r="F13" s="5">
         <f>VLOOKUP(A:A,MASTER!A:I,9,0)</f>
-        <v>517567.56756756699</v>
+        <v>306618054.05405408</v>
       </c>
       <c r="G13" s="5">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>17967567.567567568</v>
+        <v>40307207.20720721</v>
       </c>
       <c r="H13" s="5">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>35318468.468468465</v>
+        <v>93015315.315315306</v>
       </c>
       <c r="I13" s="5">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
-        <v>28004486.486486487</v>
+        <v>31708351.351351351</v>
       </c>
       <c r="J13" s="5">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>24938810.810810812</v>
+        <v>28277099.0990991</v>
       </c>
       <c r="K13" s="5">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>16709189.189189188</v>
+        <v>17722882.882882882</v>
       </c>
       <c r="L13" s="5">
         <f>VLOOKUP(A:A,MASTER!A:C,3,0)</f>
-        <v>31392342.342342339</v>
+        <v>50179819.819819823</v>
       </c>
     </row>
     <row r="14" spans="1:12" ht="64.5" customHeight="1" x14ac:dyDescent="0.35">
@@ -1042,43 +1042,43 @@
       </c>
       <c r="C14" s="5">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>62404702.44519119</v>
+        <v>70187104.712153107</v>
       </c>
       <c r="D14" s="5">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>59767927.222687922</v>
+        <v>66272045.910958104</v>
       </c>
       <c r="E14" s="5">
         <f>VLOOKUP(A:A,MASTER!A:H,8,0)</f>
-        <v>581081.08108108304</v>
+        <v>851351.35135135299</v>
       </c>
       <c r="F14" s="5">
         <f>VLOOKUP(A:A,MASTER!A:I,9,0)</f>
-        <v>681081.08108108095</v>
+        <v>690090.09009008994</v>
       </c>
       <c r="G14" s="5">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>18331531.531531531</v>
+        <v>18601801.801801804</v>
       </c>
       <c r="H14" s="5">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>17289189.189189188</v>
+        <v>27226126.126126129</v>
       </c>
       <c r="I14" s="5">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
-        <v>21517324.324324325</v>
+        <v>24060162.162162159</v>
       </c>
       <c r="J14" s="5">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>23160972.972972974</v>
+        <v>25455198.198198196</v>
       </c>
       <c r="K14" s="5">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>18255495.495495494</v>
+        <v>19848018.018018015</v>
       </c>
       <c r="L14" s="5">
         <f>VLOOKUP(A:A,MASTER!A:C,3,0)</f>
-        <v>18200990.990990993</v>
+        <v>18954774.774774775</v>
       </c>
     </row>
     <row r="15" spans="1:12" ht="64.5" customHeight="1" x14ac:dyDescent="0.35">
@@ -1090,15 +1090,15 @@
       </c>
       <c r="C15" s="5">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>66338717.994545102</v>
+        <v>75348708.800628439</v>
       </c>
       <c r="D15" s="5">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>66872358.581491873</v>
+        <v>74886227.59351182</v>
       </c>
       <c r="E15" s="5">
         <f>VLOOKUP(A:A,MASTER!A:H,8,0)</f>
-        <v>133333.33333333401</v>
+        <v>147747.74774774801</v>
       </c>
       <c r="F15" s="5">
         <f>VLOOKUP(A:A,MASTER!A:I,9,0)</f>
@@ -1106,27 +1106,27 @@
       </c>
       <c r="G15" s="5">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>5870270.2702702703</v>
+        <v>5893693.6936936928</v>
       </c>
       <c r="H15" s="5">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>10545045.045045046</v>
+        <v>10725225.225225225</v>
       </c>
       <c r="I15" s="5">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
-        <v>26884432.432432432</v>
+        <v>30558927.927927926</v>
       </c>
       <c r="J15" s="5">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>27272828.828828827</v>
+        <v>30988135.135135137</v>
       </c>
       <c r="K15" s="5">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>5072072.072072072</v>
+        <v>5518378.3783783782</v>
       </c>
       <c r="L15" s="5">
         <f>VLOOKUP(A:A,MASTER!A:C,3,0)</f>
-        <v>9064594.594594596</v>
+        <v>9525675.6756756753</v>
       </c>
     </row>
     <row r="16" spans="1:12" ht="64.5" customHeight="1" x14ac:dyDescent="0.35">
@@ -1138,43 +1138,43 @@
       </c>
       <c r="C16" s="5">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>73767078.653999969</v>
+        <v>83854093.49572067</v>
       </c>
       <c r="D16" s="5">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>82122878.510911092</v>
+        <v>90960999.439689696</v>
       </c>
       <c r="E16" s="5">
         <f>VLOOKUP(A:A,MASTER!A:H,8,0)</f>
-        <v>1076576.5765765789</v>
+        <v>1211711.711711714</v>
       </c>
       <c r="F16" s="5">
         <f>VLOOKUP(A:A,MASTER!A:I,9,0)</f>
-        <v>1043243.243243242</v>
+        <v>1065765.765765765</v>
       </c>
       <c r="G16" s="5">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>12693693.693693696</v>
+        <v>12828828.82882883</v>
       </c>
       <c r="H16" s="5">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>15003153.153153153</v>
+        <v>15034684.684684686</v>
       </c>
       <c r="I16" s="5">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
-        <v>21991135.135135137</v>
+        <v>24929153.153153151</v>
       </c>
       <c r="J16" s="5">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>24521081.081081081</v>
+        <v>27055720.72072072</v>
       </c>
       <c r="K16" s="5">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>10061801.801801801</v>
+        <v>11406396.396396397</v>
       </c>
       <c r="L16" s="5">
         <f>VLOOKUP(A:A,MASTER!A:C,3,0)</f>
-        <v>14082162.162162162</v>
+        <v>14261441.441441443</v>
       </c>
     </row>
     <row r="17" spans="1:12" ht="64.5" customHeight="1" x14ac:dyDescent="0.35">
@@ -1186,43 +1186,43 @@
       </c>
       <c r="C17" s="5">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>145409761.07349011</v>
+        <v>165977897.33642882</v>
       </c>
       <c r="D17" s="5">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>146328695.43384358</v>
+        <v>162771216.34899825</v>
       </c>
       <c r="E17" s="5">
         <f>VLOOKUP(A:A,MASTER!A:H,8,0)</f>
-        <v>1290090.0900900951</v>
+        <v>1371171.171171176</v>
       </c>
       <c r="F17" s="5">
         <f>VLOOKUP(A:A,MASTER!A:I,9,0)</f>
-        <v>806306.30630630604</v>
+        <v>851801.80180180096</v>
       </c>
       <c r="G17" s="5">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>156094594.5945946</v>
+        <v>183202702.7027027</v>
       </c>
       <c r="H17" s="5">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>234180990.99099097</v>
+        <v>261253513.51351351</v>
       </c>
       <c r="I17" s="5">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
-        <v>52621846.846846849</v>
+        <v>61103225.225225225</v>
       </c>
       <c r="J17" s="5">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>52213945.945945941</v>
+        <v>57755018.018018015</v>
       </c>
       <c r="K17" s="5">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>138257117.11711711</v>
+        <v>156418018.01801801</v>
       </c>
       <c r="L17" s="5">
         <f>VLOOKUP(A:A,MASTER!A:C,3,0)</f>
-        <v>203271891.8918919</v>
+        <v>222087837.83783782</v>
       </c>
     </row>
     <row r="18" spans="1:12" ht="64.5" customHeight="1" x14ac:dyDescent="0.35">
@@ -1234,43 +1234,43 @@
       </c>
       <c r="C18" s="5">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>119450143.23495574</v>
+        <v>135883629.59817576</v>
       </c>
       <c r="D18" s="5">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>120834377.32331549</v>
+        <v>132967322.54034512</v>
       </c>
       <c r="E18" s="5">
         <f>VLOOKUP(A:A,MASTER!A:H,8,0)</f>
-        <v>725225.22522522497</v>
+        <v>823423.42342342495</v>
       </c>
       <c r="F18" s="5">
         <f>VLOOKUP(A:A,MASTER!A:I,9,0)</f>
-        <v>130180.180180182</v>
+        <v>162612.612612614</v>
       </c>
       <c r="G18" s="5">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>26844054.054054055</v>
+        <v>27392702.702702705</v>
       </c>
       <c r="H18" s="5">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>29228378.378378384</v>
+        <v>31242792.792792797</v>
       </c>
       <c r="I18" s="5">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
-        <v>67946792.792792797</v>
+        <v>79070351.351351365</v>
       </c>
       <c r="J18" s="5">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>67848189.189189181</v>
+        <v>74886153.153153151</v>
       </c>
       <c r="K18" s="5">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>29070360.360360362</v>
+        <v>31047567.567567568</v>
       </c>
       <c r="L18" s="5">
         <f>VLOOKUP(A:A,MASTER!A:C,3,0)</f>
-        <v>27853423.423423424</v>
+        <v>31092882.882882889</v>
       </c>
     </row>
     <row r="19" spans="1:12" ht="64.5" customHeight="1" x14ac:dyDescent="0.35">
@@ -1282,11 +1282,11 @@
       </c>
       <c r="C19" s="5">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>61961269.757889666</v>
+        <v>71109559.115343332</v>
       </c>
       <c r="D19" s="5">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>68884930.57055968</v>
+        <v>77209357.783545718</v>
       </c>
       <c r="E19" s="5">
         <f>VLOOKUP(A:A,MASTER!A:H,8,0)</f>
@@ -1294,7 +1294,7 @@
       </c>
       <c r="F19" s="5">
         <f>VLOOKUP(A:A,MASTER!A:I,9,0)</f>
-        <v>101801.80180180199</v>
+        <v>110810.810810811</v>
       </c>
       <c r="G19" s="5">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
@@ -1302,23 +1302,23 @@
       </c>
       <c r="H19" s="5">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>6840540.5405405406</v>
+        <v>16703153.153153151</v>
       </c>
       <c r="I19" s="5">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
-        <v>21682549.54954955</v>
+        <v>24665792.792792793</v>
       </c>
       <c r="J19" s="5">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>23622765.765765768</v>
+        <v>26786909.909909911</v>
       </c>
       <c r="K19" s="5">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>25825225.225225225</v>
+        <v>26924864.864864863</v>
       </c>
       <c r="L19" s="5">
         <f>VLOOKUP(A:A,MASTER!A:C,3,0)</f>
-        <v>4760720.7207207195</v>
+        <v>14761261.26126126</v>
       </c>
     </row>
   </sheetData>
@@ -1385,34 +1385,34 @@
         <v>1</v>
       </c>
       <c r="B3">
-        <v>16552522.522522526</v>
+        <v>18313333.333333332</v>
       </c>
       <c r="C3">
-        <v>19355630.630630631</v>
+        <v>21375450.450450446</v>
       </c>
       <c r="D3">
-        <v>64046747.747747742</v>
+        <v>73013324.324324325</v>
       </c>
       <c r="E3">
-        <v>65476054.054054059</v>
+        <v>73107450.45045045</v>
       </c>
       <c r="F3">
-        <v>41743063.063063063</v>
+        <v>21616486.486486487</v>
       </c>
       <c r="G3">
-        <v>57606306.306306303</v>
+        <v>22493918.918918919</v>
       </c>
       <c r="H3">
-        <v>315073894.5945946</v>
+        <v>1062162.1621621649</v>
       </c>
       <c r="I3">
-        <v>256209569.36936939</v>
+        <v>803603.60360360495</v>
       </c>
       <c r="J3">
-        <v>132264920.29211617</v>
+        <v>150167027.1591804</v>
       </c>
       <c r="K3">
-        <v>142994835.09886238</v>
+        <v>158833895.18746045</v>
       </c>
     </row>
     <row r="4" spans="1:11" x14ac:dyDescent="0.35">
@@ -1423,31 +1423,31 @@
         <v>157657.65765765801</v>
       </c>
       <c r="C4">
-        <v>118918.91891891899</v>
+        <v>203603.60360360399</v>
       </c>
       <c r="D4">
-        <v>4872702.702702703</v>
+        <v>5641351.3513513505</v>
       </c>
       <c r="E4">
         <v>4088639.6396396402</v>
       </c>
       <c r="F4">
-        <v>533558.55855855905</v>
+        <v>647522.52252252295</v>
       </c>
       <c r="G4">
-        <v>158558.558558558</v>
+        <v>248648.648648648</v>
       </c>
       <c r="H4">
-        <v>232469742.34234235</v>
+        <v>3378378.3783783782</v>
       </c>
       <c r="I4">
-        <v>148396432.43243244</v>
+        <v>51171171.171171166</v>
       </c>
       <c r="J4">
-        <v>8660479.7989407126</v>
+        <v>9987199.9195197597</v>
       </c>
       <c r="K4">
-        <v>7510668.6871368838</v>
+        <v>7512189.1632019328</v>
       </c>
     </row>
     <row r="5" spans="1:11" x14ac:dyDescent="0.35">
@@ -1455,34 +1455,34 @@
         <v>3</v>
       </c>
       <c r="B5">
-        <v>16709189.189189188</v>
+        <v>17722882.882882882</v>
       </c>
       <c r="C5">
-        <v>31392342.342342339</v>
+        <v>50179819.819819823</v>
       </c>
       <c r="D5">
-        <v>28004486.486486487</v>
+        <v>31708351.351351351</v>
       </c>
       <c r="E5">
-        <v>24938810.810810812</v>
+        <v>28277099.0990991</v>
       </c>
       <c r="F5">
-        <v>17967567.567567568</v>
+        <v>40307207.20720721</v>
       </c>
       <c r="G5">
-        <v>35318468.468468465</v>
+        <v>93015315.315315306</v>
       </c>
       <c r="H5">
-        <v>1364864.864864866</v>
+        <v>319496879.27927929</v>
       </c>
       <c r="I5">
-        <v>517567.56756756699</v>
+        <v>306618054.05405408</v>
       </c>
       <c r="J5">
-        <v>98339581.103002876</v>
+        <v>112187053.30400717</v>
       </c>
       <c r="K5">
-        <v>88025424.340662733</v>
+        <v>99340915.538647428</v>
       </c>
     </row>
     <row r="6" spans="1:11" x14ac:dyDescent="0.35">
@@ -1490,34 +1490,34 @@
         <v>4</v>
       </c>
       <c r="B6">
-        <v>18255495.495495494</v>
+        <v>19848018.018018015</v>
       </c>
       <c r="C6">
-        <v>18200990.990990993</v>
+        <v>18954774.774774775</v>
       </c>
       <c r="D6">
-        <v>21517324.324324325</v>
+        <v>24060162.162162159</v>
       </c>
       <c r="E6">
-        <v>23160972.972972974</v>
+        <v>25455198.198198196</v>
       </c>
       <c r="F6">
-        <v>18331531.531531531</v>
+        <v>18601801.801801804</v>
       </c>
       <c r="G6">
-        <v>17289189.189189188</v>
+        <v>27226126.126126129</v>
       </c>
       <c r="H6">
-        <v>581081.08108108304</v>
+        <v>851351.35135135299</v>
       </c>
       <c r="I6">
-        <v>681081.08108108095</v>
+        <v>690090.09009008994</v>
       </c>
       <c r="J6">
-        <v>62404702.44519119</v>
+        <v>70187104.712153107</v>
       </c>
       <c r="K6">
-        <v>59767927.222687922</v>
+        <v>66272045.910958104</v>
       </c>
     </row>
     <row r="7" spans="1:11" x14ac:dyDescent="0.35">
@@ -1525,34 +1525,34 @@
         <v>5</v>
       </c>
       <c r="B7">
-        <v>5072072.072072072</v>
+        <v>5518378.3783783782</v>
       </c>
       <c r="C7">
-        <v>9064594.594594596</v>
+        <v>9525675.6756756753</v>
       </c>
       <c r="D7">
-        <v>26884432.432432432</v>
+        <v>30558927.927927926</v>
       </c>
       <c r="E7">
-        <v>27272828.828828827</v>
+        <v>30988135.135135137</v>
       </c>
       <c r="F7">
-        <v>5870270.2702702703</v>
+        <v>5893693.6936936928</v>
       </c>
       <c r="G7">
-        <v>10545045.045045046</v>
+        <v>10725225.225225225</v>
       </c>
       <c r="H7">
-        <v>133333.33333333401</v>
+        <v>147747.74774774801</v>
       </c>
       <c r="I7">
         <v>13513.513513514001</v>
       </c>
       <c r="J7">
-        <v>66338717.994545102</v>
+        <v>75348708.800628439</v>
       </c>
       <c r="K7">
-        <v>66872358.581491873</v>
+        <v>74886227.59351182</v>
       </c>
     </row>
     <row r="8" spans="1:11" x14ac:dyDescent="0.35">
@@ -1560,34 +1560,34 @@
         <v>6</v>
       </c>
       <c r="B8">
-        <v>105400720.72072072</v>
+        <v>107143243.24324325</v>
       </c>
       <c r="C8">
-        <v>140731621.62162161</v>
+        <v>153548468.46846846</v>
       </c>
       <c r="D8">
-        <v>152323765.76576576</v>
+        <v>174425135.13513514</v>
       </c>
       <c r="E8">
-        <v>150183072.07207206</v>
+        <v>167789855.85585588</v>
       </c>
       <c r="F8">
-        <v>112500000</v>
+        <v>112554954.95495497</v>
       </c>
       <c r="G8">
-        <v>155177207.2072072</v>
+        <v>170276306.3063063</v>
       </c>
       <c r="H8">
-        <v>4406306.3063063063</v>
+        <v>235798781.98198199</v>
       </c>
       <c r="I8">
-        <v>4004504.5045045</v>
+        <v>151377498.1981982</v>
       </c>
       <c r="J8">
-        <v>221769958.63266039</v>
+        <v>250965168.44339868</v>
       </c>
       <c r="K8">
-        <v>229044753.07596684</v>
+        <v>257398940.21128601</v>
       </c>
     </row>
     <row r="9" spans="1:11" x14ac:dyDescent="0.35">
@@ -1595,16 +1595,16 @@
         <v>7</v>
       </c>
       <c r="B9">
-        <v>8717387.3873873875</v>
+        <v>8814774.774774773</v>
       </c>
       <c r="C9">
-        <v>20225225.225225225</v>
+        <v>20500810.810810808</v>
       </c>
       <c r="D9">
-        <v>39424072.072072074</v>
+        <v>44273927.927927926</v>
       </c>
       <c r="E9">
-        <v>35650486.486486487</v>
+        <v>40218369.369369365</v>
       </c>
       <c r="F9">
         <v>7012612.6126126107</v>
@@ -1619,10 +1619,10 @@
         <v>37837.837837838</v>
       </c>
       <c r="J9">
-        <v>55784970.612387374</v>
+        <v>62714447.095244333</v>
       </c>
       <c r="K9">
-        <v>55050728.680071183</v>
+        <v>61120914.303842261</v>
       </c>
     </row>
     <row r="10" spans="1:11" x14ac:dyDescent="0.35">
@@ -1630,34 +1630,34 @@
         <v>8</v>
       </c>
       <c r="B10">
-        <v>10061801.801801801</v>
+        <v>11406396.396396397</v>
       </c>
       <c r="C10">
-        <v>14082162.162162162</v>
+        <v>14261441.441441443</v>
       </c>
       <c r="D10">
-        <v>21991135.135135137</v>
+        <v>24929153.153153151</v>
       </c>
       <c r="E10">
-        <v>24521081.081081081</v>
+        <v>27055720.72072072</v>
       </c>
       <c r="F10">
-        <v>12693693.693693696</v>
+        <v>12828828.82882883</v>
       </c>
       <c r="G10">
-        <v>15003153.153153153</v>
+        <v>15034684.684684686</v>
       </c>
       <c r="H10">
-        <v>1076576.5765765789</v>
+        <v>1211711.711711714</v>
       </c>
       <c r="I10">
-        <v>1043243.243243242</v>
+        <v>1065765.765765765</v>
       </c>
       <c r="J10">
-        <v>73767078.653999969</v>
+        <v>83854093.49572067</v>
       </c>
       <c r="K10">
-        <v>82122878.510911092</v>
+        <v>90960999.439689696</v>
       </c>
     </row>
     <row r="11" spans="1:11" x14ac:dyDescent="0.35">
@@ -1665,34 +1665,34 @@
         <v>9</v>
       </c>
       <c r="B11">
-        <v>138257117.11711711</v>
+        <v>156418018.01801801</v>
       </c>
       <c r="C11">
-        <v>203271891.8918919</v>
+        <v>222087837.83783782</v>
       </c>
       <c r="D11">
-        <v>52621846.846846849</v>
+        <v>61103225.225225225</v>
       </c>
       <c r="E11">
-        <v>52213945.945945941</v>
+        <v>57755018.018018015</v>
       </c>
       <c r="F11">
-        <v>156094594.5945946</v>
+        <v>183202702.7027027</v>
       </c>
       <c r="G11">
-        <v>234180990.99099097</v>
+        <v>261253513.51351351</v>
       </c>
       <c r="H11">
-        <v>1290090.0900900951</v>
+        <v>1371171.171171176</v>
       </c>
       <c r="I11">
-        <v>806306.30630630604</v>
+        <v>851801.80180180096</v>
       </c>
       <c r="J11">
-        <v>145409761.07349011</v>
+        <v>165977897.33642882</v>
       </c>
       <c r="K11">
-        <v>146328695.43384358</v>
+        <v>162771216.34899825</v>
       </c>
     </row>
     <row r="12" spans="1:11" x14ac:dyDescent="0.35">
@@ -1706,16 +1706,16 @@
         <v>250720.72072072001</v>
       </c>
       <c r="D12">
-        <v>35940792.79279279</v>
+        <v>40885747.747747742</v>
       </c>
       <c r="E12">
-        <v>39796477.477477483</v>
+        <v>44202873.873873875</v>
       </c>
       <c r="J12">
-        <v>59447255.050917439</v>
+        <v>67720075.572822079</v>
       </c>
       <c r="K12">
-        <v>64839617.028884411</v>
+        <v>72300740.44801721</v>
       </c>
     </row>
     <row r="13" spans="1:11" x14ac:dyDescent="0.35">
@@ -1723,22 +1723,22 @@
         <v>11</v>
       </c>
       <c r="B13">
-        <v>1335585.585585586</v>
+        <v>1365315.315315316</v>
       </c>
       <c r="C13">
-        <v>849729.72972973005</v>
+        <v>909189.189189189</v>
       </c>
       <c r="D13">
-        <v>17627540.540540539</v>
+        <v>20201414.414414417</v>
       </c>
       <c r="E13">
-        <v>21593117.117117114</v>
+        <v>23949729.729729727</v>
       </c>
       <c r="F13">
         <v>1819819.8198198189</v>
       </c>
       <c r="G13">
-        <v>648648.64864864899</v>
+        <v>2450450.4504504511</v>
       </c>
       <c r="H13">
         <v>18018.018018018</v>
@@ -1747,10 +1747,10 @@
         <v>18018.018018018</v>
       </c>
       <c r="J13">
-        <v>51389036.302047253</v>
+        <v>58717243.269229785</v>
       </c>
       <c r="K13">
-        <v>51054003.623513147</v>
+        <v>57049699.601031773</v>
       </c>
     </row>
     <row r="14" spans="1:11" x14ac:dyDescent="0.35">
@@ -1758,34 +1758,34 @@
         <v>12</v>
       </c>
       <c r="B14">
-        <v>4705675.6756756762</v>
+        <v>4922792.7927927934</v>
       </c>
       <c r="C14">
-        <v>1931531.5315315309</v>
+        <v>1938738.738738738</v>
       </c>
       <c r="D14">
-        <v>13945720.72072072</v>
+        <v>15974360.36036036</v>
       </c>
       <c r="E14">
-        <v>16015612.612612613</v>
+        <v>17574081.081081081</v>
       </c>
       <c r="F14">
-        <v>2981981.981981982</v>
+        <v>3442342.3423423418</v>
       </c>
       <c r="G14">
         <v>551351.35135135101</v>
       </c>
       <c r="H14">
-        <v>279279.27927927999</v>
+        <v>289189.18918918999</v>
       </c>
       <c r="I14">
         <v>100900.900900901</v>
       </c>
       <c r="J14">
-        <v>33166530.840455465</v>
+        <v>38037294.012150496</v>
       </c>
       <c r="K14">
-        <v>35688394.586691581</v>
+        <v>39399917.081062913</v>
       </c>
     </row>
     <row r="15" spans="1:11" x14ac:dyDescent="0.35">
@@ -1793,34 +1793,34 @@
         <v>13</v>
       </c>
       <c r="B15">
-        <v>29070360.360360362</v>
+        <v>31047567.567567568</v>
       </c>
       <c r="C15">
-        <v>27853423.423423424</v>
+        <v>31092882.882882889</v>
       </c>
       <c r="D15">
-        <v>67946792.792792797</v>
+        <v>79070351.351351365</v>
       </c>
       <c r="E15">
-        <v>67848189.189189181</v>
+        <v>74886153.153153151</v>
       </c>
       <c r="F15">
-        <v>26844054.054054055</v>
+        <v>27392702.702702705</v>
       </c>
       <c r="G15">
-        <v>29228378.378378384</v>
+        <v>31242792.792792797</v>
       </c>
       <c r="H15">
-        <v>725225.22522522497</v>
+        <v>823423.42342342495</v>
       </c>
       <c r="I15">
-        <v>130180.180180182</v>
+        <v>162612.612612614</v>
       </c>
       <c r="J15">
-        <v>119450143.23495574</v>
+        <v>135883629.59817576</v>
       </c>
       <c r="K15">
-        <v>120834377.32331549</v>
+        <v>132967322.54034512</v>
       </c>
     </row>
     <row r="16" spans="1:11" x14ac:dyDescent="0.35">
@@ -1828,34 +1828,34 @@
         <v>14</v>
       </c>
       <c r="B16">
-        <v>25825225.225225225</v>
+        <v>26924864.864864863</v>
       </c>
       <c r="C16">
-        <v>4760720.7207207195</v>
+        <v>14761261.26126126</v>
       </c>
       <c r="D16">
-        <v>21682549.54954955</v>
+        <v>24665792.792792793</v>
       </c>
       <c r="E16">
-        <v>23622765.765765768</v>
+        <v>26786909.909909911</v>
       </c>
       <c r="F16">
         <v>22243243.243243244</v>
       </c>
       <c r="G16">
-        <v>6840540.5405405406</v>
+        <v>16703153.153153151</v>
       </c>
       <c r="H16">
         <v>669369.36936937098</v>
       </c>
       <c r="I16">
-        <v>101801.80180180199</v>
+        <v>110810.810810811</v>
       </c>
       <c r="J16">
-        <v>61961269.757889666</v>
+        <v>71109559.115343332</v>
       </c>
       <c r="K16">
-        <v>68884930.57055968</v>
+        <v>77209357.783545718</v>
       </c>
     </row>
     <row r="17" spans="1:11" x14ac:dyDescent="0.35">
@@ -1864,43 +1864,43 @@
       </c>
       <c r="B17" s="11">
         <f>SUM(B3:B16)</f>
-        <v>380131891.89189196</v>
+        <v>409614324.32432431</v>
       </c>
       <c r="C17" s="11">
         <f t="shared" ref="C17:K17" si="0">SUM(C3:C16)</f>
-        <v>492089504.50450444</v>
+        <v>559590675.67567551</v>
       </c>
       <c r="D17" s="11">
         <f t="shared" si="0"/>
-        <v>568829909.90990984</v>
+        <v>650511225.22522509</v>
       </c>
       <c r="E17" s="11">
         <f t="shared" si="0"/>
-        <v>576382054.05405402</v>
+        <v>642135234.23423433</v>
       </c>
       <c r="F17" s="11">
         <f t="shared" si="0"/>
-        <v>426635990.990991</v>
+        <v>457563918.91891885</v>
       </c>
       <c r="G17" s="11">
         <f t="shared" si="0"/>
-        <v>582238828.82882893</v>
+        <v>670912477.47747743</v>
       </c>
       <c r="H17" s="11">
         <f t="shared" si="0"/>
-        <v>558240033.33333325</v>
+        <v>565270436.03603601</v>
       </c>
       <c r="I17" s="11">
         <f t="shared" si="0"/>
-        <v>412060956.75675672</v>
+        <v>513021678.37837839</v>
       </c>
       <c r="J17" s="11">
         <f t="shared" si="0"/>
-        <v>1190154405.7925994</v>
+        <v>1352856501.834003</v>
       </c>
       <c r="K17" s="11">
         <f t="shared" si="0"/>
-        <v>1219019592.7645988</v>
+        <v>1358024381.1515987</v>
       </c>
     </row>
   </sheetData>

--- a/MS BENGKAYANG 19 JULI 2026.xlsx
+++ b/MS BENGKAYANG 19 JULI 2026.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="19200" windowHeight="6640" activeTab="1"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="19200" windowHeight="6640"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="66" uniqueCount="40">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="68" uniqueCount="42">
   <si>
     <t>KECAMATAN</t>
   </si>
@@ -148,6 +148,12 @@
   </si>
   <si>
     <t>Sum of Prepaid Rev2 LMTD</t>
+  </si>
+  <si>
+    <t>VLR SUBS MTD</t>
+  </si>
+  <si>
+    <t>VLR SUBS LMTD</t>
   </si>
 </sst>
 </file>
@@ -278,7 +284,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="43" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
@@ -309,6 +315,9 @@
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="164" fontId="5" fillId="5" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Comma" xfId="1" builtinId="3"/>
@@ -590,16 +599,18 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A4:L19"/>
+  <dimension ref="A4:N19"/>
   <sheetFormatPr defaultColWidth="11.7265625" defaultRowHeight="64.5" customHeight="1" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="60.6328125" style="2" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="29.54296875" style="6" bestFit="1" customWidth="1"/>
     <col min="3" max="12" width="28.6328125" style="6" customWidth="1"/>
-    <col min="13" max="16384" width="11.7265625" style="2"/>
+    <col min="13" max="13" width="18" style="2" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="19.08984375" style="2" bestFit="1" customWidth="1"/>
+    <col min="15" max="16384" width="11.7265625" style="2"/>
   </cols>
   <sheetData>
-    <row r="4" spans="1:12" ht="64.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:14" ht="64.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C4" s="7"/>
       <c r="D4" s="7"/>
       <c r="E4" s="7"/>
@@ -611,7 +622,7 @@
       <c r="K4" s="7"/>
       <c r="L4" s="7"/>
     </row>
-    <row r="5" spans="1:12" ht="64.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:14" ht="64.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A5" s="3" t="s">
         <v>0</v>
       </c>
@@ -648,8 +659,14 @@
       <c r="L5" s="3" t="s">
         <v>27</v>
       </c>
-    </row>
-    <row r="6" spans="1:12" ht="64.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="M5" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="N5" s="3" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="6" spans="1:14" ht="64.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A6" s="4" t="s">
         <v>2</v>
       </c>
@@ -658,35 +675,35 @@
       </c>
       <c r="C6" s="5">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>9987199.9195197597</v>
+        <v>11435885.059074299</v>
       </c>
       <c r="D6" s="5">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>7512189.1632019328</v>
+        <v>7512201.2733524209</v>
       </c>
       <c r="E6" s="5">
         <f>VLOOKUP(A:A,MASTER!A:H,8,0)</f>
-        <v>3378378.3783783782</v>
+        <v>40540.540540542002</v>
       </c>
       <c r="F6" s="5">
         <f>VLOOKUP(A:A,MASTER!A:I,9,0)</f>
-        <v>51171171.171171166</v>
+        <v>90090.090090090001</v>
       </c>
       <c r="G6" s="5">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>647522.52252252295</v>
+        <v>40540.540540542002</v>
       </c>
       <c r="H6" s="5">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>248648.648648648</v>
+        <v>180180.18018018</v>
       </c>
       <c r="I6" s="5">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
-        <v>5641351.3513513505</v>
+        <v>7065675.6756756762</v>
       </c>
       <c r="J6" s="5">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>4088639.6396396402</v>
+        <v>4115666.666666667</v>
       </c>
       <c r="K6" s="5">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
@@ -696,8 +713,14 @@
         <f>VLOOKUP(A:A,MASTER!A:C,3,0)</f>
         <v>203603.60360360399</v>
       </c>
-    </row>
-    <row r="7" spans="1:12" ht="64.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="M6" s="12">
+        <v>8054</v>
+      </c>
+      <c r="N6" s="12">
+        <v>7964</v>
+      </c>
+    </row>
+    <row r="7" spans="1:14" ht="64.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A7" s="4" t="s">
         <v>6</v>
       </c>
@@ -706,46 +729,52 @@
       </c>
       <c r="C7" s="5">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>250965168.44339868</v>
+        <v>277758523.3629142</v>
       </c>
       <c r="D7" s="5">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>257398940.21128601</v>
+        <v>286604689.71433705</v>
       </c>
       <c r="E7" s="5">
         <f>VLOOKUP(A:A,MASTER!A:H,8,0)</f>
-        <v>235798781.98198199</v>
+        <v>4900000.0000000093</v>
       </c>
       <c r="F7" s="5">
         <f>VLOOKUP(A:A,MASTER!A:I,9,0)</f>
-        <v>151377498.1981982</v>
+        <v>4013513.5135135092</v>
       </c>
       <c r="G7" s="5">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>112554954.95495497</v>
+        <v>125583783.78378379</v>
       </c>
       <c r="H7" s="5">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>170276306.3063063</v>
+        <v>176542522.52252254</v>
       </c>
       <c r="I7" s="5">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
-        <v>174425135.13513514</v>
+        <v>195797351.35135135</v>
       </c>
       <c r="J7" s="5">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>167789855.85585588</v>
+        <v>185211054.05405405</v>
       </c>
       <c r="K7" s="5">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>107143243.24324325</v>
+        <v>122320360.36036037</v>
       </c>
       <c r="L7" s="5">
         <f>VLOOKUP(A:A,MASTER!A:C,3,0)</f>
-        <v>153548468.46846846</v>
-      </c>
-    </row>
-    <row r="8" spans="1:12" ht="64.5" customHeight="1" x14ac:dyDescent="0.35">
+        <v>161384324.32432431</v>
+      </c>
+      <c r="M7" s="12">
+        <v>1100</v>
+      </c>
+      <c r="N7" s="12">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="8" spans="1:14" ht="64.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A8" s="4" t="s">
         <v>7</v>
       </c>
@@ -754,15 +783,15 @@
       </c>
       <c r="C8" s="5">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>62714447.095244333</v>
+        <v>68804127.337667182</v>
       </c>
       <c r="D8" s="5">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>61120914.303842261</v>
+        <v>67518859.38323462</v>
       </c>
       <c r="E8" s="5">
         <f>VLOOKUP(A:A,MASTER!A:H,8,0)</f>
-        <v>152252.25225225301</v>
+        <v>192792.792792794</v>
       </c>
       <c r="F8" s="5">
         <f>VLOOKUP(A:A,MASTER!A:I,9,0)</f>
@@ -770,7 +799,7 @@
       </c>
       <c r="G8" s="5">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>7012612.6126126107</v>
+        <v>7053153.1531531513</v>
       </c>
       <c r="H8" s="5">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
@@ -778,22 +807,28 @@
       </c>
       <c r="I8" s="5">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
-        <v>44273927.927927926</v>
+        <v>49546756.756756753</v>
       </c>
       <c r="J8" s="5">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>40218369.369369365</v>
+        <v>44390981.981981985</v>
       </c>
       <c r="K8" s="5">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>8814774.774774773</v>
+        <v>9568468.4684684686</v>
       </c>
       <c r="L8" s="5">
         <f>VLOOKUP(A:A,MASTER!A:C,3,0)</f>
-        <v>20500810.810810808</v>
-      </c>
-    </row>
-    <row r="9" spans="1:12" ht="64.5" customHeight="1" x14ac:dyDescent="0.35">
+        <v>20761801.801801801</v>
+      </c>
+      <c r="M8" s="12">
+        <v>3627</v>
+      </c>
+      <c r="N8" s="12">
+        <v>3489</v>
+      </c>
+    </row>
+    <row r="9" spans="1:14" ht="64.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A9" s="4" t="s">
         <v>10</v>
       </c>
@@ -802,35 +837,35 @@
       </c>
       <c r="C9" s="5">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>67720075.572822079</v>
+        <v>75147468.387961403</v>
       </c>
       <c r="D9" s="5">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>72300740.44801721</v>
+        <v>79776886.755025342</v>
       </c>
       <c r="E9" s="5">
         <f>VLOOKUP(A:A,MASTER!A:H,8,0)</f>
-        <v>0</v>
+        <v>250713227.02702704</v>
       </c>
       <c r="F9" s="5">
         <f>VLOOKUP(A:A,MASTER!A:I,9,0)</f>
-        <v>0</v>
+        <v>203189164.86486486</v>
       </c>
       <c r="G9" s="5">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>0</v>
+        <v>786261.26126126095</v>
       </c>
       <c r="H9" s="5">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>0</v>
+        <v>88288.288288287993</v>
       </c>
       <c r="I9" s="5">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
-        <v>40885747.747747742</v>
+        <v>45267727.927927926</v>
       </c>
       <c r="J9" s="5">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>44202873.873873875</v>
+        <v>48507468.468468465</v>
       </c>
       <c r="K9" s="5">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
@@ -838,10 +873,16 @@
       </c>
       <c r="L9" s="5">
         <f>VLOOKUP(A:A,MASTER!A:C,3,0)</f>
-        <v>250720.72072072001</v>
-      </c>
-    </row>
-    <row r="10" spans="1:12" ht="64.5" customHeight="1" x14ac:dyDescent="0.35">
+        <v>357117.11711711599</v>
+      </c>
+      <c r="M9" s="12">
+        <v>3620</v>
+      </c>
+      <c r="N9" s="12">
+        <v>3407</v>
+      </c>
+    </row>
+    <row r="10" spans="1:14" ht="64.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A10" s="4" t="s">
         <v>11</v>
       </c>
@@ -850,15 +891,15 @@
       </c>
       <c r="C10" s="5">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>58717243.269229785</v>
+        <v>64957111.005213201</v>
       </c>
       <c r="D10" s="5">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>57049699.601031773</v>
+        <v>63299657.685326733</v>
       </c>
       <c r="E10" s="5">
         <f>VLOOKUP(A:A,MASTER!A:H,8,0)</f>
-        <v>18018.018018018</v>
+        <v>112612.612612615</v>
       </c>
       <c r="F10" s="5">
         <f>VLOOKUP(A:A,MASTER!A:I,9,0)</f>
@@ -866,7 +907,7 @@
       </c>
       <c r="G10" s="5">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>1819819.8198198189</v>
+        <v>1914414.4144144161</v>
       </c>
       <c r="H10" s="5">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
@@ -874,11 +915,11 @@
       </c>
       <c r="I10" s="5">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
-        <v>20201414.414414417</v>
+        <v>22453972.97297297</v>
       </c>
       <c r="J10" s="5">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>23949729.729729727</v>
+        <v>26245450.45045045</v>
       </c>
       <c r="K10" s="5">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
@@ -886,10 +927,16 @@
       </c>
       <c r="L10" s="5">
         <f>VLOOKUP(A:A,MASTER!A:C,3,0)</f>
-        <v>909189.189189189</v>
-      </c>
-    </row>
-    <row r="11" spans="1:12" ht="64.5" customHeight="1" x14ac:dyDescent="0.35">
+        <v>1430810.8108108109</v>
+      </c>
+      <c r="M10" s="12">
+        <v>3016</v>
+      </c>
+      <c r="N10" s="12">
+        <v>2926</v>
+      </c>
+    </row>
+    <row r="11" spans="1:14" ht="64.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A11" s="4" t="s">
         <v>12</v>
       </c>
@@ -898,15 +945,15 @@
       </c>
       <c r="C11" s="5">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>38037294.012150496</v>
+        <v>41953519.313358799</v>
       </c>
       <c r="D11" s="5">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>39399917.081062913</v>
+        <v>43643150.56357944</v>
       </c>
       <c r="E11" s="5">
         <f>VLOOKUP(A:A,MASTER!A:H,8,0)</f>
-        <v>289189.18918918999</v>
+        <v>389189.18918919301</v>
       </c>
       <c r="F11" s="5">
         <f>VLOOKUP(A:A,MASTER!A:I,9,0)</f>
@@ -914,7 +961,7 @@
       </c>
       <c r="G11" s="5">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>3442342.3423423418</v>
+        <v>3542342.342342345</v>
       </c>
       <c r="H11" s="5">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
@@ -922,22 +969,28 @@
       </c>
       <c r="I11" s="5">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
-        <v>15974360.36036036</v>
+        <v>17375801.801801801</v>
       </c>
       <c r="J11" s="5">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>17574081.081081081</v>
+        <v>19426288.288288288</v>
       </c>
       <c r="K11" s="5">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>4922792.7927927934</v>
+        <v>4952522.5225225231</v>
       </c>
       <c r="L11" s="5">
         <f>VLOOKUP(A:A,MASTER!A:C,3,0)</f>
-        <v>1938738.738738738</v>
-      </c>
-    </row>
-    <row r="12" spans="1:12" ht="64.5" customHeight="1" x14ac:dyDescent="0.35">
+        <v>1949549.5495495489</v>
+      </c>
+      <c r="M11" s="12">
+        <v>14019</v>
+      </c>
+      <c r="N11" s="12">
+        <v>13799</v>
+      </c>
+    </row>
+    <row r="12" spans="1:14" ht="64.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A12" s="4" t="s">
         <v>1</v>
       </c>
@@ -946,46 +999,52 @@
       </c>
       <c r="C12" s="5">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>150167027.1591804</v>
+        <v>167024012.88379335</v>
       </c>
       <c r="D12" s="5">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>158833895.18746045</v>
+        <v>175844154.47865763</v>
       </c>
       <c r="E12" s="5">
         <f>VLOOKUP(A:A,MASTER!A:H,8,0)</f>
-        <v>1062162.1621621649</v>
+        <v>1124324.3243243259</v>
       </c>
       <c r="F12" s="5">
         <f>VLOOKUP(A:A,MASTER!A:I,9,0)</f>
-        <v>803603.60360360495</v>
+        <v>817117.11711711797</v>
       </c>
       <c r="G12" s="5">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>21616486.486486487</v>
+        <v>22881531.531531531</v>
       </c>
       <c r="H12" s="5">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>22493918.918918919</v>
+        <v>22989414.414414417</v>
       </c>
       <c r="I12" s="5">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
-        <v>73013324.324324325</v>
+        <v>80831972.972972974</v>
       </c>
       <c r="J12" s="5">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>73107450.45045045</v>
+        <v>81628792.792792797</v>
       </c>
       <c r="K12" s="5">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>18313333.333333332</v>
+        <v>20012882.882882878</v>
       </c>
       <c r="L12" s="5">
         <f>VLOOKUP(A:A,MASTER!A:C,3,0)</f>
-        <v>21375450.450450446</v>
-      </c>
-    </row>
-    <row r="13" spans="1:12" ht="64.5" customHeight="1" x14ac:dyDescent="0.35">
+        <v>22198333.333333336</v>
+      </c>
+      <c r="M12" s="12">
+        <v>4423</v>
+      </c>
+      <c r="N12" s="12">
+        <v>4627</v>
+      </c>
+    </row>
+    <row r="13" spans="1:14" ht="64.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A13" s="4" t="s">
         <v>3</v>
       </c>
@@ -994,46 +1053,52 @@
       </c>
       <c r="C13" s="5">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>112187053.30400717</v>
+        <v>124479909.43520992</v>
       </c>
       <c r="D13" s="5">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>99340915.538647428</v>
+        <v>111464263.10669373</v>
       </c>
       <c r="E13" s="5">
         <f>VLOOKUP(A:A,MASTER!A:H,8,0)</f>
-        <v>319496879.27927929</v>
+        <v>1681081.081081083</v>
       </c>
       <c r="F13" s="5">
         <f>VLOOKUP(A:A,MASTER!A:I,9,0)</f>
-        <v>306618054.05405408</v>
+        <v>578828.82882882899</v>
       </c>
       <c r="G13" s="5">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>40307207.20720721</v>
+        <v>19211711.711711712</v>
       </c>
       <c r="H13" s="5">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>93015315.315315306</v>
+        <v>55008108.108108111</v>
       </c>
       <c r="I13" s="5">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
-        <v>31708351.351351351</v>
+        <v>35350648.648648649</v>
       </c>
       <c r="J13" s="5">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>28277099.0990991</v>
+        <v>31949162.162162162</v>
       </c>
       <c r="K13" s="5">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>17722882.882882882</v>
+        <v>18814324.324324325</v>
       </c>
       <c r="L13" s="5">
         <f>VLOOKUP(A:A,MASTER!A:C,3,0)</f>
-        <v>50179819.819819823</v>
-      </c>
-    </row>
-    <row r="14" spans="1:12" ht="64.5" customHeight="1" x14ac:dyDescent="0.35">
+        <v>50869549.54954955</v>
+      </c>
+      <c r="M13" s="12">
+        <v>6018</v>
+      </c>
+      <c r="N13" s="12">
+        <v>3449</v>
+      </c>
+    </row>
+    <row r="14" spans="1:14" ht="64.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A14" s="4" t="s">
         <v>4</v>
       </c>
@@ -1042,11 +1107,11 @@
       </c>
       <c r="C14" s="5">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>70187104.712153107</v>
+        <v>77443561.495953918</v>
       </c>
       <c r="D14" s="5">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>66272045.910958104</v>
+        <v>73133788.445529953</v>
       </c>
       <c r="E14" s="5">
         <f>VLOOKUP(A:A,MASTER!A:H,8,0)</f>
@@ -1054,34 +1119,40 @@
       </c>
       <c r="F14" s="5">
         <f>VLOOKUP(A:A,MASTER!A:I,9,0)</f>
-        <v>690090.09009008994</v>
+        <v>703603.60360360402</v>
       </c>
       <c r="G14" s="5">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>18601801.801801804</v>
+        <v>19953153.153153151</v>
       </c>
       <c r="H14" s="5">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>27226126.126126129</v>
+        <v>28203603.603603605</v>
       </c>
       <c r="I14" s="5">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
-        <v>24060162.162162159</v>
+        <v>26811324.324324325</v>
       </c>
       <c r="J14" s="5">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>25455198.198198196</v>
+        <v>28138891.891891893</v>
       </c>
       <c r="K14" s="5">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>19848018.018018015</v>
+        <v>21801981.981981982</v>
       </c>
       <c r="L14" s="5">
         <f>VLOOKUP(A:A,MASTER!A:C,3,0)</f>
-        <v>18954774.774774775</v>
-      </c>
-    </row>
-    <row r="15" spans="1:12" ht="64.5" customHeight="1" x14ac:dyDescent="0.35">
+        <v>21557027.02702703</v>
+      </c>
+      <c r="M14" s="12">
+        <v>7259</v>
+      </c>
+      <c r="N14" s="12">
+        <v>7191</v>
+      </c>
+    </row>
+    <row r="15" spans="1:14" ht="64.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A15" s="4" t="s">
         <v>5</v>
       </c>
@@ -1090,15 +1161,15 @@
       </c>
       <c r="C15" s="5">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>75348708.800628439</v>
+        <v>83638677.803553104</v>
       </c>
       <c r="D15" s="5">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>74886227.59351182</v>
+        <v>83241276.547920391</v>
       </c>
       <c r="E15" s="5">
         <f>VLOOKUP(A:A,MASTER!A:H,8,0)</f>
-        <v>147747.74774774801</v>
+        <v>150450.45045045001</v>
       </c>
       <c r="F15" s="5">
         <f>VLOOKUP(A:A,MASTER!A:I,9,0)</f>
@@ -1106,30 +1177,36 @@
       </c>
       <c r="G15" s="5">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>5893693.6936936928</v>
+        <v>6797297.2972972961</v>
       </c>
       <c r="H15" s="5">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>10725225.225225225</v>
+        <v>11175675.675675675</v>
       </c>
       <c r="I15" s="5">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
-        <v>30558927.927927926</v>
+        <v>34689288.288288288</v>
       </c>
       <c r="J15" s="5">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>30988135.135135137</v>
+        <v>34429891.891891889</v>
       </c>
       <c r="K15" s="5">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>5518378.3783783782</v>
+        <v>5917567.5675675683</v>
       </c>
       <c r="L15" s="5">
         <f>VLOOKUP(A:A,MASTER!A:C,3,0)</f>
-        <v>9525675.6756756753</v>
-      </c>
-    </row>
-    <row r="16" spans="1:12" ht="64.5" customHeight="1" x14ac:dyDescent="0.35">
+        <v>9870000</v>
+      </c>
+      <c r="M15" s="12">
+        <v>3674</v>
+      </c>
+      <c r="N15" s="12">
+        <v>3667</v>
+      </c>
+    </row>
+    <row r="16" spans="1:14" ht="64.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A16" s="4" t="s">
         <v>8</v>
       </c>
@@ -1138,46 +1215,52 @@
       </c>
       <c r="C16" s="5">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>83854093.49572067</v>
+        <v>92677006.923511267</v>
       </c>
       <c r="D16" s="5">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>90960999.439689696</v>
+        <v>99911377.220618293</v>
       </c>
       <c r="E16" s="5">
         <f>VLOOKUP(A:A,MASTER!A:H,8,0)</f>
-        <v>1211711.711711714</v>
+        <v>1301801.801801804</v>
       </c>
       <c r="F16" s="5">
         <f>VLOOKUP(A:A,MASTER!A:I,9,0)</f>
-        <v>1065765.765765765</v>
+        <v>1115315.315315316</v>
       </c>
       <c r="G16" s="5">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>12828828.82882883</v>
+        <v>12918918.918918921</v>
       </c>
       <c r="H16" s="5">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>15034684.684684686</v>
+        <v>19396396.396396399</v>
       </c>
       <c r="I16" s="5">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
-        <v>24929153.153153151</v>
+        <v>27309549.54954955</v>
       </c>
       <c r="J16" s="5">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>27055720.72072072</v>
+        <v>30287387.387387387</v>
       </c>
       <c r="K16" s="5">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>11406396.396396397</v>
+        <v>12188738.738738736</v>
       </c>
       <c r="L16" s="5">
         <f>VLOOKUP(A:A,MASTER!A:C,3,0)</f>
-        <v>14261441.441441443</v>
-      </c>
-    </row>
-    <row r="17" spans="1:12" ht="64.5" customHeight="1" x14ac:dyDescent="0.35">
+        <v>18979459.459459461</v>
+      </c>
+      <c r="M16" s="12">
+        <v>3875</v>
+      </c>
+      <c r="N16" s="12">
+        <v>4035</v>
+      </c>
+    </row>
+    <row r="17" spans="1:14" ht="64.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A17" s="4" t="s">
         <v>9</v>
       </c>
@@ -1186,46 +1269,52 @@
       </c>
       <c r="C17" s="5">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>165977897.33642882</v>
+        <v>184208203.93830642</v>
       </c>
       <c r="D17" s="5">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>162771216.34899825</v>
+        <v>178909452.82663804</v>
       </c>
       <c r="E17" s="5">
         <f>VLOOKUP(A:A,MASTER!A:H,8,0)</f>
-        <v>1371171.171171176</v>
+        <v>1532432.4324324371</v>
       </c>
       <c r="F17" s="5">
         <f>VLOOKUP(A:A,MASTER!A:I,9,0)</f>
-        <v>851801.80180180096</v>
+        <v>894144.14414414496</v>
       </c>
       <c r="G17" s="5">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>183202702.7027027</v>
+        <v>197469369.36936939</v>
       </c>
       <c r="H17" s="5">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>261253513.51351351</v>
+        <v>264517477.47747746</v>
       </c>
       <c r="I17" s="5">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
-        <v>61103225.225225225</v>
+        <v>68568540.540540546</v>
       </c>
       <c r="J17" s="5">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>57755018.018018015</v>
+        <v>64665108.108108103</v>
       </c>
       <c r="K17" s="5">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>156418018.01801801</v>
+        <v>184796486.48648649</v>
       </c>
       <c r="L17" s="5">
         <f>VLOOKUP(A:A,MASTER!A:C,3,0)</f>
-        <v>222087837.83783782</v>
-      </c>
-    </row>
-    <row r="18" spans="1:12" ht="64.5" customHeight="1" x14ac:dyDescent="0.35">
+        <v>240402882.88288289</v>
+      </c>
+      <c r="M17" s="12">
+        <v>2921</v>
+      </c>
+      <c r="N17" s="12">
+        <v>3061</v>
+      </c>
+    </row>
+    <row r="18" spans="1:14" ht="64.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A18" s="4" t="s">
         <v>13</v>
       </c>
@@ -1234,46 +1323,52 @@
       </c>
       <c r="C18" s="5">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>135883629.59817576</v>
+        <v>151110852.08540854</v>
       </c>
       <c r="D18" s="5">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>132967322.54034512</v>
+        <v>146960764.92853495</v>
       </c>
       <c r="E18" s="5">
         <f>VLOOKUP(A:A,MASTER!A:H,8,0)</f>
-        <v>823423.42342342495</v>
+        <v>912612.61261261499</v>
       </c>
       <c r="F18" s="5">
         <f>VLOOKUP(A:A,MASTER!A:I,9,0)</f>
-        <v>162612.612612614</v>
+        <v>189189.18918918999</v>
       </c>
       <c r="G18" s="5">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>27392702.702702705</v>
+        <v>37331621.621621616</v>
       </c>
       <c r="H18" s="5">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>31242792.792792797</v>
+        <v>35474774.774774775</v>
       </c>
       <c r="I18" s="5">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
-        <v>79070351.351351365</v>
+        <v>87426378.378378391</v>
       </c>
       <c r="J18" s="5">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>74886153.153153151</v>
+        <v>83530387.387387395</v>
       </c>
       <c r="K18" s="5">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>31047567.567567568</v>
+        <v>38159639.639639638</v>
       </c>
       <c r="L18" s="5">
         <f>VLOOKUP(A:A,MASTER!A:C,3,0)</f>
-        <v>31092882.882882889</v>
-      </c>
-    </row>
-    <row r="19" spans="1:12" ht="64.5" customHeight="1" x14ac:dyDescent="0.35">
+        <v>35027297.297297299</v>
+      </c>
+      <c r="M18" s="12">
+        <v>7031</v>
+      </c>
+      <c r="N18" s="12">
+        <v>6924</v>
+      </c>
+    </row>
+    <row r="19" spans="1:14" ht="64.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A19" s="4" t="s">
         <v>14</v>
       </c>
@@ -1282,11 +1377,11 @@
       </c>
       <c r="C19" s="5">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>71109559.115343332</v>
+        <v>78813022.56256333</v>
       </c>
       <c r="D19" s="5">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>77209357.783545718</v>
+        <v>86101440.05152458</v>
       </c>
       <c r="E19" s="5">
         <f>VLOOKUP(A:A,MASTER!A:H,8,0)</f>
@@ -1294,7 +1389,7 @@
       </c>
       <c r="F19" s="5">
         <f>VLOOKUP(A:A,MASTER!A:I,9,0)</f>
-        <v>110810.810810811</v>
+        <v>124324.324324325</v>
       </c>
       <c r="G19" s="5">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
@@ -1302,23 +1397,29 @@
       </c>
       <c r="H19" s="5">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>16703153.153153151</v>
+        <v>16811261.261261258</v>
       </c>
       <c r="I19" s="5">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
-        <v>24665792.792792793</v>
+        <v>27161783.783783782</v>
       </c>
       <c r="J19" s="5">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>26786909.909909911</v>
+        <v>29936234.234234232</v>
       </c>
       <c r="K19" s="5">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>26924864.864864863</v>
+        <v>27517477.47747748</v>
       </c>
       <c r="L19" s="5">
         <f>VLOOKUP(A:A,MASTER!A:C,3,0)</f>
-        <v>14761261.26126126</v>
+        <v>15241801.801801801</v>
+      </c>
+      <c r="M19" s="12">
+        <v>3941</v>
+      </c>
+      <c r="N19" s="12">
+        <v>4169</v>
       </c>
     </row>
   </sheetData>
@@ -1385,34 +1486,34 @@
         <v>1</v>
       </c>
       <c r="B3">
-        <v>18313333.333333332</v>
+        <v>20012882.882882878</v>
       </c>
       <c r="C3">
-        <v>21375450.450450446</v>
+        <v>22198333.333333336</v>
       </c>
       <c r="D3">
-        <v>73013324.324324325</v>
+        <v>80831972.972972974</v>
       </c>
       <c r="E3">
-        <v>73107450.45045045</v>
+        <v>81628792.792792797</v>
       </c>
       <c r="F3">
-        <v>21616486.486486487</v>
+        <v>22881531.531531531</v>
       </c>
       <c r="G3">
-        <v>22493918.918918919</v>
+        <v>22989414.414414417</v>
       </c>
       <c r="H3">
-        <v>1062162.1621621649</v>
+        <v>1124324.3243243259</v>
       </c>
       <c r="I3">
-        <v>803603.60360360495</v>
+        <v>817117.11711711797</v>
       </c>
       <c r="J3">
-        <v>150167027.1591804</v>
+        <v>167024012.88379335</v>
       </c>
       <c r="K3">
-        <v>158833895.18746045</v>
+        <v>175844154.47865763</v>
       </c>
     </row>
     <row r="4" spans="1:11" x14ac:dyDescent="0.35">
@@ -1426,28 +1527,28 @@
         <v>203603.60360360399</v>
       </c>
       <c r="D4">
-        <v>5641351.3513513505</v>
+        <v>7065675.6756756762</v>
       </c>
       <c r="E4">
-        <v>4088639.6396396402</v>
+        <v>4115666.666666667</v>
       </c>
       <c r="F4">
-        <v>647522.52252252295</v>
+        <v>40540.540540542002</v>
       </c>
       <c r="G4">
-        <v>248648.648648648</v>
+        <v>180180.18018018</v>
       </c>
       <c r="H4">
-        <v>3378378.3783783782</v>
+        <v>40540.540540542002</v>
       </c>
       <c r="I4">
-        <v>51171171.171171166</v>
+        <v>90090.090090090001</v>
       </c>
       <c r="J4">
-        <v>9987199.9195197597</v>
+        <v>11435885.059074299</v>
       </c>
       <c r="K4">
-        <v>7512189.1632019328</v>
+        <v>7512201.2733524209</v>
       </c>
     </row>
     <row r="5" spans="1:11" x14ac:dyDescent="0.35">
@@ -1455,34 +1556,34 @@
         <v>3</v>
       </c>
       <c r="B5">
-        <v>17722882.882882882</v>
+        <v>18814324.324324325</v>
       </c>
       <c r="C5">
-        <v>50179819.819819823</v>
+        <v>50869549.54954955</v>
       </c>
       <c r="D5">
-        <v>31708351.351351351</v>
+        <v>35350648.648648649</v>
       </c>
       <c r="E5">
-        <v>28277099.0990991</v>
+        <v>31949162.162162162</v>
       </c>
       <c r="F5">
-        <v>40307207.20720721</v>
+        <v>19211711.711711712</v>
       </c>
       <c r="G5">
-        <v>93015315.315315306</v>
+        <v>55008108.108108111</v>
       </c>
       <c r="H5">
-        <v>319496879.27927929</v>
+        <v>1681081.081081083</v>
       </c>
       <c r="I5">
-        <v>306618054.05405408</v>
+        <v>578828.82882882899</v>
       </c>
       <c r="J5">
-        <v>112187053.30400717</v>
+        <v>124479909.43520992</v>
       </c>
       <c r="K5">
-        <v>99340915.538647428</v>
+        <v>111464263.10669373</v>
       </c>
     </row>
     <row r="6" spans="1:11" x14ac:dyDescent="0.35">
@@ -1490,34 +1591,34 @@
         <v>4</v>
       </c>
       <c r="B6">
-        <v>19848018.018018015</v>
+        <v>21801981.981981982</v>
       </c>
       <c r="C6">
-        <v>18954774.774774775</v>
+        <v>21557027.02702703</v>
       </c>
       <c r="D6">
-        <v>24060162.162162159</v>
+        <v>26811324.324324325</v>
       </c>
       <c r="E6">
-        <v>25455198.198198196</v>
+        <v>28138891.891891893</v>
       </c>
       <c r="F6">
-        <v>18601801.801801804</v>
+        <v>19953153.153153151</v>
       </c>
       <c r="G6">
-        <v>27226126.126126129</v>
+        <v>28203603.603603605</v>
       </c>
       <c r="H6">
         <v>851351.35135135299</v>
       </c>
       <c r="I6">
-        <v>690090.09009008994</v>
+        <v>703603.60360360402</v>
       </c>
       <c r="J6">
-        <v>70187104.712153107</v>
+        <v>77443561.495953918</v>
       </c>
       <c r="K6">
-        <v>66272045.910958104</v>
+        <v>73133788.445529953</v>
       </c>
     </row>
     <row r="7" spans="1:11" x14ac:dyDescent="0.35">
@@ -1525,34 +1626,34 @@
         <v>5</v>
       </c>
       <c r="B7">
-        <v>5518378.3783783782</v>
+        <v>5917567.5675675683</v>
       </c>
       <c r="C7">
-        <v>9525675.6756756753</v>
+        <v>9870000</v>
       </c>
       <c r="D7">
-        <v>30558927.927927926</v>
+        <v>34689288.288288288</v>
       </c>
       <c r="E7">
-        <v>30988135.135135137</v>
+        <v>34429891.891891889</v>
       </c>
       <c r="F7">
-        <v>5893693.6936936928</v>
+        <v>6797297.2972972961</v>
       </c>
       <c r="G7">
-        <v>10725225.225225225</v>
+        <v>11175675.675675675</v>
       </c>
       <c r="H7">
-        <v>147747.74774774801</v>
+        <v>150450.45045045001</v>
       </c>
       <c r="I7">
         <v>13513.513513514001</v>
       </c>
       <c r="J7">
-        <v>75348708.800628439</v>
+        <v>83638677.803553104</v>
       </c>
       <c r="K7">
-        <v>74886227.59351182</v>
+        <v>83241276.547920391</v>
       </c>
     </row>
     <row r="8" spans="1:11" x14ac:dyDescent="0.35">
@@ -1560,34 +1661,34 @@
         <v>6</v>
       </c>
       <c r="B8">
-        <v>107143243.24324325</v>
+        <v>122320360.36036037</v>
       </c>
       <c r="C8">
-        <v>153548468.46846846</v>
+        <v>161384324.32432431</v>
       </c>
       <c r="D8">
-        <v>174425135.13513514</v>
+        <v>195797351.35135135</v>
       </c>
       <c r="E8">
-        <v>167789855.85585588</v>
+        <v>185211054.05405405</v>
       </c>
       <c r="F8">
-        <v>112554954.95495497</v>
+        <v>125583783.78378379</v>
       </c>
       <c r="G8">
-        <v>170276306.3063063</v>
+        <v>176542522.52252254</v>
       </c>
       <c r="H8">
-        <v>235798781.98198199</v>
+        <v>4900000.0000000093</v>
       </c>
       <c r="I8">
-        <v>151377498.1981982</v>
+        <v>4013513.5135135092</v>
       </c>
       <c r="J8">
-        <v>250965168.44339868</v>
+        <v>277758523.3629142</v>
       </c>
       <c r="K8">
-        <v>257398940.21128601</v>
+        <v>286604689.71433705</v>
       </c>
     </row>
     <row r="9" spans="1:11" x14ac:dyDescent="0.35">
@@ -1595,34 +1696,34 @@
         <v>7</v>
       </c>
       <c r="B9">
-        <v>8814774.774774773</v>
+        <v>9568468.4684684686</v>
       </c>
       <c r="C9">
-        <v>20500810.810810808</v>
+        <v>20761801.801801801</v>
       </c>
       <c r="D9">
-        <v>44273927.927927926</v>
+        <v>49546756.756756753</v>
       </c>
       <c r="E9">
-        <v>40218369.369369365</v>
+        <v>44390981.981981985</v>
       </c>
       <c r="F9">
-        <v>7012612.6126126107</v>
+        <v>7053153.1531531513</v>
       </c>
       <c r="G9">
         <v>19690990.990990993</v>
       </c>
       <c r="H9">
-        <v>152252.25225225301</v>
+        <v>192792.792792794</v>
       </c>
       <c r="I9">
         <v>37837.837837838</v>
       </c>
       <c r="J9">
-        <v>62714447.095244333</v>
+        <v>68804127.337667182</v>
       </c>
       <c r="K9">
-        <v>61120914.303842261</v>
+        <v>67518859.38323462</v>
       </c>
     </row>
     <row r="10" spans="1:11" x14ac:dyDescent="0.35">
@@ -1630,34 +1731,34 @@
         <v>8</v>
       </c>
       <c r="B10">
-        <v>11406396.396396397</v>
+        <v>12188738.738738736</v>
       </c>
       <c r="C10">
-        <v>14261441.441441443</v>
+        <v>18979459.459459461</v>
       </c>
       <c r="D10">
-        <v>24929153.153153151</v>
+        <v>27309549.54954955</v>
       </c>
       <c r="E10">
-        <v>27055720.72072072</v>
+        <v>30287387.387387387</v>
       </c>
       <c r="F10">
-        <v>12828828.82882883</v>
+        <v>12918918.918918921</v>
       </c>
       <c r="G10">
-        <v>15034684.684684686</v>
+        <v>19396396.396396399</v>
       </c>
       <c r="H10">
-        <v>1211711.711711714</v>
+        <v>1301801.801801804</v>
       </c>
       <c r="I10">
-        <v>1065765.765765765</v>
+        <v>1115315.315315316</v>
       </c>
       <c r="J10">
-        <v>83854093.49572067</v>
+        <v>92677006.923511267</v>
       </c>
       <c r="K10">
-        <v>90960999.439689696</v>
+        <v>99911377.220618293</v>
       </c>
     </row>
     <row r="11" spans="1:11" x14ac:dyDescent="0.35">
@@ -1665,34 +1766,34 @@
         <v>9</v>
       </c>
       <c r="B11">
-        <v>156418018.01801801</v>
+        <v>184796486.48648649</v>
       </c>
       <c r="C11">
-        <v>222087837.83783782</v>
+        <v>240402882.88288289</v>
       </c>
       <c r="D11">
-        <v>61103225.225225225</v>
+        <v>68568540.540540546</v>
       </c>
       <c r="E11">
-        <v>57755018.018018015</v>
+        <v>64665108.108108103</v>
       </c>
       <c r="F11">
-        <v>183202702.7027027</v>
+        <v>197469369.36936939</v>
       </c>
       <c r="G11">
-        <v>261253513.51351351</v>
+        <v>264517477.47747746</v>
       </c>
       <c r="H11">
-        <v>1371171.171171176</v>
+        <v>1532432.4324324371</v>
       </c>
       <c r="I11">
-        <v>851801.80180180096</v>
+        <v>894144.14414414496</v>
       </c>
       <c r="J11">
-        <v>165977897.33642882</v>
+        <v>184208203.93830642</v>
       </c>
       <c r="K11">
-        <v>162771216.34899825</v>
+        <v>178909452.82663804</v>
       </c>
     </row>
     <row r="12" spans="1:11" x14ac:dyDescent="0.35">
@@ -1703,19 +1804,31 @@
         <v>11081.081081081</v>
       </c>
       <c r="C12">
-        <v>250720.72072072001</v>
+        <v>357117.11711711599</v>
       </c>
       <c r="D12">
-        <v>40885747.747747742</v>
+        <v>45267727.927927926</v>
       </c>
       <c r="E12">
-        <v>44202873.873873875</v>
+        <v>48507468.468468465</v>
+      </c>
+      <c r="F12">
+        <v>786261.26126126095</v>
+      </c>
+      <c r="G12">
+        <v>88288.288288287993</v>
+      </c>
+      <c r="H12">
+        <v>250713227.02702704</v>
+      </c>
+      <c r="I12">
+        <v>203189164.86486486</v>
       </c>
       <c r="J12">
-        <v>67720075.572822079</v>
+        <v>75147468.387961403</v>
       </c>
       <c r="K12">
-        <v>72300740.44801721</v>
+        <v>79776886.755025342</v>
       </c>
     </row>
     <row r="13" spans="1:11" x14ac:dyDescent="0.35">
@@ -1726,31 +1839,31 @@
         <v>1365315.315315316</v>
       </c>
       <c r="C13">
-        <v>909189.189189189</v>
+        <v>1430810.8108108109</v>
       </c>
       <c r="D13">
-        <v>20201414.414414417</v>
+        <v>22453972.97297297</v>
       </c>
       <c r="E13">
-        <v>23949729.729729727</v>
+        <v>26245450.45045045</v>
       </c>
       <c r="F13">
-        <v>1819819.8198198189</v>
+        <v>1914414.4144144161</v>
       </c>
       <c r="G13">
         <v>2450450.4504504511</v>
       </c>
       <c r="H13">
-        <v>18018.018018018</v>
+        <v>112612.612612615</v>
       </c>
       <c r="I13">
         <v>18018.018018018</v>
       </c>
       <c r="J13">
-        <v>58717243.269229785</v>
+        <v>64957111.005213201</v>
       </c>
       <c r="K13">
-        <v>57049699.601031773</v>
+        <v>63299657.685326733</v>
       </c>
     </row>
     <row r="14" spans="1:11" x14ac:dyDescent="0.35">
@@ -1758,34 +1871,34 @@
         <v>12</v>
       </c>
       <c r="B14">
-        <v>4922792.7927927934</v>
+        <v>4952522.5225225231</v>
       </c>
       <c r="C14">
-        <v>1938738.738738738</v>
+        <v>1949549.5495495489</v>
       </c>
       <c r="D14">
-        <v>15974360.36036036</v>
+        <v>17375801.801801801</v>
       </c>
       <c r="E14">
-        <v>17574081.081081081</v>
+        <v>19426288.288288288</v>
       </c>
       <c r="F14">
-        <v>3442342.3423423418</v>
+        <v>3542342.342342345</v>
       </c>
       <c r="G14">
         <v>551351.35135135101</v>
       </c>
       <c r="H14">
-        <v>289189.18918918999</v>
+        <v>389189.18918919301</v>
       </c>
       <c r="I14">
         <v>100900.900900901</v>
       </c>
       <c r="J14">
-        <v>38037294.012150496</v>
+        <v>41953519.313358799</v>
       </c>
       <c r="K14">
-        <v>39399917.081062913</v>
+        <v>43643150.56357944</v>
       </c>
     </row>
     <row r="15" spans="1:11" x14ac:dyDescent="0.35">
@@ -1793,34 +1906,34 @@
         <v>13</v>
       </c>
       <c r="B15">
-        <v>31047567.567567568</v>
+        <v>38159639.639639638</v>
       </c>
       <c r="C15">
-        <v>31092882.882882889</v>
+        <v>35027297.297297299</v>
       </c>
       <c r="D15">
-        <v>79070351.351351365</v>
+        <v>87426378.378378391</v>
       </c>
       <c r="E15">
-        <v>74886153.153153151</v>
+        <v>83530387.387387395</v>
       </c>
       <c r="F15">
-        <v>27392702.702702705</v>
+        <v>37331621.621621616</v>
       </c>
       <c r="G15">
-        <v>31242792.792792797</v>
+        <v>35474774.774774775</v>
       </c>
       <c r="H15">
-        <v>823423.42342342495</v>
+        <v>912612.61261261499</v>
       </c>
       <c r="I15">
-        <v>162612.612612614</v>
+        <v>189189.18918918999</v>
       </c>
       <c r="J15">
-        <v>135883629.59817576</v>
+        <v>151110852.08540854</v>
       </c>
       <c r="K15">
-        <v>132967322.54034512</v>
+        <v>146960764.92853495</v>
       </c>
     </row>
     <row r="16" spans="1:11" x14ac:dyDescent="0.35">
@@ -1828,34 +1941,34 @@
         <v>14</v>
       </c>
       <c r="B16">
-        <v>26924864.864864863</v>
+        <v>27517477.47747748</v>
       </c>
       <c r="C16">
-        <v>14761261.26126126</v>
+        <v>15241801.801801801</v>
       </c>
       <c r="D16">
-        <v>24665792.792792793</v>
+        <v>27161783.783783782</v>
       </c>
       <c r="E16">
-        <v>26786909.909909911</v>
+        <v>29936234.234234232</v>
       </c>
       <c r="F16">
         <v>22243243.243243244</v>
       </c>
       <c r="G16">
-        <v>16703153.153153151</v>
+        <v>16811261.261261258</v>
       </c>
       <c r="H16">
         <v>669369.36936937098</v>
       </c>
       <c r="I16">
-        <v>110810.810810811</v>
+        <v>124324.324324325</v>
       </c>
       <c r="J16">
-        <v>71109559.115343332</v>
+        <v>78813022.56256333</v>
       </c>
       <c r="K16">
-        <v>77209357.783545718</v>
+        <v>86101440.05152458</v>
       </c>
     </row>
     <row r="17" spans="1:11" x14ac:dyDescent="0.35">
@@ -1864,43 +1977,43 @@
       </c>
       <c r="B17" s="11">
         <f>SUM(B3:B16)</f>
-        <v>409614324.32432431</v>
+        <v>467584504.5045045</v>
       </c>
       <c r="C17" s="11">
         <f t="shared" ref="C17:K17" si="0">SUM(C3:C16)</f>
-        <v>559590675.67567551</v>
+        <v>600233558.55855858</v>
       </c>
       <c r="D17" s="11">
         <f t="shared" si="0"/>
-        <v>650511225.22522509</v>
+        <v>725656772.97297311</v>
       </c>
       <c r="E17" s="11">
         <f t="shared" si="0"/>
-        <v>642135234.23423433</v>
+        <v>712462765.76576567</v>
       </c>
       <c r="F17" s="11">
         <f t="shared" si="0"/>
-        <v>457563918.91891885</v>
+        <v>477727342.34234226</v>
       </c>
       <c r="G17" s="11">
         <f t="shared" si="0"/>
-        <v>670912477.47747743</v>
+        <v>653080495.49549544</v>
       </c>
       <c r="H17" s="11">
         <f t="shared" si="0"/>
-        <v>565270436.03603601</v>
+        <v>264571785.58558559</v>
       </c>
       <c r="I17" s="11">
         <f t="shared" si="0"/>
-        <v>513021678.37837839</v>
+        <v>211885561.26126125</v>
       </c>
       <c r="J17" s="11">
         <f t="shared" si="0"/>
-        <v>1352856501.834003</v>
+        <v>1499451881.5944889</v>
       </c>
       <c r="K17" s="11">
         <f t="shared" si="0"/>
-        <v>1358024381.1515987</v>
+        <v>1503921962.9809732</v>
       </c>
     </row>
   </sheetData>

--- a/MS BENGKAYANG 19 JULI 2026.xlsx
+++ b/MS BENGKAYANG 19 JULI 2026.xlsx
@@ -204,6 +204,7 @@
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="6">
@@ -714,10 +715,10 @@
         <v>203603.60360360399</v>
       </c>
       <c r="M6" s="12">
-        <v>8054</v>
+        <v>1100</v>
       </c>
       <c r="N6" s="12">
-        <v>7964</v>
+        <v>34</v>
       </c>
     </row>
     <row r="7" spans="1:14" ht="64.5" customHeight="1" x14ac:dyDescent="0.35">
@@ -768,10 +769,10 @@
         <v>161384324.32432431</v>
       </c>
       <c r="M7" s="12">
-        <v>1100</v>
+        <v>14019</v>
       </c>
       <c r="N7" s="12">
-        <v>34</v>
+        <v>13799</v>
       </c>
     </row>
     <row r="8" spans="1:14" ht="64.5" customHeight="1" x14ac:dyDescent="0.35">
@@ -822,10 +823,10 @@
         <v>20761801.801801801</v>
       </c>
       <c r="M8" s="12">
-        <v>3627</v>
+        <v>4423</v>
       </c>
       <c r="N8" s="12">
-        <v>3489</v>
+        <v>4627</v>
       </c>
     </row>
     <row r="9" spans="1:14" ht="64.5" customHeight="1" x14ac:dyDescent="0.35">
@@ -876,10 +877,10 @@
         <v>357117.11711711599</v>
       </c>
       <c r="M9" s="12">
-        <v>3620</v>
+        <v>3674</v>
       </c>
       <c r="N9" s="12">
-        <v>3407</v>
+        <v>3667</v>
       </c>
     </row>
     <row r="10" spans="1:14" ht="64.5" customHeight="1" x14ac:dyDescent="0.35">
@@ -930,10 +931,10 @@
         <v>1430810.8108108109</v>
       </c>
       <c r="M10" s="12">
-        <v>3016</v>
+        <v>3875</v>
       </c>
       <c r="N10" s="12">
-        <v>2926</v>
+        <v>4035</v>
       </c>
     </row>
     <row r="11" spans="1:14" ht="64.5" customHeight="1" x14ac:dyDescent="0.35">
@@ -984,10 +985,10 @@
         <v>1949549.5495495489</v>
       </c>
       <c r="M11" s="12">
-        <v>14019</v>
+        <v>2921</v>
       </c>
       <c r="N11" s="12">
-        <v>13799</v>
+        <v>3061</v>
       </c>
     </row>
     <row r="12" spans="1:14" ht="64.5" customHeight="1" x14ac:dyDescent="0.35">
@@ -1038,10 +1039,10 @@
         <v>22198333.333333336</v>
       </c>
       <c r="M12" s="12">
-        <v>4423</v>
+        <v>8054</v>
       </c>
       <c r="N12" s="12">
-        <v>4627</v>
+        <v>7964</v>
       </c>
     </row>
     <row r="13" spans="1:14" ht="64.5" customHeight="1" x14ac:dyDescent="0.35">
@@ -1092,10 +1093,10 @@
         <v>50869549.54954955</v>
       </c>
       <c r="M13" s="12">
-        <v>6018</v>
+        <v>3627</v>
       </c>
       <c r="N13" s="12">
-        <v>3449</v>
+        <v>3489</v>
       </c>
     </row>
     <row r="14" spans="1:14" ht="64.5" customHeight="1" x14ac:dyDescent="0.35">
@@ -1146,10 +1147,10 @@
         <v>21557027.02702703</v>
       </c>
       <c r="M14" s="12">
-        <v>7259</v>
+        <v>3620</v>
       </c>
       <c r="N14" s="12">
-        <v>7191</v>
+        <v>3407</v>
       </c>
     </row>
     <row r="15" spans="1:14" ht="64.5" customHeight="1" x14ac:dyDescent="0.35">
@@ -1200,10 +1201,10 @@
         <v>9870000</v>
       </c>
       <c r="M15" s="12">
-        <v>3674</v>
+        <v>3016</v>
       </c>
       <c r="N15" s="12">
-        <v>3667</v>
+        <v>2926</v>
       </c>
     </row>
     <row r="16" spans="1:14" ht="64.5" customHeight="1" x14ac:dyDescent="0.35">
@@ -1254,10 +1255,10 @@
         <v>18979459.459459461</v>
       </c>
       <c r="M16" s="12">
-        <v>3875</v>
+        <v>6018</v>
       </c>
       <c r="N16" s="12">
-        <v>4035</v>
+        <v>3449</v>
       </c>
     </row>
     <row r="17" spans="1:14" ht="64.5" customHeight="1" x14ac:dyDescent="0.35">
@@ -1308,10 +1309,10 @@
         <v>240402882.88288289</v>
       </c>
       <c r="M17" s="12">
-        <v>2921</v>
+        <v>7259</v>
       </c>
       <c r="N17" s="12">
-        <v>3061</v>
+        <v>7191</v>
       </c>
     </row>
     <row r="18" spans="1:14" ht="64.5" customHeight="1" x14ac:dyDescent="0.35">

--- a/MS BENGKAYANG 19 JULI 2026.xlsx
+++ b/MS BENGKAYANG 19 JULI 2026.xlsx
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="68" uniqueCount="42">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="72" uniqueCount="45">
   <si>
     <t>KECAMATAN</t>
   </si>
@@ -154,6 +154,15 @@
   </si>
   <si>
     <t>VLR SUBS LMTD</t>
+  </si>
+  <si>
+    <t>VLR_SUBS</t>
+  </si>
+  <si>
+    <t>MTD</t>
+  </si>
+  <si>
+    <t>LMTD</t>
   </si>
 </sst>
 </file>
@@ -239,7 +248,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="4">
+  <borders count="5">
     <border>
       <left/>
       <right/>
@@ -280,12 +289,21 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="43" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
@@ -319,6 +337,11 @@
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Comma" xfId="1" builtinId="3"/>
@@ -676,11 +699,11 @@
       </c>
       <c r="C6" s="5">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>11435885.059074299</v>
+        <v>13395326.593805984</v>
       </c>
       <c r="D6" s="5">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>7512201.2733524209</v>
+        <v>7512211.1851744372</v>
       </c>
       <c r="E6" s="5">
         <f>VLOOKUP(A:A,MASTER!A:H,8,0)</f>
@@ -700,7 +723,7 @@
       </c>
       <c r="I6" s="5">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
-        <v>7065675.6756756762</v>
+        <v>8455585.5855855867</v>
       </c>
       <c r="J6" s="5">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
@@ -715,10 +738,12 @@
         <v>203603.60360360399</v>
       </c>
       <c r="M6" s="12">
-        <v>1100</v>
+        <f>VLOOKUP(A:A,MASTER!A:L,12,0)</f>
+        <v>1622</v>
       </c>
       <c r="N6" s="12">
-        <v>34</v>
+        <f>VLOOKUP(A:A,MASTER!A:M,13,0)</f>
+        <v>41</v>
       </c>
     </row>
     <row r="7" spans="1:14" ht="64.5" customHeight="1" x14ac:dyDescent="0.35">
@@ -730,49 +755,51 @@
       </c>
       <c r="C7" s="5">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>277758523.3629142</v>
+        <v>306453254.68844277</v>
       </c>
       <c r="D7" s="5">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>286604689.71433705</v>
+        <v>316576001.14128393</v>
       </c>
       <c r="E7" s="5">
         <f>VLOOKUP(A:A,MASTER!A:H,8,0)</f>
-        <v>4900000.0000000093</v>
+        <v>4958558.5585585674</v>
       </c>
       <c r="F7" s="5">
         <f>VLOOKUP(A:A,MASTER!A:I,9,0)</f>
-        <v>4013513.5135135092</v>
+        <v>4395045.0450450405</v>
       </c>
       <c r="G7" s="5">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>125583783.78378379</v>
+        <v>135590990.990991</v>
       </c>
       <c r="H7" s="5">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>176542522.52252254</v>
+        <v>182622702.7027027</v>
       </c>
       <c r="I7" s="5">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
-        <v>195797351.35135135</v>
+        <v>213654909.90990993</v>
       </c>
       <c r="J7" s="5">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>185211054.05405405</v>
+        <v>205806864.86486486</v>
       </c>
       <c r="K7" s="5">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>122320360.36036037</v>
+        <v>129198828.82882883</v>
       </c>
       <c r="L7" s="5">
         <f>VLOOKUP(A:A,MASTER!A:C,3,0)</f>
-        <v>161384324.32432431</v>
+        <v>169045045.04504505</v>
       </c>
       <c r="M7" s="12">
-        <v>14019</v>
+        <f>VLOOKUP(A:A,MASTER!A:L,12,0)</f>
+        <v>12612</v>
       </c>
       <c r="N7" s="12">
-        <v>13799</v>
+        <f>VLOOKUP(A:A,MASTER!A:M,13,0)</f>
+        <v>13681</v>
       </c>
     </row>
     <row r="8" spans="1:14" ht="64.5" customHeight="1" x14ac:dyDescent="0.35">
@@ -784,11 +811,11 @@
       </c>
       <c r="C8" s="5">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>68804127.337667182</v>
+        <v>74949918.7997915</v>
       </c>
       <c r="D8" s="5">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>67518859.38323462</v>
+        <v>74239058.1176157</v>
       </c>
       <c r="E8" s="5">
         <f>VLOOKUP(A:A,MASTER!A:H,8,0)</f>
@@ -796,7 +823,7 @@
       </c>
       <c r="F8" s="5">
         <f>VLOOKUP(A:A,MASTER!A:I,9,0)</f>
-        <v>37837.837837838</v>
+        <v>51351.351351350997</v>
       </c>
       <c r="G8" s="5">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
@@ -804,29 +831,31 @@
       </c>
       <c r="H8" s="5">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>19690990.990990993</v>
+        <v>19704504.504504506</v>
       </c>
       <c r="I8" s="5">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
-        <v>49546756.756756753</v>
+        <v>52957333.333333336</v>
       </c>
       <c r="J8" s="5">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>44390981.981981985</v>
+        <v>48921792.79279279</v>
       </c>
       <c r="K8" s="5">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>9568468.4684684686</v>
+        <v>9751981.9819819797</v>
       </c>
       <c r="L8" s="5">
         <f>VLOOKUP(A:A,MASTER!A:C,3,0)</f>
-        <v>20761801.801801801</v>
+        <v>20800090.090090089</v>
       </c>
       <c r="M8" s="12">
-        <v>4423</v>
+        <f>VLOOKUP(A:A,MASTER!A:L,12,0)</f>
+        <v>4652</v>
       </c>
       <c r="N8" s="12">
-        <v>4627</v>
+        <f>VLOOKUP(A:A,MASTER!A:M,13,0)</f>
+        <v>4553</v>
       </c>
     </row>
     <row r="9" spans="1:14" ht="64.5" customHeight="1" x14ac:dyDescent="0.35">
@@ -838,35 +867,35 @@
       </c>
       <c r="C9" s="5">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>75147468.387961403</v>
+        <v>82549625.094686285</v>
       </c>
       <c r="D9" s="5">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>79776886.755025342</v>
+        <v>87741942.073753685</v>
       </c>
       <c r="E9" s="5">
         <f>VLOOKUP(A:A,MASTER!A:H,8,0)</f>
-        <v>250713227.02702704</v>
+        <v>233986091.8918919</v>
       </c>
       <c r="F9" s="5">
         <f>VLOOKUP(A:A,MASTER!A:I,9,0)</f>
-        <v>203189164.86486486</v>
+        <v>149968010.8108108</v>
       </c>
       <c r="G9" s="5">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>786261.26126126095</v>
+        <v>0</v>
       </c>
       <c r="H9" s="5">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>88288.288288287993</v>
+        <v>0</v>
       </c>
       <c r="I9" s="5">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
-        <v>45267727.927927926</v>
+        <v>49186646.846846849</v>
       </c>
       <c r="J9" s="5">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>48507468.468468465</v>
+        <v>53389225.225225225</v>
       </c>
       <c r="K9" s="5">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
@@ -874,13 +903,15 @@
       </c>
       <c r="L9" s="5">
         <f>VLOOKUP(A:A,MASTER!A:C,3,0)</f>
-        <v>357117.11711711599</v>
+        <v>399009.009009008</v>
       </c>
       <c r="M9" s="12">
-        <v>3674</v>
+        <f>VLOOKUP(A:A,MASTER!A:L,12,0)</f>
+        <v>3580</v>
       </c>
       <c r="N9" s="12">
-        <v>3667</v>
+        <f>VLOOKUP(A:A,MASTER!A:M,13,0)</f>
+        <v>3768</v>
       </c>
     </row>
     <row r="10" spans="1:14" ht="64.5" customHeight="1" x14ac:dyDescent="0.35">
@@ -892,11 +923,11 @@
       </c>
       <c r="C10" s="5">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>64957111.005213201</v>
+        <v>71471417.771803141</v>
       </c>
       <c r="D10" s="5">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>63299657.685326733</v>
+        <v>69968552.695591569</v>
       </c>
       <c r="E10" s="5">
         <f>VLOOKUP(A:A,MASTER!A:H,8,0)</f>
@@ -916,25 +947,27 @@
       </c>
       <c r="I10" s="5">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
-        <v>22453972.97297297</v>
+        <v>24249099.0990991</v>
       </c>
       <c r="J10" s="5">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>26245450.45045045</v>
+        <v>29277342.342342343</v>
       </c>
       <c r="K10" s="5">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>1365315.315315316</v>
+        <v>1468468.4684684691</v>
       </c>
       <c r="L10" s="5">
         <f>VLOOKUP(A:A,MASTER!A:C,3,0)</f>
-        <v>1430810.8108108109</v>
+        <v>1465045.0450450459</v>
       </c>
       <c r="M10" s="12">
-        <v>3875</v>
+        <f>VLOOKUP(A:A,MASTER!A:L,12,0)</f>
+        <v>3923</v>
       </c>
       <c r="N10" s="12">
-        <v>4035</v>
+        <f>VLOOKUP(A:A,MASTER!A:M,13,0)</f>
+        <v>4320</v>
       </c>
     </row>
     <row r="11" spans="1:14" ht="64.5" customHeight="1" x14ac:dyDescent="0.35">
@@ -946,49 +979,51 @@
       </c>
       <c r="C11" s="5">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>41953519.313358799</v>
+        <v>46004800.459567517</v>
       </c>
       <c r="D11" s="5">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>43643150.56357944</v>
+        <v>48193473.258935727</v>
       </c>
       <c r="E11" s="5">
         <f>VLOOKUP(A:A,MASTER!A:H,8,0)</f>
-        <v>389189.18918919301</v>
+        <v>20322522.522522524</v>
       </c>
       <c r="F11" s="5">
         <f>VLOOKUP(A:A,MASTER!A:I,9,0)</f>
-        <v>100900.900900901</v>
+        <v>54569369.369369365</v>
       </c>
       <c r="G11" s="5">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>3542342.342342345</v>
+        <v>6317342.3423423441</v>
       </c>
       <c r="H11" s="5">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>551351.35135135101</v>
+        <v>668468.46846846805</v>
       </c>
       <c r="I11" s="5">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
-        <v>17375801.801801801</v>
+        <v>18725216.216216218</v>
       </c>
       <c r="J11" s="5">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>19426288.288288288</v>
+        <v>21205837.837837841</v>
       </c>
       <c r="K11" s="5">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>4952522.5225225231</v>
+        <v>5006306.3063063072</v>
       </c>
       <c r="L11" s="5">
         <f>VLOOKUP(A:A,MASTER!A:C,3,0)</f>
-        <v>1949549.5495495489</v>
+        <v>2107207.2072072071</v>
       </c>
       <c r="M11" s="12">
-        <v>2921</v>
+        <f>VLOOKUP(A:A,MASTER!A:L,12,0)</f>
+        <v>3761</v>
       </c>
       <c r="N11" s="12">
-        <v>3061</v>
+        <f>VLOOKUP(A:A,MASTER!A:M,13,0)</f>
+        <v>3023</v>
       </c>
     </row>
     <row r="12" spans="1:14" ht="64.5" customHeight="1" x14ac:dyDescent="0.35">
@@ -1000,49 +1035,51 @@
       </c>
       <c r="C12" s="5">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>167024012.88379335</v>
+        <v>183904896.18193716</v>
       </c>
       <c r="D12" s="5">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>175844154.47865763</v>
+        <v>192986083.8231118</v>
       </c>
       <c r="E12" s="5">
         <f>VLOOKUP(A:A,MASTER!A:H,8,0)</f>
-        <v>1124324.3243243259</v>
+        <v>1169369.369369373</v>
       </c>
       <c r="F12" s="5">
         <f>VLOOKUP(A:A,MASTER!A:I,9,0)</f>
-        <v>817117.11711711797</v>
+        <v>991891.89189189195</v>
       </c>
       <c r="G12" s="5">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>22881531.531531531</v>
+        <v>23693963.963963963</v>
       </c>
       <c r="H12" s="5">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>22989414.414414417</v>
+        <v>25470495.495495494</v>
       </c>
       <c r="I12" s="5">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
-        <v>80831972.972972974</v>
+        <v>88503036.036036029</v>
       </c>
       <c r="J12" s="5">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>81628792.792792797</v>
+        <v>90365315.315315306</v>
       </c>
       <c r="K12" s="5">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>20012882.882882878</v>
+        <v>21230630.630630627</v>
       </c>
       <c r="L12" s="5">
         <f>VLOOKUP(A:A,MASTER!A:C,3,0)</f>
-        <v>22198333.333333336</v>
+        <v>24296351.351351351</v>
       </c>
       <c r="M12" s="12">
-        <v>8054</v>
+        <f>VLOOKUP(A:A,MASTER!A:L,12,0)</f>
+        <v>7988</v>
       </c>
       <c r="N12" s="12">
-        <v>7964</v>
+        <f>VLOOKUP(A:A,MASTER!A:M,13,0)</f>
+        <v>7928</v>
       </c>
     </row>
     <row r="13" spans="1:14" ht="64.5" customHeight="1" x14ac:dyDescent="0.35">
@@ -1054,49 +1091,51 @@
       </c>
       <c r="C13" s="5">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>124479909.43520992</v>
+        <v>138307206.11321077</v>
       </c>
       <c r="D13" s="5">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>111464263.10669373</v>
+        <v>123312636.9197247</v>
       </c>
       <c r="E13" s="5">
         <f>VLOOKUP(A:A,MASTER!A:H,8,0)</f>
-        <v>1681081.081081083</v>
+        <v>2074774.774774777</v>
       </c>
       <c r="F13" s="5">
         <f>VLOOKUP(A:A,MASTER!A:I,9,0)</f>
-        <v>578828.82882882899</v>
+        <v>736486.48648648697</v>
       </c>
       <c r="G13" s="5">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>19211711.711711712</v>
+        <v>21102702.702702705</v>
       </c>
       <c r="H13" s="5">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>55008108.108108111</v>
+        <v>57778378.378378376</v>
       </c>
       <c r="I13" s="5">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
-        <v>35350648.648648649</v>
+        <v>39286729.729729727</v>
       </c>
       <c r="J13" s="5">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>31949162.162162162</v>
+        <v>35456774.774774775</v>
       </c>
       <c r="K13" s="5">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>18814324.324324325</v>
+        <v>20983423.423423424</v>
       </c>
       <c r="L13" s="5">
         <f>VLOOKUP(A:A,MASTER!A:C,3,0)</f>
-        <v>50869549.54954955</v>
+        <v>55497477.477477483</v>
       </c>
       <c r="M13" s="12">
-        <v>3627</v>
+        <f>VLOOKUP(A:A,MASTER!A:L,12,0)</f>
+        <v>3555</v>
       </c>
       <c r="N13" s="12">
-        <v>3489</v>
+        <f>VLOOKUP(A:A,MASTER!A:M,13,0)</f>
+        <v>3341</v>
       </c>
     </row>
     <row r="14" spans="1:14" ht="64.5" customHeight="1" x14ac:dyDescent="0.35">
@@ -1108,49 +1147,51 @@
       </c>
       <c r="C14" s="5">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>77443561.495953918</v>
+        <v>84798306.063745201</v>
       </c>
       <c r="D14" s="5">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>73133788.445529953</v>
+        <v>80170332.138596565</v>
       </c>
       <c r="E14" s="5">
         <f>VLOOKUP(A:A,MASTER!A:H,8,0)</f>
-        <v>851351.35135135299</v>
+        <v>92810810.810810819</v>
       </c>
       <c r="F14" s="5">
         <f>VLOOKUP(A:A,MASTER!A:I,9,0)</f>
-        <v>703603.60360360402</v>
+        <v>26846846.846846849</v>
       </c>
       <c r="G14" s="5">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>19953153.153153151</v>
+        <v>34687387.387387387</v>
       </c>
       <c r="H14" s="5">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>28203603.603603605</v>
+        <v>49219369.369369365</v>
       </c>
       <c r="I14" s="5">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
-        <v>26811324.324324325</v>
+        <v>29075063.063063063</v>
       </c>
       <c r="J14" s="5">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>28138891.891891893</v>
+        <v>30874747.747747749</v>
       </c>
       <c r="K14" s="5">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>21801981.981981982</v>
+        <v>22406576.576576576</v>
       </c>
       <c r="L14" s="5">
         <f>VLOOKUP(A:A,MASTER!A:C,3,0)</f>
-        <v>21557027.02702703</v>
+        <v>27107297.297297295</v>
       </c>
       <c r="M14" s="12">
-        <v>3620</v>
+        <f>VLOOKUP(A:A,MASTER!A:L,12,0)</f>
+        <v>3611</v>
       </c>
       <c r="N14" s="12">
-        <v>3407</v>
+        <f>VLOOKUP(A:A,MASTER!A:M,13,0)</f>
+        <v>3458</v>
       </c>
     </row>
     <row r="15" spans="1:14" ht="64.5" customHeight="1" x14ac:dyDescent="0.35">
@@ -1162,49 +1203,51 @@
       </c>
       <c r="C15" s="5">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>83638677.803553104</v>
+        <v>91816940.607951462</v>
       </c>
       <c r="D15" s="5">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>83241276.547920391</v>
+        <v>91368737.558266193</v>
       </c>
       <c r="E15" s="5">
         <f>VLOOKUP(A:A,MASTER!A:H,8,0)</f>
-        <v>150450.45045045001</v>
+        <v>282350956.75675678</v>
       </c>
       <c r="F15" s="5">
         <f>VLOOKUP(A:A,MASTER!A:I,9,0)</f>
-        <v>13513.513513514001</v>
+        <v>329410634.23423421</v>
       </c>
       <c r="G15" s="5">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>6797297.2972972961</v>
+        <v>27727027.027027026</v>
       </c>
       <c r="H15" s="5">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>11175675.675675675</v>
+        <v>40603603.603603601</v>
       </c>
       <c r="I15" s="5">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
-        <v>34689288.288288288</v>
+        <v>37416090.090090089</v>
       </c>
       <c r="J15" s="5">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>34429891.891891889</v>
+        <v>38265747.747747742</v>
       </c>
       <c r="K15" s="5">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>5917567.5675675683</v>
+        <v>7046846.8468468469</v>
       </c>
       <c r="L15" s="5">
         <f>VLOOKUP(A:A,MASTER!A:C,3,0)</f>
-        <v>9870000</v>
+        <v>10431711.711711714</v>
       </c>
       <c r="M15" s="12">
-        <v>3016</v>
+        <f>VLOOKUP(A:A,MASTER!A:L,12,0)</f>
+        <v>3025</v>
       </c>
       <c r="N15" s="12">
-        <v>2926</v>
+        <f>VLOOKUP(A:A,MASTER!A:M,13,0)</f>
+        <v>2849</v>
       </c>
     </row>
     <row r="16" spans="1:14" ht="64.5" customHeight="1" x14ac:dyDescent="0.35">
@@ -1216,49 +1259,51 @@
       </c>
       <c r="C16" s="5">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>92677006.923511267</v>
+        <v>102240113.32315846</v>
       </c>
       <c r="D16" s="5">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>99911377.220618293</v>
+        <v>110255442.7059771</v>
       </c>
       <c r="E16" s="5">
         <f>VLOOKUP(A:A,MASTER!A:H,8,0)</f>
-        <v>1301801.801801804</v>
+        <v>1369369.3693693711</v>
       </c>
       <c r="F16" s="5">
         <f>VLOOKUP(A:A,MASTER!A:I,9,0)</f>
-        <v>1115315.315315316</v>
+        <v>1220720.72072072</v>
       </c>
       <c r="G16" s="5">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>12918918.918918921</v>
+        <v>12986486.486486487</v>
       </c>
       <c r="H16" s="5">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>19396396.396396399</v>
+        <v>23015315.315315321</v>
       </c>
       <c r="I16" s="5">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
-        <v>27309549.54954955</v>
+        <v>29770711.711711712</v>
       </c>
       <c r="J16" s="5">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>30287387.387387387</v>
+        <v>32746891.891891893</v>
       </c>
       <c r="K16" s="5">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>12188738.738738736</v>
+        <v>12479819.819819819</v>
       </c>
       <c r="L16" s="5">
         <f>VLOOKUP(A:A,MASTER!A:C,3,0)</f>
-        <v>18979459.459459461</v>
+        <v>21886666.666666668</v>
       </c>
       <c r="M16" s="12">
-        <v>6018</v>
+        <f>VLOOKUP(A:A,MASTER!A:L,12,0)</f>
+        <v>3696</v>
       </c>
       <c r="N16" s="12">
-        <v>3449</v>
+        <f>VLOOKUP(A:A,MASTER!A:M,13,0)</f>
+        <v>3783</v>
       </c>
     </row>
     <row r="17" spans="1:14" ht="64.5" customHeight="1" x14ac:dyDescent="0.35">
@@ -1270,49 +1315,51 @@
       </c>
       <c r="C17" s="5">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>184208203.93830642</v>
+        <v>203526950.74839038</v>
       </c>
       <c r="D17" s="5">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>178909452.82663804</v>
+        <v>195955976.21289811</v>
       </c>
       <c r="E17" s="5">
         <f>VLOOKUP(A:A,MASTER!A:H,8,0)</f>
-        <v>1532432.4324324371</v>
+        <v>1590090.0900900939</v>
       </c>
       <c r="F17" s="5">
         <f>VLOOKUP(A:A,MASTER!A:I,9,0)</f>
-        <v>894144.14414414496</v>
+        <v>1042792.792792793</v>
       </c>
       <c r="G17" s="5">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>197469369.36936939</v>
+        <v>223312612.61261261</v>
       </c>
       <c r="H17" s="5">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>264517477.47747746</v>
+        <v>314359819.81981987</v>
       </c>
       <c r="I17" s="5">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
-        <v>68568540.540540546</v>
+        <v>74621135.135135129</v>
       </c>
       <c r="J17" s="5">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>64665108.108108103</v>
+        <v>71049333.333333343</v>
       </c>
       <c r="K17" s="5">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>184796486.48648649</v>
+        <v>206395945.94594595</v>
       </c>
       <c r="L17" s="5">
         <f>VLOOKUP(A:A,MASTER!A:C,3,0)</f>
-        <v>240402882.88288289</v>
+        <v>261121711.7117117</v>
       </c>
       <c r="M17" s="12">
-        <v>7259</v>
+        <f>VLOOKUP(A:A,MASTER!A:L,12,0)</f>
+        <v>7017</v>
       </c>
       <c r="N17" s="12">
-        <v>7191</v>
+        <f>VLOOKUP(A:A,MASTER!A:M,13,0)</f>
+        <v>6930</v>
       </c>
     </row>
     <row r="18" spans="1:14" ht="64.5" customHeight="1" x14ac:dyDescent="0.35">
@@ -1324,49 +1371,51 @@
       </c>
       <c r="C18" s="5">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>151110852.08540854</v>
+        <v>166406375.15526605</v>
       </c>
       <c r="D18" s="5">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>146960764.92853495</v>
+        <v>161782311.04450738</v>
       </c>
       <c r="E18" s="5">
         <f>VLOOKUP(A:A,MASTER!A:H,8,0)</f>
-        <v>912612.61261261499</v>
+        <v>970270.27027027204</v>
       </c>
       <c r="F18" s="5">
         <f>VLOOKUP(A:A,MASTER!A:I,9,0)</f>
-        <v>189189.18918918999</v>
+        <v>492342.342342344</v>
       </c>
       <c r="G18" s="5">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>37331621.621621616</v>
+        <v>41250900.900900893</v>
       </c>
       <c r="H18" s="5">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>35474774.774774775</v>
+        <v>42441441.441441439</v>
       </c>
       <c r="I18" s="5">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
-        <v>87426378.378378391</v>
+        <v>94641486.48648648</v>
       </c>
       <c r="J18" s="5">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>83530387.387387395</v>
+        <v>93214702.702702701</v>
       </c>
       <c r="K18" s="5">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>38159639.639639638</v>
+        <v>40399459.459459454</v>
       </c>
       <c r="L18" s="5">
         <f>VLOOKUP(A:A,MASTER!A:C,3,0)</f>
-        <v>35027297.297297299</v>
+        <v>45909549.54954955</v>
       </c>
       <c r="M18" s="12">
-        <v>7031</v>
+        <f>VLOOKUP(A:A,MASTER!A:L,12,0)</f>
+        <v>7095</v>
       </c>
       <c r="N18" s="12">
-        <v>6924</v>
+        <f>VLOOKUP(A:A,MASTER!A:M,13,0)</f>
+        <v>7045</v>
       </c>
     </row>
     <row r="19" spans="1:14" ht="64.5" customHeight="1" x14ac:dyDescent="0.35">
@@ -1378,11 +1427,11 @@
       </c>
       <c r="C19" s="5">
         <f>VLOOKUP(A:A,MASTER!A:J,10,0)</f>
-        <v>78813022.56256333</v>
+        <v>86467136.84016487</v>
       </c>
       <c r="D19" s="5">
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
-        <v>86101440.05152458</v>
+        <v>94474395.245280206</v>
       </c>
       <c r="E19" s="5">
         <f>VLOOKUP(A:A,MASTER!A:H,8,0)</f>
@@ -1390,37 +1439,39 @@
       </c>
       <c r="F19" s="5">
         <f>VLOOKUP(A:A,MASTER!A:I,9,0)</f>
-        <v>124324.324324325</v>
+        <v>132432.43243243301</v>
       </c>
       <c r="G19" s="5">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
-        <v>22243243.243243244</v>
+        <v>25846846.846846849</v>
       </c>
       <c r="H19" s="5">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
-        <v>16811261.261261258</v>
+        <v>17729279.27927928</v>
       </c>
       <c r="I19" s="5">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
-        <v>27161783.783783782</v>
+        <v>29553990.990990993</v>
       </c>
       <c r="J19" s="5">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
-        <v>29936234.234234232</v>
+        <v>33205108.108108107</v>
       </c>
       <c r="K19" s="5">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
-        <v>27517477.47747748</v>
+        <v>28104504.504504506</v>
       </c>
       <c r="L19" s="5">
         <f>VLOOKUP(A:A,MASTER!A:C,3,0)</f>
-        <v>15241801.801801801</v>
+        <v>16053873.873873873</v>
       </c>
       <c r="M19" s="12">
-        <v>3941</v>
+        <f>VLOOKUP(A:A,MASTER!A:L,12,0)</f>
+        <v>4080</v>
       </c>
       <c r="N19" s="12">
-        <v>4169</v>
+        <f>VLOOKUP(A:A,MASTER!A:M,13,0)</f>
+        <v>4058</v>
       </c>
     </row>
   </sheetData>
@@ -1431,7 +1482,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A2:K17"/>
+  <dimension ref="A1:M17"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="36.90625" bestFit="1" customWidth="1"/>
@@ -1447,7 +1498,15 @@
     <col min="11" max="11" width="19.453125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="L1" s="14" t="s">
+        <v>42</v>
+      </c>
+      <c r="M1" s="14" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="2" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A2" s="8" t="s">
         <v>28</v>
       </c>
@@ -1481,43 +1540,55 @@
       <c r="K2" s="8" t="s">
         <v>39</v>
       </c>
-    </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="L2" s="15" t="s">
+        <v>43</v>
+      </c>
+      <c r="M2" s="15" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A3" s="9" t="s">
         <v>1</v>
       </c>
       <c r="B3">
-        <v>20012882.882882878</v>
+        <v>21230630.630630627</v>
       </c>
       <c r="C3">
-        <v>22198333.333333336</v>
+        <v>24296351.351351351</v>
       </c>
       <c r="D3">
-        <v>80831972.972972974</v>
+        <v>88503036.036036029</v>
       </c>
       <c r="E3">
-        <v>81628792.792792797</v>
+        <v>90365315.315315306</v>
       </c>
       <c r="F3">
-        <v>22881531.531531531</v>
+        <v>23693963.963963963</v>
       </c>
       <c r="G3">
-        <v>22989414.414414417</v>
-      </c>
-      <c r="H3">
-        <v>1124324.3243243259</v>
-      </c>
-      <c r="I3">
-        <v>817117.11711711797</v>
+        <v>25470495.495495494</v>
+      </c>
+      <c r="H3" s="13">
+        <v>1169369.369369373</v>
+      </c>
+      <c r="I3" s="13">
+        <v>991891.89189189195</v>
       </c>
       <c r="J3">
-        <v>167024012.88379335</v>
+        <v>183904896.18193716</v>
       </c>
       <c r="K3">
-        <v>175844154.47865763</v>
-      </c>
-    </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.35">
+        <v>192986083.8231118</v>
+      </c>
+      <c r="L3">
+        <v>7988</v>
+      </c>
+      <c r="M3">
+        <v>7928</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A4" s="9" t="s">
         <v>2</v>
       </c>
@@ -1528,7 +1599,7 @@
         <v>203603.60360360399</v>
       </c>
       <c r="D4">
-        <v>7065675.6756756762</v>
+        <v>8455585.5855855867</v>
       </c>
       <c r="E4">
         <v>4115666.666666667</v>
@@ -1539,265 +1610,313 @@
       <c r="G4">
         <v>180180.18018018</v>
       </c>
-      <c r="H4">
+      <c r="H4" s="13">
         <v>40540.540540542002</v>
       </c>
-      <c r="I4">
+      <c r="I4" s="13">
         <v>90090.090090090001</v>
       </c>
       <c r="J4">
-        <v>11435885.059074299</v>
+        <v>13395326.593805984</v>
       </c>
       <c r="K4">
-        <v>7512201.2733524209</v>
-      </c>
-    </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.35">
+        <v>7512211.1851744372</v>
+      </c>
+      <c r="L4">
+        <v>1622</v>
+      </c>
+      <c r="M4">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A5" s="9" t="s">
         <v>3</v>
       </c>
       <c r="B5">
-        <v>18814324.324324325</v>
+        <v>20983423.423423424</v>
       </c>
       <c r="C5">
-        <v>50869549.54954955</v>
+        <v>55497477.477477483</v>
       </c>
       <c r="D5">
-        <v>35350648.648648649</v>
+        <v>39286729.729729727</v>
       </c>
       <c r="E5">
-        <v>31949162.162162162</v>
+        <v>35456774.774774775</v>
       </c>
       <c r="F5">
-        <v>19211711.711711712</v>
+        <v>21102702.702702705</v>
       </c>
       <c r="G5">
-        <v>55008108.108108111</v>
-      </c>
-      <c r="H5">
-        <v>1681081.081081083</v>
-      </c>
-      <c r="I5">
-        <v>578828.82882882899</v>
+        <v>57778378.378378376</v>
+      </c>
+      <c r="H5" s="13">
+        <v>2074774.774774777</v>
+      </c>
+      <c r="I5" s="13">
+        <v>736486.48648648697</v>
       </c>
       <c r="J5">
-        <v>124479909.43520992</v>
+        <v>138307206.11321077</v>
       </c>
       <c r="K5">
-        <v>111464263.10669373</v>
-      </c>
-    </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.35">
+        <v>123312636.9197247</v>
+      </c>
+      <c r="L5">
+        <v>3555</v>
+      </c>
+      <c r="M5">
+        <v>3341</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A6" s="9" t="s">
         <v>4</v>
       </c>
       <c r="B6">
-        <v>21801981.981981982</v>
+        <v>22406576.576576576</v>
       </c>
       <c r="C6">
-        <v>21557027.02702703</v>
+        <v>27107297.297297295</v>
       </c>
       <c r="D6">
-        <v>26811324.324324325</v>
+        <v>29075063.063063063</v>
       </c>
       <c r="E6">
-        <v>28138891.891891893</v>
+        <v>30874747.747747749</v>
       </c>
       <c r="F6">
-        <v>19953153.153153151</v>
+        <v>34687387.387387387</v>
       </c>
       <c r="G6">
-        <v>28203603.603603605</v>
-      </c>
-      <c r="H6">
-        <v>851351.35135135299</v>
-      </c>
-      <c r="I6">
-        <v>703603.60360360402</v>
+        <v>49219369.369369365</v>
+      </c>
+      <c r="H6" s="13">
+        <v>92810810.810810819</v>
+      </c>
+      <c r="I6" s="13">
+        <v>26846846.846846849</v>
       </c>
       <c r="J6">
-        <v>77443561.495953918</v>
+        <v>84798306.063745201</v>
       </c>
       <c r="K6">
-        <v>73133788.445529953</v>
-      </c>
-    </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.35">
+        <v>80170332.138596565</v>
+      </c>
+      <c r="L6">
+        <v>3611</v>
+      </c>
+      <c r="M6">
+        <v>3458</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A7" s="9" t="s">
         <v>5</v>
       </c>
       <c r="B7">
-        <v>5917567.5675675683</v>
+        <v>7046846.8468468469</v>
       </c>
       <c r="C7">
-        <v>9870000</v>
+        <v>10431711.711711714</v>
       </c>
       <c r="D7">
-        <v>34689288.288288288</v>
+        <v>37416090.090090089</v>
       </c>
       <c r="E7">
-        <v>34429891.891891889</v>
+        <v>38265747.747747742</v>
       </c>
       <c r="F7">
-        <v>6797297.2972972961</v>
+        <v>27727027.027027026</v>
       </c>
       <c r="G7">
-        <v>11175675.675675675</v>
-      </c>
-      <c r="H7">
-        <v>150450.45045045001</v>
-      </c>
-      <c r="I7">
-        <v>13513.513513514001</v>
+        <v>40603603.603603601</v>
+      </c>
+      <c r="H7" s="13">
+        <v>282350956.75675678</v>
+      </c>
+      <c r="I7" s="13">
+        <v>329410634.23423421</v>
       </c>
       <c r="J7">
-        <v>83638677.803553104</v>
+        <v>91816940.607951462</v>
       </c>
       <c r="K7">
-        <v>83241276.547920391</v>
-      </c>
-    </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.35">
+        <v>91368737.558266193</v>
+      </c>
+      <c r="L7">
+        <v>3025</v>
+      </c>
+      <c r="M7">
+        <v>2849</v>
+      </c>
+    </row>
+    <row r="8" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A8" s="9" t="s">
         <v>6</v>
       </c>
       <c r="B8">
-        <v>122320360.36036037</v>
+        <v>129198828.82882883</v>
       </c>
       <c r="C8">
-        <v>161384324.32432431</v>
+        <v>169045045.04504505</v>
       </c>
       <c r="D8">
-        <v>195797351.35135135</v>
+        <v>213654909.90990993</v>
       </c>
       <c r="E8">
-        <v>185211054.05405405</v>
+        <v>205806864.86486486</v>
       </c>
       <c r="F8">
-        <v>125583783.78378379</v>
+        <v>135590990.990991</v>
       </c>
       <c r="G8">
-        <v>176542522.52252254</v>
-      </c>
-      <c r="H8">
-        <v>4900000.0000000093</v>
-      </c>
-      <c r="I8">
-        <v>4013513.5135135092</v>
+        <v>182622702.7027027</v>
+      </c>
+      <c r="H8" s="13">
+        <v>4958558.5585585674</v>
+      </c>
+      <c r="I8" s="13">
+        <v>4395045.0450450405</v>
       </c>
       <c r="J8">
-        <v>277758523.3629142</v>
+        <v>306453254.68844277</v>
       </c>
       <c r="K8">
-        <v>286604689.71433705</v>
-      </c>
-    </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.35">
+        <v>316576001.14128393</v>
+      </c>
+      <c r="L8">
+        <v>12612</v>
+      </c>
+      <c r="M8">
+        <v>13681</v>
+      </c>
+    </row>
+    <row r="9" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A9" s="9" t="s">
         <v>7</v>
       </c>
       <c r="B9">
-        <v>9568468.4684684686</v>
+        <v>9751981.9819819797</v>
       </c>
       <c r="C9">
-        <v>20761801.801801801</v>
+        <v>20800090.090090089</v>
       </c>
       <c r="D9">
-        <v>49546756.756756753</v>
+        <v>52957333.333333336</v>
       </c>
       <c r="E9">
-        <v>44390981.981981985</v>
+        <v>48921792.79279279</v>
       </c>
       <c r="F9">
         <v>7053153.1531531513</v>
       </c>
       <c r="G9">
-        <v>19690990.990990993</v>
-      </c>
-      <c r="H9">
+        <v>19704504.504504506</v>
+      </c>
+      <c r="H9" s="13">
         <v>192792.792792794</v>
       </c>
-      <c r="I9">
-        <v>37837.837837838</v>
+      <c r="I9" s="13">
+        <v>51351.351351350997</v>
       </c>
       <c r="J9">
-        <v>68804127.337667182</v>
+        <v>74949918.7997915</v>
       </c>
       <c r="K9">
-        <v>67518859.38323462</v>
-      </c>
-    </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.35">
+        <v>74239058.1176157</v>
+      </c>
+      <c r="L9">
+        <v>4652</v>
+      </c>
+      <c r="M9">
+        <v>4553</v>
+      </c>
+    </row>
+    <row r="10" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A10" s="9" t="s">
         <v>8</v>
       </c>
       <c r="B10">
-        <v>12188738.738738736</v>
+        <v>12479819.819819819</v>
       </c>
       <c r="C10">
-        <v>18979459.459459461</v>
+        <v>21886666.666666668</v>
       </c>
       <c r="D10">
-        <v>27309549.54954955</v>
+        <v>29770711.711711712</v>
       </c>
       <c r="E10">
-        <v>30287387.387387387</v>
+        <v>32746891.891891893</v>
       </c>
       <c r="F10">
-        <v>12918918.918918921</v>
+        <v>12986486.486486487</v>
       </c>
       <c r="G10">
-        <v>19396396.396396399</v>
-      </c>
-      <c r="H10">
-        <v>1301801.801801804</v>
-      </c>
-      <c r="I10">
-        <v>1115315.315315316</v>
+        <v>23015315.315315321</v>
+      </c>
+      <c r="H10" s="13">
+        <v>1369369.3693693711</v>
+      </c>
+      <c r="I10" s="13">
+        <v>1220720.72072072</v>
       </c>
       <c r="J10">
-        <v>92677006.923511267</v>
+        <v>102240113.32315846</v>
       </c>
       <c r="K10">
-        <v>99911377.220618293</v>
-      </c>
-    </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.35">
+        <v>110255442.7059771</v>
+      </c>
+      <c r="L10">
+        <v>3696</v>
+      </c>
+      <c r="M10">
+        <v>3783</v>
+      </c>
+    </row>
+    <row r="11" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A11" s="9" t="s">
         <v>9</v>
       </c>
       <c r="B11">
-        <v>184796486.48648649</v>
+        <v>206395945.94594595</v>
       </c>
       <c r="C11">
-        <v>240402882.88288289</v>
+        <v>261121711.7117117</v>
       </c>
       <c r="D11">
-        <v>68568540.540540546</v>
+        <v>74621135.135135129</v>
       </c>
       <c r="E11">
-        <v>64665108.108108103</v>
+        <v>71049333.333333343</v>
       </c>
       <c r="F11">
-        <v>197469369.36936939</v>
+        <v>223312612.61261261</v>
       </c>
       <c r="G11">
-        <v>264517477.47747746</v>
-      </c>
-      <c r="H11">
-        <v>1532432.4324324371</v>
-      </c>
-      <c r="I11">
-        <v>894144.14414414496</v>
+        <v>314359819.81981987</v>
+      </c>
+      <c r="H11" s="13">
+        <v>1590090.0900900939</v>
+      </c>
+      <c r="I11" s="13">
+        <v>1042792.792792793</v>
       </c>
       <c r="J11">
-        <v>184208203.93830642</v>
+        <v>203526950.74839038</v>
       </c>
       <c r="K11">
-        <v>178909452.82663804</v>
-      </c>
-    </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.35">
+        <v>195955976.21289811</v>
+      </c>
+      <c r="L11">
+        <v>7017</v>
+      </c>
+      <c r="M11">
+        <v>6930</v>
+      </c>
+    </row>
+    <row r="12" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A12" s="9" t="s">
         <v>10</v>
       </c>
@@ -1805,48 +1924,48 @@
         <v>11081.081081081</v>
       </c>
       <c r="C12">
-        <v>357117.11711711599</v>
+        <v>399009.009009008</v>
       </c>
       <c r="D12">
-        <v>45267727.927927926</v>
+        <v>49186646.846846849</v>
       </c>
       <c r="E12">
-        <v>48507468.468468465</v>
-      </c>
-      <c r="F12">
-        <v>786261.26126126095</v>
-      </c>
-      <c r="G12">
-        <v>88288.288288287993</v>
-      </c>
-      <c r="H12">
-        <v>250713227.02702704</v>
-      </c>
-      <c r="I12">
-        <v>203189164.86486486</v>
+        <v>53389225.225225225</v>
+      </c>
+      <c r="H12" s="13">
+        <v>233986091.8918919</v>
+      </c>
+      <c r="I12" s="13">
+        <v>149968010.8108108</v>
       </c>
       <c r="J12">
-        <v>75147468.387961403</v>
+        <v>82549625.094686285</v>
       </c>
       <c r="K12">
-        <v>79776886.755025342</v>
-      </c>
-    </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.35">
+        <v>87741942.073753685</v>
+      </c>
+      <c r="L12">
+        <v>3580</v>
+      </c>
+      <c r="M12">
+        <v>3768</v>
+      </c>
+    </row>
+    <row r="13" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A13" s="9" t="s">
         <v>11</v>
       </c>
       <c r="B13">
-        <v>1365315.315315316</v>
+        <v>1468468.4684684691</v>
       </c>
       <c r="C13">
-        <v>1430810.8108108109</v>
+        <v>1465045.0450450459</v>
       </c>
       <c r="D13">
-        <v>22453972.97297297</v>
+        <v>24249099.0990991</v>
       </c>
       <c r="E13">
-        <v>26245450.45045045</v>
+        <v>29277342.342342343</v>
       </c>
       <c r="F13">
         <v>1914414.4144144161</v>
@@ -1854,167 +1973,199 @@
       <c r="G13">
         <v>2450450.4504504511</v>
       </c>
-      <c r="H13">
+      <c r="H13" s="13">
         <v>112612.612612615</v>
       </c>
-      <c r="I13">
+      <c r="I13" s="13">
         <v>18018.018018018</v>
       </c>
       <c r="J13">
-        <v>64957111.005213201</v>
+        <v>71471417.771803141</v>
       </c>
       <c r="K13">
-        <v>63299657.685326733</v>
-      </c>
-    </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.35">
+        <v>69968552.695591569</v>
+      </c>
+      <c r="L13">
+        <v>3923</v>
+      </c>
+      <c r="M13">
+        <v>4320</v>
+      </c>
+    </row>
+    <row r="14" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A14" s="9" t="s">
         <v>12</v>
       </c>
       <c r="B14">
-        <v>4952522.5225225231</v>
+        <v>5006306.3063063072</v>
       </c>
       <c r="C14">
-        <v>1949549.5495495489</v>
+        <v>2107207.2072072071</v>
       </c>
       <c r="D14">
-        <v>17375801.801801801</v>
+        <v>18725216.216216218</v>
       </c>
       <c r="E14">
-        <v>19426288.288288288</v>
+        <v>21205837.837837841</v>
       </c>
       <c r="F14">
-        <v>3542342.342342345</v>
+        <v>6317342.3423423441</v>
       </c>
       <c r="G14">
-        <v>551351.35135135101</v>
-      </c>
-      <c r="H14">
-        <v>389189.18918919301</v>
-      </c>
-      <c r="I14">
-        <v>100900.900900901</v>
+        <v>668468.46846846805</v>
+      </c>
+      <c r="H14" s="13">
+        <v>20322522.522522524</v>
+      </c>
+      <c r="I14" s="13">
+        <v>54569369.369369365</v>
       </c>
       <c r="J14">
-        <v>41953519.313358799</v>
+        <v>46004800.459567517</v>
       </c>
       <c r="K14">
-        <v>43643150.56357944</v>
-      </c>
-    </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.35">
+        <v>48193473.258935727</v>
+      </c>
+      <c r="L14">
+        <v>3761</v>
+      </c>
+      <c r="M14">
+        <v>3023</v>
+      </c>
+    </row>
+    <row r="15" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A15" s="9" t="s">
         <v>13</v>
       </c>
       <c r="B15">
-        <v>38159639.639639638</v>
+        <v>40399459.459459454</v>
       </c>
       <c r="C15">
-        <v>35027297.297297299</v>
+        <v>45909549.54954955</v>
       </c>
       <c r="D15">
-        <v>87426378.378378391</v>
+        <v>94641486.48648648</v>
       </c>
       <c r="E15">
-        <v>83530387.387387395</v>
+        <v>93214702.702702701</v>
       </c>
       <c r="F15">
-        <v>37331621.621621616</v>
+        <v>41250900.900900893</v>
       </c>
       <c r="G15">
-        <v>35474774.774774775</v>
-      </c>
-      <c r="H15">
-        <v>912612.61261261499</v>
-      </c>
-      <c r="I15">
-        <v>189189.18918918999</v>
+        <v>42441441.441441439</v>
+      </c>
+      <c r="H15" s="13">
+        <v>970270.27027027204</v>
+      </c>
+      <c r="I15" s="13">
+        <v>492342.342342344</v>
       </c>
       <c r="J15">
-        <v>151110852.08540854</v>
+        <v>166406375.15526605</v>
       </c>
       <c r="K15">
-        <v>146960764.92853495</v>
-      </c>
-    </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.35">
+        <v>161782311.04450738</v>
+      </c>
+      <c r="L15">
+        <v>7095</v>
+      </c>
+      <c r="M15">
+        <v>7045</v>
+      </c>
+    </row>
+    <row r="16" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A16" s="9" t="s">
         <v>14</v>
       </c>
       <c r="B16">
-        <v>27517477.47747748</v>
+        <v>28104504.504504506</v>
       </c>
       <c r="C16">
-        <v>15241801.801801801</v>
+        <v>16053873.873873873</v>
       </c>
       <c r="D16">
-        <v>27161783.783783782</v>
+        <v>29553990.990990993</v>
       </c>
       <c r="E16">
-        <v>29936234.234234232</v>
+        <v>33205108.108108107</v>
       </c>
       <c r="F16">
-        <v>22243243.243243244</v>
+        <v>25846846.846846849</v>
       </c>
       <c r="G16">
-        <v>16811261.261261258</v>
-      </c>
-      <c r="H16">
+        <v>17729279.27927928</v>
+      </c>
+      <c r="H16" s="13">
         <v>669369.36936937098</v>
       </c>
-      <c r="I16">
-        <v>124324.324324325</v>
+      <c r="I16" s="13">
+        <v>132432.43243243301</v>
       </c>
       <c r="J16">
-        <v>78813022.56256333</v>
+        <v>86467136.84016487</v>
       </c>
       <c r="K16">
-        <v>86101440.05152458</v>
-      </c>
-    </row>
-    <row r="17" spans="1:11" x14ac:dyDescent="0.35">
+        <v>94474395.245280206</v>
+      </c>
+      <c r="L16">
+        <v>4080</v>
+      </c>
+      <c r="M16">
+        <v>4058</v>
+      </c>
+    </row>
+    <row r="17" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A17" s="10" t="s">
         <v>34</v>
       </c>
       <c r="B17" s="11">
         <f>SUM(B3:B16)</f>
-        <v>467584504.5045045</v>
+        <v>504641531.53153151</v>
       </c>
       <c r="C17" s="11">
-        <f t="shared" ref="C17:K17" si="0">SUM(C3:C16)</f>
-        <v>600233558.55855858</v>
+        <f t="shared" ref="C17:M17" si="0">SUM(C3:C16)</f>
+        <v>656324639.63963962</v>
       </c>
       <c r="D17" s="11">
         <f t="shared" si="0"/>
-        <v>725656772.97297311</v>
+        <v>790097034.23423409</v>
       </c>
       <c r="E17" s="11">
         <f t="shared" si="0"/>
-        <v>712462765.76576567</v>
+        <v>787895351.35135138</v>
       </c>
       <c r="F17" s="11">
         <f t="shared" si="0"/>
-        <v>477727342.34234226</v>
+        <v>561524369.36936927</v>
       </c>
       <c r="G17" s="11">
         <f t="shared" si="0"/>
-        <v>653080495.49549544</v>
+        <v>776244009.00900888</v>
       </c>
       <c r="H17" s="11">
         <f t="shared" si="0"/>
-        <v>264571785.58558559</v>
+        <v>642618129.72972989</v>
       </c>
       <c r="I17" s="11">
         <f t="shared" si="0"/>
-        <v>211885561.26126125</v>
+        <v>569966032.43243241</v>
       </c>
       <c r="J17" s="11">
         <f t="shared" si="0"/>
-        <v>1499451881.5944889</v>
+        <v>1652292268.4419215</v>
       </c>
       <c r="K17" s="11">
         <f t="shared" si="0"/>
-        <v>1503921962.9809732</v>
+        <v>1654537154.120717</v>
+      </c>
+      <c r="L17" s="11">
+        <f t="shared" si="0"/>
+        <v>70217</v>
+      </c>
+      <c r="M17" s="11">
+        <f t="shared" si="0"/>
+        <v>68778</v>
       </c>
     </row>
   </sheetData>

--- a/MS BENGKAYANG 19 JULI 2026.xlsx
+++ b/MS BENGKAYANG 19 JULI 2026.xlsx
@@ -16,7 +16,7 @@
     <sheet name="MASTER" sheetId="2" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$5:$K$11</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$5:$O$11</definedName>
   </definedNames>
   <calcPr calcId="162913"/>
   <extLst>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="72" uniqueCount="45">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="78" uniqueCount="46">
   <si>
     <t>KECAMATAN</t>
   </si>
@@ -163,6 +163,9 @@
   </si>
   <si>
     <t>LMTD</t>
+  </si>
+  <si>
+    <t>GROWTH</t>
   </si>
 </sst>
 </file>
@@ -299,11 +302,12 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="2">
+  <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="43" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
@@ -342,12 +346,77 @@
       <alignment vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
+    <xf numFmtId="10" fontId="1" fillId="3" borderId="1" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="2">
+  <cellStyles count="3">
     <cellStyle name="Comma" xfId="1" builtinId="3"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Percent" xfId="2" builtinId="5"/>
   </cellStyles>
-  <dxfs count="0"/>
+  <dxfs count="6">
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -623,18 +692,19 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A4:N19"/>
+  <dimension ref="A4:T19"/>
   <sheetFormatPr defaultColWidth="11.7265625" defaultRowHeight="64.5" customHeight="1" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="60.6328125" style="2" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="29.54296875" style="6" bestFit="1" customWidth="1"/>
-    <col min="3" max="12" width="28.6328125" style="6" customWidth="1"/>
-    <col min="13" max="13" width="18" style="2" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="19.08984375" style="2" bestFit="1" customWidth="1"/>
-    <col min="15" max="16384" width="11.7265625" style="2"/>
+    <col min="3" max="17" width="28.6328125" style="6" customWidth="1"/>
+    <col min="18" max="18" width="18" style="2" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="19.08984375" style="2" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="12.453125" style="2" bestFit="1" customWidth="1"/>
+    <col min="21" max="16384" width="11.7265625" style="2"/>
   </cols>
   <sheetData>
-    <row r="4" spans="1:14" ht="64.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:20" ht="64.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C4" s="7"/>
       <c r="D4" s="7"/>
       <c r="E4" s="7"/>
@@ -645,8 +715,13 @@
       <c r="J4" s="7"/>
       <c r="K4" s="7"/>
       <c r="L4" s="7"/>
-    </row>
-    <row r="5" spans="1:14" ht="64.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="M4" s="7"/>
+      <c r="N4" s="7"/>
+      <c r="O4" s="7"/>
+      <c r="P4" s="7"/>
+      <c r="Q4" s="7"/>
+    </row>
+    <row r="5" spans="1:20" ht="64.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A5" s="3" t="s">
         <v>0</v>
       </c>
@@ -660,37 +735,55 @@
         <v>23</v>
       </c>
       <c r="E5" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="F5" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="F5" s="3" t="s">
+      <c r="G5" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="G5" s="3" t="s">
+      <c r="H5" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="I5" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="H5" s="3" t="s">
+      <c r="J5" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="I5" s="3" t="s">
+      <c r="K5" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="L5" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="J5" s="3" t="s">
+      <c r="M5" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="K5" s="3" t="s">
+      <c r="N5" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="O5" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="L5" s="3" t="s">
+      <c r="P5" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="M5" s="3" t="s">
+      <c r="Q5" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="R5" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="N5" s="3" t="s">
+      <c r="S5" s="3" t="s">
         <v>41</v>
       </c>
-    </row>
-    <row r="6" spans="1:14" ht="64.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="T5" s="3" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="6" spans="1:20" ht="64.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A6" s="4" t="s">
         <v>2</v>
       </c>
@@ -705,48 +798,72 @@
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
         <v>7512211.1851744372</v>
       </c>
-      <c r="E6" s="5">
+      <c r="E6" s="16">
+        <f>C6/D6-1</f>
+        <v>0.78314031163581266</v>
+      </c>
+      <c r="F6" s="5">
         <f>VLOOKUP(A:A,MASTER!A:H,8,0)</f>
         <v>40540.540540542002</v>
       </c>
-      <c r="F6" s="5">
+      <c r="G6" s="5">
         <f>VLOOKUP(A:A,MASTER!A:I,9,0)</f>
         <v>90090.090090090001</v>
       </c>
-      <c r="G6" s="5">
+      <c r="H6" s="16">
+        <f>F6/G6-1</f>
+        <v>-0.54999999999998339</v>
+      </c>
+      <c r="I6" s="5">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
         <v>40540.540540542002</v>
       </c>
-      <c r="H6" s="5">
+      <c r="J6" s="5">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
         <v>180180.18018018</v>
       </c>
-      <c r="I6" s="5">
+      <c r="K6" s="16">
+        <f>I6/J6-1</f>
+        <v>-0.7749999999999917</v>
+      </c>
+      <c r="L6" s="5">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
         <v>8455585.5855855867</v>
       </c>
-      <c r="J6" s="5">
+      <c r="M6" s="5">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
         <v>4115666.666666667</v>
       </c>
-      <c r="K6" s="5">
+      <c r="N6" s="16">
+        <f>L6/M6-1</f>
+        <v>1.0544874671383138</v>
+      </c>
+      <c r="O6" s="5">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
         <v>157657.65765765801</v>
       </c>
-      <c r="L6" s="5">
+      <c r="P6" s="5">
         <f>VLOOKUP(A:A,MASTER!A:C,3,0)</f>
         <v>203603.60360360399</v>
       </c>
-      <c r="M6" s="12">
+      <c r="Q6" s="16">
+        <f>O6/P6-1</f>
+        <v>-0.22566371681415898</v>
+      </c>
+      <c r="R6" s="12">
         <f>VLOOKUP(A:A,MASTER!A:L,12,0)</f>
         <v>1622</v>
       </c>
-      <c r="N6" s="12">
+      <c r="S6" s="12">
         <f>VLOOKUP(A:A,MASTER!A:M,13,0)</f>
         <v>41</v>
       </c>
-    </row>
-    <row r="7" spans="1:14" ht="64.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="T6" s="16">
+        <f>R6/S6-1</f>
+        <v>38.560975609756099</v>
+      </c>
+    </row>
+    <row r="7" spans="1:20" ht="64.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A7" s="4" t="s">
         <v>6</v>
       </c>
@@ -761,48 +878,72 @@
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
         <v>316576001.14128393</v>
       </c>
-      <c r="E7" s="5">
+      <c r="E7" s="16">
+        <f t="shared" ref="E7:E19" si="0">C7/D7-1</f>
+        <v>-3.1975722784885141E-2</v>
+      </c>
+      <c r="F7" s="5">
         <f>VLOOKUP(A:A,MASTER!A:H,8,0)</f>
         <v>4958558.5585585674</v>
       </c>
-      <c r="F7" s="5">
+      <c r="G7" s="5">
         <f>VLOOKUP(A:A,MASTER!A:I,9,0)</f>
         <v>4395045.0450450405</v>
       </c>
-      <c r="G7" s="5">
+      <c r="H7" s="16">
+        <f t="shared" ref="H7:H19" si="1">F7/G7-1</f>
+        <v>0.12821564005329833</v>
+      </c>
+      <c r="I7" s="5">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
         <v>135590990.990991</v>
       </c>
-      <c r="H7" s="5">
+      <c r="J7" s="5">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
         <v>182622702.7027027</v>
       </c>
-      <c r="I7" s="5">
+      <c r="K7" s="16">
+        <f t="shared" ref="K7:K19" si="2">I7/J7-1</f>
+        <v>-0.25753485747210803</v>
+      </c>
+      <c r="L7" s="5">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
         <v>213654909.90990993</v>
       </c>
-      <c r="J7" s="5">
+      <c r="M7" s="5">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
         <v>205806864.86486486</v>
       </c>
-      <c r="K7" s="5">
+      <c r="N7" s="16">
+        <f t="shared" ref="N7:N19" si="3">L7/M7-1</f>
+        <v>3.8133057661600356E-2</v>
+      </c>
+      <c r="O7" s="5">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
         <v>129198828.82882883</v>
       </c>
-      <c r="L7" s="5">
+      <c r="P7" s="5">
         <f>VLOOKUP(A:A,MASTER!A:C,3,0)</f>
         <v>169045045.04504505</v>
       </c>
-      <c r="M7" s="12">
+      <c r="Q7" s="16">
+        <f t="shared" ref="Q7:Q19" si="4">O7/P7-1</f>
+        <v>-0.23571360051161805</v>
+      </c>
+      <c r="R7" s="12">
         <f>VLOOKUP(A:A,MASTER!A:L,12,0)</f>
         <v>12612</v>
       </c>
-      <c r="N7" s="12">
+      <c r="S7" s="12">
         <f>VLOOKUP(A:A,MASTER!A:M,13,0)</f>
         <v>13681</v>
       </c>
-    </row>
-    <row r="8" spans="1:14" ht="64.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="T7" s="16">
+        <f t="shared" ref="T7:T19" si="5">R7/S7-1</f>
+        <v>-7.813756304363717E-2</v>
+      </c>
+    </row>
+    <row r="8" spans="1:20" ht="64.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A8" s="4" t="s">
         <v>7</v>
       </c>
@@ -817,48 +958,72 @@
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
         <v>74239058.1176157</v>
       </c>
-      <c r="E8" s="5">
+      <c r="E8" s="16">
+        <f t="shared" si="0"/>
+        <v>9.5752923083909369E-3</v>
+      </c>
+      <c r="F8" s="5">
         <f>VLOOKUP(A:A,MASTER!A:H,8,0)</f>
         <v>192792.792792794</v>
       </c>
-      <c r="F8" s="5">
+      <c r="G8" s="5">
         <f>VLOOKUP(A:A,MASTER!A:I,9,0)</f>
         <v>51351.351351350997</v>
       </c>
-      <c r="G8" s="5">
+      <c r="H8" s="16">
+        <f t="shared" si="1"/>
+        <v>2.7543859649123301</v>
+      </c>
+      <c r="I8" s="5">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
         <v>7053153.1531531513</v>
       </c>
-      <c r="H8" s="5">
+      <c r="J8" s="5">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
         <v>19704504.504504506</v>
       </c>
-      <c r="I8" s="5">
+      <c r="K8" s="16">
+        <f t="shared" si="2"/>
+        <v>-0.64205376737381137</v>
+      </c>
+      <c r="L8" s="5">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
         <v>52957333.333333336</v>
       </c>
-      <c r="J8" s="5">
+      <c r="M8" s="5">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
         <v>48921792.79279279</v>
       </c>
-      <c r="K8" s="5">
+      <c r="N8" s="16">
+        <f t="shared" si="3"/>
+        <v>8.2489629062307612E-2</v>
+      </c>
+      <c r="O8" s="5">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
         <v>9751981.9819819797</v>
       </c>
-      <c r="L8" s="5">
+      <c r="P8" s="5">
         <f>VLOOKUP(A:A,MASTER!A:C,3,0)</f>
         <v>20800090.090090089</v>
       </c>
-      <c r="M8" s="12">
+      <c r="Q8" s="16">
+        <f t="shared" si="4"/>
+        <v>-0.53115674308409966</v>
+      </c>
+      <c r="R8" s="12">
         <f>VLOOKUP(A:A,MASTER!A:L,12,0)</f>
         <v>4652</v>
       </c>
-      <c r="N8" s="12">
+      <c r="S8" s="12">
         <f>VLOOKUP(A:A,MASTER!A:M,13,0)</f>
         <v>4553</v>
       </c>
-    </row>
-    <row r="9" spans="1:14" ht="64.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="T8" s="16">
+        <f t="shared" si="5"/>
+        <v>2.1743905117505014E-2</v>
+      </c>
+    </row>
+    <row r="9" spans="1:20" ht="64.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A9" s="4" t="s">
         <v>10</v>
       </c>
@@ -873,48 +1038,72 @@
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
         <v>87741942.073753685</v>
       </c>
-      <c r="E9" s="5">
+      <c r="E9" s="16">
+        <f t="shared" si="0"/>
+        <v>-5.9177137596326146E-2</v>
+      </c>
+      <c r="F9" s="5">
         <f>VLOOKUP(A:A,MASTER!A:H,8,0)</f>
         <v>233986091.8918919</v>
       </c>
-      <c r="F9" s="5">
+      <c r="G9" s="5">
         <f>VLOOKUP(A:A,MASTER!A:I,9,0)</f>
         <v>149968010.8108108</v>
       </c>
-      <c r="G9" s="5">
+      <c r="H9" s="16">
+        <f t="shared" si="1"/>
+        <v>0.56024001803339551</v>
+      </c>
+      <c r="I9" s="5">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
         <v>0</v>
       </c>
-      <c r="H9" s="5">
+      <c r="J9" s="5">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
         <v>0</v>
       </c>
-      <c r="I9" s="5">
+      <c r="K9" s="16" t="e">
+        <f t="shared" si="2"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="L9" s="5">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
         <v>49186646.846846849</v>
       </c>
-      <c r="J9" s="5">
+      <c r="M9" s="5">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
         <v>53389225.225225225</v>
       </c>
-      <c r="K9" s="5">
+      <c r="N9" s="16">
+        <f t="shared" si="3"/>
+        <v>-7.8715852508621009E-2</v>
+      </c>
+      <c r="O9" s="5">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
         <v>11081.081081081</v>
       </c>
-      <c r="L9" s="5">
+      <c r="P9" s="5">
         <f>VLOOKUP(A:A,MASTER!A:C,3,0)</f>
         <v>399009.009009008</v>
       </c>
-      <c r="M9" s="12">
+      <c r="Q9" s="16">
+        <f t="shared" si="4"/>
+        <v>-0.97222849401670819</v>
+      </c>
+      <c r="R9" s="12">
         <f>VLOOKUP(A:A,MASTER!A:L,12,0)</f>
         <v>3580</v>
       </c>
-      <c r="N9" s="12">
+      <c r="S9" s="12">
         <f>VLOOKUP(A:A,MASTER!A:M,13,0)</f>
         <v>3768</v>
       </c>
-    </row>
-    <row r="10" spans="1:14" ht="64.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="T9" s="16">
+        <f t="shared" si="5"/>
+        <v>-4.989384288747345E-2</v>
+      </c>
+    </row>
+    <row r="10" spans="1:20" ht="64.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A10" s="4" t="s">
         <v>11</v>
       </c>
@@ -929,48 +1118,72 @@
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
         <v>69968552.695591569</v>
       </c>
-      <c r="E10" s="5">
+      <c r="E10" s="16">
+        <f t="shared" si="0"/>
+        <v>2.1479150537099256E-2</v>
+      </c>
+      <c r="F10" s="5">
         <f>VLOOKUP(A:A,MASTER!A:H,8,0)</f>
         <v>112612.612612615</v>
       </c>
-      <c r="F10" s="5">
+      <c r="G10" s="5">
         <f>VLOOKUP(A:A,MASTER!A:I,9,0)</f>
         <v>18018.018018018</v>
       </c>
-      <c r="G10" s="5">
+      <c r="H10" s="16">
+        <f t="shared" si="1"/>
+        <v>5.2500000000001394</v>
+      </c>
+      <c r="I10" s="5">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
         <v>1914414.4144144161</v>
       </c>
-      <c r="H10" s="5">
+      <c r="J10" s="5">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
         <v>2450450.4504504511</v>
       </c>
-      <c r="I10" s="5">
+      <c r="K10" s="16">
+        <f t="shared" si="2"/>
+        <v>-0.21874999999999956</v>
+      </c>
+      <c r="L10" s="5">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
         <v>24249099.0990991</v>
       </c>
-      <c r="J10" s="5">
+      <c r="M10" s="5">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
         <v>29277342.342342343</v>
       </c>
-      <c r="K10" s="5">
+      <c r="N10" s="16">
+        <f t="shared" si="3"/>
+        <v>-0.17174520775989799</v>
+      </c>
+      <c r="O10" s="5">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
         <v>1468468.4684684691</v>
       </c>
-      <c r="L10" s="5">
+      <c r="P10" s="5">
         <f>VLOOKUP(A:A,MASTER!A:C,3,0)</f>
         <v>1465045.0450450459</v>
       </c>
-      <c r="M10" s="12">
+      <c r="Q10" s="16">
+        <f t="shared" si="4"/>
+        <v>2.3367359488375428E-3</v>
+      </c>
+      <c r="R10" s="12">
         <f>VLOOKUP(A:A,MASTER!A:L,12,0)</f>
         <v>3923</v>
       </c>
-      <c r="N10" s="12">
+      <c r="S10" s="12">
         <f>VLOOKUP(A:A,MASTER!A:M,13,0)</f>
         <v>4320</v>
       </c>
-    </row>
-    <row r="11" spans="1:14" ht="64.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="T10" s="16">
+        <f t="shared" si="5"/>
+        <v>-9.1898148148148118E-2</v>
+      </c>
+    </row>
+    <row r="11" spans="1:20" ht="64.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A11" s="4" t="s">
         <v>12</v>
       </c>
@@ -985,48 +1198,72 @@
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
         <v>48193473.258935727</v>
       </c>
-      <c r="E11" s="5">
+      <c r="E11" s="16">
+        <f t="shared" si="0"/>
+        <v>-4.5414298894973282E-2</v>
+      </c>
+      <c r="F11" s="5">
         <f>VLOOKUP(A:A,MASTER!A:H,8,0)</f>
         <v>20322522.522522524</v>
       </c>
-      <c r="F11" s="5">
+      <c r="G11" s="5">
         <f>VLOOKUP(A:A,MASTER!A:I,9,0)</f>
         <v>54569369.369369365</v>
       </c>
-      <c r="G11" s="5">
+      <c r="H11" s="16">
+        <f t="shared" si="1"/>
+        <v>-0.62758370204054681</v>
+      </c>
+      <c r="I11" s="5">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
         <v>6317342.3423423441</v>
       </c>
-      <c r="H11" s="5">
+      <c r="J11" s="5">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
         <v>668468.46846846805</v>
       </c>
-      <c r="I11" s="5">
+      <c r="K11" s="16">
+        <f t="shared" si="2"/>
+        <v>8.4504716981132155</v>
+      </c>
+      <c r="L11" s="5">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
         <v>18725216.216216218</v>
       </c>
-      <c r="J11" s="5">
+      <c r="M11" s="5">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
         <v>21205837.837837841</v>
       </c>
-      <c r="K11" s="5">
+      <c r="N11" s="16">
+        <f t="shared" si="3"/>
+        <v>-0.11697824158569292</v>
+      </c>
+      <c r="O11" s="5">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
         <v>5006306.3063063072</v>
       </c>
-      <c r="L11" s="5">
+      <c r="P11" s="5">
         <f>VLOOKUP(A:A,MASTER!A:C,3,0)</f>
         <v>2107207.2072072071</v>
       </c>
-      <c r="M11" s="12">
+      <c r="Q11" s="16">
+        <f t="shared" si="4"/>
+        <v>1.3758016246259093</v>
+      </c>
+      <c r="R11" s="12">
         <f>VLOOKUP(A:A,MASTER!A:L,12,0)</f>
         <v>3761</v>
       </c>
-      <c r="N11" s="12">
+      <c r="S11" s="12">
         <f>VLOOKUP(A:A,MASTER!A:M,13,0)</f>
         <v>3023</v>
       </c>
-    </row>
-    <row r="12" spans="1:14" ht="64.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="T11" s="16">
+        <f t="shared" si="5"/>
+        <v>0.24412834932186578</v>
+      </c>
+    </row>
+    <row r="12" spans="1:20" ht="64.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A12" s="4" t="s">
         <v>1</v>
       </c>
@@ -1041,48 +1278,72 @@
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
         <v>192986083.8231118</v>
       </c>
-      <c r="E12" s="5">
+      <c r="E12" s="16">
+        <f t="shared" si="0"/>
+        <v>-4.7056178669848125E-2</v>
+      </c>
+      <c r="F12" s="5">
         <f>VLOOKUP(A:A,MASTER!A:H,8,0)</f>
         <v>1169369.369369373</v>
       </c>
-      <c r="F12" s="5">
+      <c r="G12" s="5">
         <f>VLOOKUP(A:A,MASTER!A:I,9,0)</f>
         <v>991891.89189189195</v>
       </c>
-      <c r="G12" s="5">
+      <c r="H12" s="16">
+        <f t="shared" si="1"/>
+        <v>0.1789282470481417</v>
+      </c>
+      <c r="I12" s="5">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
         <v>23693963.963963963</v>
       </c>
-      <c r="H12" s="5">
+      <c r="J12" s="5">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
         <v>25470495.495495494</v>
       </c>
-      <c r="I12" s="5">
+      <c r="K12" s="16">
+        <f t="shared" si="2"/>
+        <v>-6.9748605080953929E-2</v>
+      </c>
+      <c r="L12" s="5">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
         <v>88503036.036036029</v>
       </c>
-      <c r="J12" s="5">
+      <c r="M12" s="5">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
         <v>90365315.315315306</v>
       </c>
-      <c r="K12" s="5">
+      <c r="N12" s="16">
+        <f t="shared" si="3"/>
+        <v>-2.0608341516666573E-2</v>
+      </c>
+      <c r="O12" s="5">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
         <v>21230630.630630627</v>
       </c>
-      <c r="L12" s="5">
+      <c r="P12" s="5">
         <f>VLOOKUP(A:A,MASTER!A:C,3,0)</f>
         <v>24296351.351351351</v>
       </c>
-      <c r="M12" s="12">
+      <c r="Q12" s="16">
+        <f t="shared" si="4"/>
+        <v>-0.12618029252158514</v>
+      </c>
+      <c r="R12" s="12">
         <f>VLOOKUP(A:A,MASTER!A:L,12,0)</f>
         <v>7988</v>
       </c>
-      <c r="N12" s="12">
+      <c r="S12" s="12">
         <f>VLOOKUP(A:A,MASTER!A:M,13,0)</f>
         <v>7928</v>
       </c>
-    </row>
-    <row r="13" spans="1:14" ht="64.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="T12" s="16">
+        <f t="shared" si="5"/>
+        <v>7.5681130171543209E-3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:20" ht="64.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A13" s="4" t="s">
         <v>3</v>
       </c>
@@ -1097,48 +1358,72 @@
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
         <v>123312636.9197247</v>
       </c>
-      <c r="E13" s="5">
+      <c r="E13" s="16">
+        <f t="shared" si="0"/>
+        <v>0.12159799326363752</v>
+      </c>
+      <c r="F13" s="5">
         <f>VLOOKUP(A:A,MASTER!A:H,8,0)</f>
         <v>2074774.774774777</v>
       </c>
-      <c r="F13" s="5">
+      <c r="G13" s="5">
         <f>VLOOKUP(A:A,MASTER!A:I,9,0)</f>
         <v>736486.48648648697</v>
       </c>
-      <c r="G13" s="5">
+      <c r="H13" s="16">
+        <f t="shared" si="1"/>
+        <v>1.817125382262998</v>
+      </c>
+      <c r="I13" s="5">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
         <v>21102702.702702705</v>
       </c>
-      <c r="H13" s="5">
+      <c r="J13" s="5">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
         <v>57778378.378378376</v>
       </c>
-      <c r="I13" s="5">
+      <c r="K13" s="16">
+        <f t="shared" si="2"/>
+        <v>-0.63476471138553647</v>
+      </c>
+      <c r="L13" s="5">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
         <v>39286729.729729727</v>
       </c>
-      <c r="J13" s="5">
+      <c r="M13" s="5">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
         <v>35456774.774774775</v>
       </c>
-      <c r="K13" s="5">
+      <c r="N13" s="16">
+        <f t="shared" si="3"/>
+        <v>0.10801757856666994</v>
+      </c>
+      <c r="O13" s="5">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
         <v>20983423.423423424</v>
       </c>
-      <c r="L13" s="5">
+      <c r="P13" s="5">
         <f>VLOOKUP(A:A,MASTER!A:C,3,0)</f>
         <v>55497477.477477483</v>
       </c>
-      <c r="M13" s="12">
+      <c r="Q13" s="16">
+        <f t="shared" si="4"/>
+        <v>-0.6219031138498301</v>
+      </c>
+      <c r="R13" s="12">
         <f>VLOOKUP(A:A,MASTER!A:L,12,0)</f>
         <v>3555</v>
       </c>
-      <c r="N13" s="12">
+      <c r="S13" s="12">
         <f>VLOOKUP(A:A,MASTER!A:M,13,0)</f>
         <v>3341</v>
       </c>
-    </row>
-    <row r="14" spans="1:14" ht="64.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="T13" s="16">
+        <f t="shared" si="5"/>
+        <v>6.4052678838671051E-2</v>
+      </c>
+    </row>
+    <row r="14" spans="1:20" ht="64.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A14" s="4" t="s">
         <v>4</v>
       </c>
@@ -1153,48 +1438,72 @@
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
         <v>80170332.138596565</v>
       </c>
-      <c r="E14" s="5">
+      <c r="E14" s="16">
+        <f t="shared" si="0"/>
+        <v>5.772676502260099E-2</v>
+      </c>
+      <c r="F14" s="5">
         <f>VLOOKUP(A:A,MASTER!A:H,8,0)</f>
         <v>92810810.810810819</v>
       </c>
-      <c r="F14" s="5">
+      <c r="G14" s="5">
         <f>VLOOKUP(A:A,MASTER!A:I,9,0)</f>
         <v>26846846.846846849</v>
       </c>
-      <c r="G14" s="5">
+      <c r="H14" s="16">
+        <f t="shared" si="1"/>
+        <v>2.4570469798657717</v>
+      </c>
+      <c r="I14" s="5">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
         <v>34687387.387387387</v>
       </c>
-      <c r="H14" s="5">
+      <c r="J14" s="5">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
         <v>49219369.369369365</v>
       </c>
-      <c r="I14" s="5">
+      <c r="K14" s="16">
+        <f t="shared" si="2"/>
+        <v>-0.2952492518326667</v>
+      </c>
+      <c r="L14" s="5">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
         <v>29075063.063063063</v>
       </c>
-      <c r="J14" s="5">
+      <c r="M14" s="5">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
         <v>30874747.747747749</v>
       </c>
-      <c r="K14" s="5">
+      <c r="N14" s="16">
+        <f t="shared" si="3"/>
+        <v>-5.8289858734666744E-2</v>
+      </c>
+      <c r="O14" s="5">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
         <v>22406576.576576576</v>
       </c>
-      <c r="L14" s="5">
+      <c r="P14" s="5">
         <f>VLOOKUP(A:A,MASTER!A:C,3,0)</f>
         <v>27107297.297297295</v>
       </c>
-      <c r="M14" s="12">
+      <c r="Q14" s="16">
+        <f t="shared" si="4"/>
+        <v>-0.17341163411335003</v>
+      </c>
+      <c r="R14" s="12">
         <f>VLOOKUP(A:A,MASTER!A:L,12,0)</f>
         <v>3611</v>
       </c>
-      <c r="N14" s="12">
+      <c r="S14" s="12">
         <f>VLOOKUP(A:A,MASTER!A:M,13,0)</f>
         <v>3458</v>
       </c>
-    </row>
-    <row r="15" spans="1:14" ht="64.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="T14" s="16">
+        <f t="shared" si="5"/>
+        <v>4.4245228455754848E-2</v>
+      </c>
+    </row>
+    <row r="15" spans="1:20" ht="64.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A15" s="4" t="s">
         <v>5</v>
       </c>
@@ -1209,48 +1518,72 @@
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
         <v>91368737.558266193</v>
       </c>
-      <c r="E15" s="5">
+      <c r="E15" s="16">
+        <f t="shared" si="0"/>
+        <v>4.9054311317309196E-3</v>
+      </c>
+      <c r="F15" s="5">
         <f>VLOOKUP(A:A,MASTER!A:H,8,0)</f>
         <v>282350956.75675678</v>
       </c>
-      <c r="F15" s="5">
+      <c r="G15" s="5">
         <f>VLOOKUP(A:A,MASTER!A:I,9,0)</f>
         <v>329410634.23423421</v>
       </c>
-      <c r="G15" s="5">
+      <c r="H15" s="16">
+        <f t="shared" si="1"/>
+        <v>-0.1428602254656256</v>
+      </c>
+      <c r="I15" s="5">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
         <v>27727027.027027026</v>
       </c>
-      <c r="H15" s="5">
+      <c r="J15" s="5">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
         <v>40603603.603603601</v>
       </c>
-      <c r="I15" s="5">
+      <c r="K15" s="16">
+        <f t="shared" si="2"/>
+        <v>-0.31712891058353676</v>
+      </c>
+      <c r="L15" s="5">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
         <v>37416090.090090089</v>
       </c>
-      <c r="J15" s="5">
+      <c r="M15" s="5">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
         <v>38265747.747747742</v>
       </c>
-      <c r="K15" s="5">
+      <c r="N15" s="16">
+        <f t="shared" si="3"/>
+        <v>-2.2204130525782406E-2</v>
+      </c>
+      <c r="O15" s="5">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
         <v>7046846.8468468469</v>
       </c>
-      <c r="L15" s="5">
+      <c r="P15" s="5">
         <f>VLOOKUP(A:A,MASTER!A:C,3,0)</f>
         <v>10431711.711711714</v>
       </c>
-      <c r="M15" s="12">
+      <c r="Q15" s="16">
+        <f t="shared" si="4"/>
+        <v>-0.3244783750172725</v>
+      </c>
+      <c r="R15" s="12">
         <f>VLOOKUP(A:A,MASTER!A:L,12,0)</f>
         <v>3025</v>
       </c>
-      <c r="N15" s="12">
+      <c r="S15" s="12">
         <f>VLOOKUP(A:A,MASTER!A:M,13,0)</f>
         <v>2849</v>
       </c>
-    </row>
-    <row r="16" spans="1:14" ht="64.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="T15" s="16">
+        <f t="shared" si="5"/>
+        <v>6.1776061776061875E-2</v>
+      </c>
+    </row>
+    <row r="16" spans="1:20" ht="64.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A16" s="4" t="s">
         <v>8</v>
       </c>
@@ -1265,48 +1598,72 @@
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
         <v>110255442.7059771</v>
       </c>
-      <c r="E16" s="5">
+      <c r="E16" s="16">
+        <f t="shared" si="0"/>
+        <v>-7.2697811428624526E-2</v>
+      </c>
+      <c r="F16" s="5">
         <f>VLOOKUP(A:A,MASTER!A:H,8,0)</f>
         <v>1369369.3693693711</v>
       </c>
-      <c r="F16" s="5">
+      <c r="G16" s="5">
         <f>VLOOKUP(A:A,MASTER!A:I,9,0)</f>
         <v>1220720.72072072</v>
       </c>
-      <c r="G16" s="5">
+      <c r="H16" s="16">
+        <f t="shared" si="1"/>
+        <v>0.12177121771217925</v>
+      </c>
+      <c r="I16" s="5">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
         <v>12986486.486486487</v>
       </c>
-      <c r="H16" s="5">
+      <c r="J16" s="5">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
         <v>23015315.315315321</v>
       </c>
-      <c r="I16" s="5">
+      <c r="K16" s="16">
+        <f t="shared" si="2"/>
+        <v>-0.43574588014248261</v>
+      </c>
+      <c r="L16" s="5">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
         <v>29770711.711711712</v>
       </c>
-      <c r="J16" s="5">
+      <c r="M16" s="5">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
         <v>32746891.891891893</v>
       </c>
-      <c r="K16" s="5">
+      <c r="N16" s="16">
+        <f t="shared" si="3"/>
+        <v>-9.0884355987295384E-2</v>
+      </c>
+      <c r="O16" s="5">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
         <v>12479819.819819819</v>
       </c>
-      <c r="L16" s="5">
+      <c r="P16" s="5">
         <f>VLOOKUP(A:A,MASTER!A:C,3,0)</f>
         <v>21886666.666666668</v>
       </c>
-      <c r="M16" s="12">
+      <c r="Q16" s="16">
+        <f t="shared" si="4"/>
+        <v>-0.4297980587959267</v>
+      </c>
+      <c r="R16" s="12">
         <f>VLOOKUP(A:A,MASTER!A:L,12,0)</f>
         <v>3696</v>
       </c>
-      <c r="N16" s="12">
+      <c r="S16" s="12">
         <f>VLOOKUP(A:A,MASTER!A:M,13,0)</f>
         <v>3783</v>
       </c>
-    </row>
-    <row r="17" spans="1:14" ht="64.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="T16" s="16">
+        <f t="shared" si="5"/>
+        <v>-2.2997620935765295E-2</v>
+      </c>
+    </row>
+    <row r="17" spans="1:20" ht="64.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A17" s="4" t="s">
         <v>9</v>
       </c>
@@ -1321,48 +1678,72 @@
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
         <v>195955976.21289811</v>
       </c>
-      <c r="E17" s="5">
+      <c r="E17" s="16">
+        <f t="shared" si="0"/>
+        <v>3.8636099198458229E-2</v>
+      </c>
+      <c r="F17" s="5">
         <f>VLOOKUP(A:A,MASTER!A:H,8,0)</f>
         <v>1590090.0900900939</v>
       </c>
-      <c r="F17" s="5">
+      <c r="G17" s="5">
         <f>VLOOKUP(A:A,MASTER!A:I,9,0)</f>
         <v>1042792.792792793</v>
       </c>
-      <c r="G17" s="5">
+      <c r="H17" s="16">
+        <f t="shared" si="1"/>
+        <v>0.5248380129589667</v>
+      </c>
+      <c r="I17" s="5">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
         <v>223312612.61261261</v>
       </c>
-      <c r="H17" s="5">
+      <c r="J17" s="5">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
         <v>314359819.81981987</v>
       </c>
-      <c r="I17" s="5">
+      <c r="K17" s="16">
+        <f t="shared" si="2"/>
+        <v>-0.28962736796131372</v>
+      </c>
+      <c r="L17" s="5">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
         <v>74621135.135135129</v>
       </c>
-      <c r="J17" s="5">
+      <c r="M17" s="5">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
         <v>71049333.333333343</v>
       </c>
-      <c r="K17" s="5">
+      <c r="N17" s="16">
+        <f t="shared" si="3"/>
+        <v>5.0272136756644992E-2</v>
+      </c>
+      <c r="O17" s="5">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
         <v>206395945.94594595</v>
       </c>
-      <c r="L17" s="5">
+      <c r="P17" s="5">
         <f>VLOOKUP(A:A,MASTER!A:C,3,0)</f>
         <v>261121711.7117117</v>
       </c>
-      <c r="M17" s="12">
+      <c r="Q17" s="16">
+        <f t="shared" si="4"/>
+        <v>-0.20957953058374967</v>
+      </c>
+      <c r="R17" s="12">
         <f>VLOOKUP(A:A,MASTER!A:L,12,0)</f>
         <v>7017</v>
       </c>
-      <c r="N17" s="12">
+      <c r="S17" s="12">
         <f>VLOOKUP(A:A,MASTER!A:M,13,0)</f>
         <v>6930</v>
       </c>
-    </row>
-    <row r="18" spans="1:14" ht="64.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="T17" s="16">
+        <f t="shared" si="5"/>
+        <v>1.2554112554112651E-2</v>
+      </c>
+    </row>
+    <row r="18" spans="1:20" ht="64.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A18" s="4" t="s">
         <v>13</v>
       </c>
@@ -1377,48 +1758,72 @@
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
         <v>161782311.04450738</v>
       </c>
-      <c r="E18" s="5">
+      <c r="E18" s="16">
+        <f t="shared" si="0"/>
+        <v>2.8582012958676017E-2</v>
+      </c>
+      <c r="F18" s="5">
         <f>VLOOKUP(A:A,MASTER!A:H,8,0)</f>
         <v>970270.27027027204</v>
       </c>
-      <c r="F18" s="5">
+      <c r="G18" s="5">
         <f>VLOOKUP(A:A,MASTER!A:I,9,0)</f>
         <v>492342.342342344</v>
       </c>
-      <c r="G18" s="5">
+      <c r="H18" s="16">
+        <f t="shared" si="1"/>
+        <v>0.97072278133577017</v>
+      </c>
+      <c r="I18" s="5">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
         <v>41250900.900900893</v>
       </c>
-      <c r="H18" s="5">
+      <c r="J18" s="5">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
         <v>42441441.441441439</v>
       </c>
-      <c r="I18" s="5">
+      <c r="K18" s="16">
+        <f t="shared" si="2"/>
+        <v>-2.8051369136064652E-2</v>
+      </c>
+      <c r="L18" s="5">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
         <v>94641486.48648648</v>
       </c>
-      <c r="J18" s="5">
+      <c r="M18" s="5">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
         <v>93214702.702702701</v>
       </c>
-      <c r="K18" s="5">
+      <c r="N18" s="16">
+        <f t="shared" si="3"/>
+        <v>1.53064242272416E-2</v>
+      </c>
+      <c r="O18" s="5">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
         <v>40399459.459459454</v>
       </c>
-      <c r="L18" s="5">
+      <c r="P18" s="5">
         <f>VLOOKUP(A:A,MASTER!A:C,3,0)</f>
         <v>45909549.54954955</v>
       </c>
-      <c r="M18" s="12">
+      <c r="Q18" s="16">
+        <f t="shared" si="4"/>
+        <v>-0.12002056531055982</v>
+      </c>
+      <c r="R18" s="12">
         <f>VLOOKUP(A:A,MASTER!A:L,12,0)</f>
         <v>7095</v>
       </c>
-      <c r="N18" s="12">
+      <c r="S18" s="12">
         <f>VLOOKUP(A:A,MASTER!A:M,13,0)</f>
         <v>7045</v>
       </c>
-    </row>
-    <row r="19" spans="1:14" ht="64.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="T18" s="16">
+        <f t="shared" si="5"/>
+        <v>7.0972320794890909E-3</v>
+      </c>
+    </row>
+    <row r="19" spans="1:20" ht="64.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A19" s="4" t="s">
         <v>14</v>
       </c>
@@ -1433,48 +1838,102 @@
         <f>VLOOKUP(A:A,MASTER!A:K,11,0)</f>
         <v>94474395.245280206</v>
       </c>
-      <c r="E19" s="5">
+      <c r="E19" s="16">
+        <f t="shared" si="0"/>
+        <v>-8.4755857757293995E-2</v>
+      </c>
+      <c r="F19" s="5">
         <f>VLOOKUP(A:A,MASTER!A:H,8,0)</f>
         <v>669369.36936937098</v>
       </c>
-      <c r="F19" s="5">
+      <c r="G19" s="5">
         <f>VLOOKUP(A:A,MASTER!A:I,9,0)</f>
         <v>132432.43243243301</v>
       </c>
-      <c r="G19" s="5">
+      <c r="H19" s="16">
+        <f t="shared" si="1"/>
+        <v>4.0544217687074733</v>
+      </c>
+      <c r="I19" s="5">
         <f>VLOOKUP(A:A,MASTER!A:F,6,0)</f>
         <v>25846846.846846849</v>
       </c>
-      <c r="H19" s="5">
+      <c r="J19" s="5">
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
         <v>17729279.27927928</v>
       </c>
-      <c r="I19" s="5">
+      <c r="K19" s="16">
+        <f t="shared" si="2"/>
+        <v>0.45786224243502116</v>
+      </c>
+      <c r="L19" s="5">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>
         <v>29553990.990990993</v>
       </c>
-      <c r="J19" s="5">
+      <c r="M19" s="5">
         <f>VLOOKUP(A:A,MASTER!A:E,5,0)</f>
         <v>33205108.108108107</v>
       </c>
-      <c r="K19" s="5">
+      <c r="N19" s="16">
+        <f t="shared" si="3"/>
+        <v>-0.10995648938199287</v>
+      </c>
+      <c r="O19" s="5">
         <f>VLOOKUP(A:A,MASTER!A:B,2,0)</f>
         <v>28104504.504504506</v>
       </c>
-      <c r="L19" s="5">
+      <c r="P19" s="5">
         <f>VLOOKUP(A:A,MASTER!A:C,3,0)</f>
         <v>16053873.873873873</v>
       </c>
-      <c r="M19" s="12">
+      <c r="Q19" s="16">
+        <f t="shared" si="4"/>
+        <v>0.75063693195209846</v>
+      </c>
+      <c r="R19" s="12">
         <f>VLOOKUP(A:A,MASTER!A:L,12,0)</f>
         <v>4080</v>
       </c>
-      <c r="N19" s="12">
+      <c r="S19" s="12">
         <f>VLOOKUP(A:A,MASTER!A:M,13,0)</f>
         <v>4058</v>
       </c>
+      <c r="T19" s="16">
+        <f t="shared" si="5"/>
+        <v>5.4213898472152966E-3</v>
+      </c>
     </row>
   </sheetData>
+  <conditionalFormatting sqref="E6:E19">
+    <cfRule type="cellIs" dxfId="5" priority="6" operator="lessThan">
+      <formula>0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H6:H19">
+    <cfRule type="cellIs" dxfId="4" priority="5" operator="lessThan">
+      <formula>0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K6:K19">
+    <cfRule type="cellIs" dxfId="3" priority="4" operator="lessThan">
+      <formula>0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="N6:N19">
+    <cfRule type="cellIs" dxfId="2" priority="3" operator="lessThan">
+      <formula>0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="Q6:Q19">
+    <cfRule type="cellIs" dxfId="1" priority="2" operator="lessThan">
+      <formula>0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="T6:T19">
+    <cfRule type="cellIs" dxfId="0" priority="1" operator="lessThan">
+      <formula>0</formula>
+    </cfRule>
+  </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="360" verticalDpi="360" r:id="rId1"/>
 </worksheet>

--- a/MS BENGKAYANG 19 JULI 2026.xlsx
+++ b/MS BENGKAYANG 19 JULI 2026.xlsx
@@ -1062,9 +1062,9 @@
         <f>VLOOKUP(A:A,MASTER!A:G,7,0)</f>
         <v>0</v>
       </c>
-      <c r="K9" s="16" t="e">
-        <f t="shared" si="2"/>
-        <v>#DIV/0!</v>
+      <c r="K9" s="16">
+        <f>IFERROR(I9/J9-1,0)</f>
+        <v>0</v>
       </c>
       <c r="L9" s="5">
         <f>VLOOKUP(A:A,MASTER!A:D,4,0)</f>

--- a/MS BENGKAYANG 19 JULI 2026.xlsx
+++ b/MS BENGKAYANG 19 JULI 2026.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="19200" windowHeight="6640" activeTab="1"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="19200" windowHeight="6640"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -18,7 +18,7 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$5:$T$22</definedName>
   </definedNames>
-  <calcPr calcId="162913"/>
+  <calcPr calcId="162913" iterate="1"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
